--- a/la-marinka/La Marinka.xlsx
+++ b/la-marinka/La Marinka.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Budget étage" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Paramètres" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Synthèse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Budget étage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Budget RDC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Paramètres" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -117,26 +119,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -222,6 +227,21 @@
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="M4" authorId="0" shapeId="0">
+      <text>
+        <t>Saisissez ici le montant TTC du devis : il remplace la moyenne dans « Montant retenu ».</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Claude</author>
@@ -525,11 +545,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>La Marinka — Synthèse du budget travaux (hors ameublement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Niveau</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Total min €</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Total max €</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Auto min €</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Auto max €</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Montant retenu €</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Étage (4 chambres + 4 SdE + WC)</t>
+        </is>
+      </c>
+      <c r="B4" s="4">
+        <f>'Budget étage'!G39</f>
+        <v/>
+      </c>
+      <c r="C4" s="4">
+        <f>'Budget étage'!H39</f>
+        <v/>
+      </c>
+      <c r="D4" s="4">
+        <f>'Budget étage'!K39</f>
+        <v/>
+      </c>
+      <c r="E4" s="4">
+        <f>'Budget étage'!L39</f>
+        <v/>
+      </c>
+      <c r="F4" s="4">
+        <f>'Budget étage'!N39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Rez-de-chaussée (séjour, baie galandage)</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>'Budget RDC'!G27</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>'Budget RDC'!H27</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>'Budget RDC'!K27</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>'Budget RDC'!L27</f>
+        <v/>
+      </c>
+      <c r="F5" s="4">
+        <f>'Budget RDC'!N27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL TRAVAUX TTC</t>
+        </is>
+      </c>
+      <c r="B6" s="6">
+        <f>SUM(B4:B5)</f>
+        <v/>
+      </c>
+      <c r="C6" s="6">
+        <f>SUM(C4:C5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="6">
+        <f>SUM(D4:D5)</f>
+        <v/>
+      </c>
+      <c r="E6" s="6">
+        <f>SUM(E4:E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="6">
+        <f>SUM(F4:F5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Postes hors budget (Paramètres)</t>
+        </is>
+      </c>
+      <c r="B8" s="8">
+        <f>Paramètres!B15</f>
+        <v/>
+      </c>
+      <c r="C8" s="8">
+        <f>Paramètres!C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Enveloppe globale (travaux + hors budget)</t>
+        </is>
+      </c>
+      <c r="B9" s="9">
+        <f>B6+B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="9">
+        <f>C6+C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Ameublement non compris. Escalier compté une seule fois (onglet étage).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -542,7 +741,7 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,1647 +752,1632 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Prix TTC indicatifs (marché France 2025-2026, entreprise). Cellules en BLEU = à ajuster ; colonne JAUNE « Devis reçu » = à remplir au fil des devis (remplace alors la moyenne).</t>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Prix TTC indicatifs (marché France 2025-2026, entreprise), travaux seuls sans ameublement. Cellules en BLEU = à ajuster ; colonne JAUNE « Devis reçu » = à remplir au fil des devis.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Lot</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Unité</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Qté</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>PU min €</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>PU max €</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Total min €</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Total max €</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Faisable soi-même</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Part matériaux</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Auto min €</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Auto max €</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Devis reçu €</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Montant retenu €</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Gros œuvre</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="12" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Nouvelle trémie, reprise solivage, rebouchage ancienne trémie</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="15" t="n">
         <v>3000</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="15" t="n">
         <v>8000</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="16">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="16">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="16">
         <f>IF(I6="Oui",G6*J6,G6)</f>
         <v/>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="16">
         <f>IF(I6="Oui",H6*J6,H6)</f>
         <v/>
       </c>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="10">
+      <c r="M6" s="18" t="n"/>
+      <c r="N6" s="16">
         <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
         <v/>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>Avis BET structure.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Étude BET structure</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="15" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="16">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="16">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="16">
         <f>IF(I7="Oui",G7*J7,G7)</f>
         <v/>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="16">
         <f>IF(I7="Oui",H7*J7,H7)</f>
         <v/>
       </c>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="10">
+      <c r="M7" s="18" t="n"/>
+      <c r="N7" s="16">
         <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
         <v/>
       </c>
-      <c r="O7" s="7" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Escalier bois ¼ tournant sur mesure, posé</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="15" t="n">
         <v>4000</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="15" t="n">
         <v>9000</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="16">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="16">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="16">
         <f>IF(I8="Oui",G8*J8,G8)</f>
         <v/>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="16">
         <f>IF(I8="Oui",H8*J8,H8)</f>
         <v/>
       </c>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="10">
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="16">
         <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
         <v/>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>Kit à poser soi-même : 1 500 – 3 000 €.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Enveloppe / isolation</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Isolation rampants fibre de bois</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="15" t="n">
         <v>120</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="16">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="16">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="17" t="n">
         <v>0.55</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="16">
         <f>IF(I10="Oui",G10*J10,G10)</f>
         <v/>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="16">
         <f>IF(I10="Oui",H10*J10,H10)</f>
         <v/>
       </c>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="10">
+      <c r="M10" s="18" t="n"/>
+      <c r="N10" s="16">
         <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
         <v/>
       </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>Surface de rampants à métrer.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Velux 78×98 posés + raccords</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="15" t="n">
         <v>1600</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="16">
         <f>D11*E11</f>
         <v/>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="16">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="16">
         <f>IF(I11="Oui",G11*J11,G11)</f>
         <v/>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="16">
         <f>IF(I11="Oui",H11*J11,H11)</f>
         <v/>
       </c>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="10">
+      <c r="M11" s="18" t="n"/>
+      <c r="N11" s="16">
         <f>IF(N(M11)&gt;0,M11,(G11+H11)/2)</f>
         <v/>
       </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>Étanchéité : à confier à un pro.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Velux 55×78 posé (dégagement)</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="15" t="n">
         <v>800</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="15" t="n">
         <v>1300</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="16">
         <f>D12*E12</f>
         <v/>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="16">
         <f>D12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="16">
         <f>IF(I12="Oui",G12*J12,G12)</f>
         <v/>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="16">
         <f>IF(I12="Oui",H12*J12,H12)</f>
         <v/>
       </c>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="10">
+      <c r="M12" s="18" t="n"/>
+      <c r="N12" s="16">
         <f>IF(N(M12)&gt;0,M12,(G12+H12)/2)</f>
         <v/>
       </c>
-      <c r="O12" s="7" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Doublage murs pisé (lame d'air + isolant perspirant + placo)</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="15" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="16">
         <f>D13*E13</f>
         <v/>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="16">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J13" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="16">
         <f>IF(I13="Oui",G13*J13,G13)</f>
         <v/>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="16">
         <f>IF(I13="Oui",H13*J13,H13)</f>
         <v/>
       </c>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="10">
+      <c r="M13" s="18" t="n"/>
+      <c r="N13" s="16">
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>Pas de pare-vapeur étanche.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Cloisons / plafonds</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Cloisons placo 72/48 + laine (dont 2 en 10 cm galandage)</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="16">
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="16">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" s="17" t="n">
         <v>0.45</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="16">
         <f>IF(I15="Oui",G15*J15,G15)</f>
         <v/>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="16">
         <f>IF(I15="Oui",H15*J15,H15)</f>
         <v/>
       </c>
-      <c r="M15" s="12" t="n"/>
-      <c r="N15" s="10">
+      <c r="M15" s="18" t="n"/>
+      <c r="N15" s="16">
         <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
         <v/>
       </c>
-      <c r="O15" s="7" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Finition plafonds / habillage sous rampant</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="16">
         <f>D16*E16</f>
         <v/>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="16">
         <f>D16*F16</f>
         <v/>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="17" t="n">
         <v>0.45</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="16">
         <f>IF(I16="Oui",G16*J16,G16)</f>
         <v/>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="16">
         <f>IF(I16="Oui",H16*J16,H16)</f>
         <v/>
       </c>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="10">
+      <c r="M16" s="18" t="n"/>
+      <c r="N16" s="16">
         <f>IF(N(M16)&gt;0,M16,(G16+H16)/2)</f>
         <v/>
       </c>
-      <c r="O16" s="7" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Plomberie</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Salle d'eau complète (douche 120×80, vasque, sèche-serviettes)</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="15" t="n">
         <v>5000</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="15" t="n">
         <v>9000</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="16">
         <f>D18*E18</f>
         <v/>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="16">
         <f>D18*F18</f>
         <v/>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="16">
         <f>IF(I18="Oui",G18*J18,G18)</f>
         <v/>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="16">
         <f>IF(I18="Oui",H18*J18,H18)</f>
         <v/>
       </c>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="10">
+      <c r="M18" s="18" t="n"/>
+      <c r="N18" s="16">
         <f>IF(N(M18)&gt;0,M18,(G18+H18)/2)</f>
         <v/>
       </c>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>Poste le plus lourd.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>WC suspendu + lave-mains</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="15" t="n">
         <v>3000</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="16">
         <f>D19*E19</f>
         <v/>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="16">
         <f>D19*F19</f>
         <v/>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J19" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="16">
         <f>IF(I19="Oui",G19*J19,G19)</f>
         <v/>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="16">
         <f>IF(I19="Oui",H19*J19,H19)</f>
         <v/>
       </c>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="10">
+      <c r="M19" s="18" t="n"/>
+      <c r="N19" s="16">
         <f>IF(N(M19)&gt;0,M19,(G19+H19)/2)</f>
         <v/>
       </c>
-      <c r="O19" s="7" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Réseaux alimentation / évacuations / chutes</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="16">
         <f>D20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="16">
         <f>D20*F20</f>
         <v/>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J20" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="16">
         <f>IF(I20="Oui",G20*J20,G20)</f>
         <v/>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="16">
         <f>IF(I20="Oui",H20*J20,H20)</f>
         <v/>
       </c>
-      <c r="M20" s="12" t="n"/>
-      <c r="N20" s="10">
+      <c r="M20" s="18" t="n"/>
+      <c r="N20" s="16">
         <f>IF(N(M20)&gt;0,M20,(G20+H20)/2)</f>
         <v/>
       </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>2 descentes (Est et Ouest).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Production eau chaude (ballon 200-300 L)</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="15" t="n">
         <v>2000</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="15" t="n">
         <v>4000</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="16">
         <f>D21*E21</f>
         <v/>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="16">
         <f>D21*F21</f>
         <v/>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J21" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="16">
         <f>IF(I21="Oui",G21*J21,G21)</f>
         <v/>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="16">
         <f>IF(I21="Oui",H21*J21,H21)</f>
         <v/>
       </c>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="10">
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="16">
         <f>IF(N(M21)&gt;0,M21,(G21+H21)/2)</f>
         <v/>
       </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>Thermodynamique = haut de fourchette.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Électricité / ventilation / chauffage</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Électricité neuve NF C 15-100</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="14" t="n">
         <v>77</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="16">
         <f>D23*E23</f>
         <v/>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="16">
         <f>D23*F23</f>
         <v/>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="J23" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="16">
         <f>IF(I23="Oui",G23*J23,G23)</f>
         <v/>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="16">
         <f>IF(I23="Oui",H23*J23,H23)</f>
         <v/>
       </c>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="10">
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="16">
         <f>IF(N(M23)&gt;0,M23,(G23+H23)/2)</f>
         <v/>
       </c>
-      <c r="O23" s="7" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>VMC hygro B (4 SdE + WC)</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="15" t="n">
         <v>3000</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="16">
         <f>D24*E24</f>
         <v/>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="16">
         <f>D24*F24</f>
         <v/>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="J24" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="16">
         <f>IF(I24="Oui",G24*J24,G24)</f>
         <v/>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="16">
         <f>IF(I24="Oui",H24*J24,H24)</f>
         <v/>
       </c>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="10">
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="16">
         <f>IF(N(M24)&gt;0,M24,(G24+H24)/2)</f>
         <v/>
       </c>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t>Obligatoire : SdE et WC sans ouvrant.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Chauffage (radiateurs inertie ou PAC air/air)</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="15" t="n">
         <v>4000</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="15" t="n">
         <v>12000</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="16">
         <f>D25*E25</f>
         <v/>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="16">
         <f>D25*F25</f>
         <v/>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J25" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="16">
         <f>IF(I25="Oui",G25*J25,G25)</f>
         <v/>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="16">
         <f>IF(I25="Oui",H25*J25,H25)</f>
         <v/>
       </c>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="10">
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="16">
         <f>IF(N(M25)&gt;0,M25,(G25+H25)/2)</f>
         <v/>
       </c>
-      <c r="O25" s="7" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Menuiseries intérieures</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="12" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Portes battantes posées</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="15" t="n">
         <v>550</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="16">
         <f>D27*E27</f>
         <v/>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="16">
         <f>D27*F27</f>
         <v/>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J27" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="16">
         <f>IF(I27="Oui",G27*J27,G27)</f>
         <v/>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="16">
         <f>IF(I27="Oui",H27*J27,H27)</f>
         <v/>
       </c>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="10">
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="16">
         <f>IF(N(M27)&gt;0,M27,(G27+H27)/2)</f>
         <v/>
       </c>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="O27" s="3" t="inlineStr">
         <is>
           <t>4 chambres, SdE 3-4, WC.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Portes à galandage (SdE 1-2) avec caisson</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="15" t="n">
         <v>700</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="16">
         <f>D28*E28</f>
         <v/>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="16">
         <f>D28*F28</f>
         <v/>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J28" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="16">
         <f>IF(I28="Oui",G28*J28,G28)</f>
         <v/>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="16">
         <f>IF(I28="Oui",H28*J28,H28)</f>
         <v/>
       </c>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="10">
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="16">
         <f>IF(N(M28)&gt;0,M28,(G28+H28)/2)</f>
         <v/>
       </c>
-      <c r="O28" s="7" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Façades rangements sous rampant</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="15" t="n">
         <v>700</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="16">
         <f>D29*E29</f>
         <v/>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="16">
         <f>D29*F29</f>
         <v/>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="J29" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="16">
         <f>IF(I29="Oui",G29*J29,G29)</f>
         <v/>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="16">
         <f>IF(I29="Oui",H29*J29,H29)</f>
         <v/>
       </c>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="10">
+      <c r="M29" s="18" t="n"/>
+      <c r="N29" s="16">
         <f>IF(N(M29)&gt;0,M29,(G29+H29)/2)</f>
         <v/>
       </c>
-      <c r="O29" s="7" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Revêtements / finitions</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
-      <c r="O30" s="5" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="12" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Parquet chambres + dégagement</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="14" t="n">
         <v>51</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="15" t="n">
         <v>90</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="16">
         <f>D31*E31</f>
         <v/>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="16">
         <f>D31*F31</f>
         <v/>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J31" s="17" t="n">
         <v>0.6</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="16">
         <f>IF(I31="Oui",G31*J31,G31)</f>
         <v/>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="16">
         <f>IF(I31="Oui",H31*J31,H31)</f>
         <v/>
       </c>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="10">
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="16">
         <f>IF(N(M31)&gt;0,M31,(G31+H31)/2)</f>
         <v/>
       </c>
-      <c r="O31" s="7" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Carrelage sols SdE + WC</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="16">
         <f>D32*E32</f>
         <v/>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="16">
         <f>D32*F32</f>
         <v/>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J32" s="11" t="n">
+      <c r="J32" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="16">
         <f>IF(I32="Oui",G32*J32,G32)</f>
         <v/>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="16">
         <f>IF(I32="Oui",H32*J32,H32)</f>
         <v/>
       </c>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="10">
+      <c r="M32" s="18" t="n"/>
+      <c r="N32" s="16">
         <f>IF(N(M32)&gt;0,M32,(G32+H32)/2)</f>
         <v/>
       </c>
-      <c r="O32" s="7" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Faïence murale SdE</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="16">
         <f>D33*E33</f>
         <v/>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="16">
         <f>D33*F33</f>
         <v/>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J33" s="11" t="n">
+      <c r="J33" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="16">
         <f>IF(I33="Oui",G33*J33,G33)</f>
         <v/>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="16">
         <f>IF(I33="Oui",H33*J33,H33)</f>
         <v/>
       </c>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="10">
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="16">
         <f>IF(N(M33)&gt;0,M33,(G33+H33)/2)</f>
         <v/>
       </c>
-      <c r="O33" s="7" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Peinture murs + plafonds</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="16">
         <f>D34*E34</f>
         <v/>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="16">
         <f>D34*F34</f>
         <v/>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J34" s="11" t="n">
+      <c r="J34" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="16">
         <f>IF(I34="Oui",G34*J34,G34)</f>
         <v/>
       </c>
-      <c r="L34" s="10">
+      <c r="L34" s="16">
         <f>IF(I34="Oui",H34*J34,H34)</f>
         <v/>
       </c>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="10">
+      <c r="M34" s="18" t="n"/>
+      <c r="N34" s="16">
         <f>IF(N(M34)&gt;0,M34,(G34+H34)/2)</f>
         <v/>
       </c>
-      <c r="O34" s="7" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="9">
         <f>SUM(G5:G34)</f>
         <v/>
       </c>
-      <c r="H36" s="14">
+      <c r="H36" s="9">
         <f>SUM(H5:H34)</f>
         <v/>
       </c>
-      <c r="K36" s="14">
+      <c r="K36" s="9">
         <f>SUM(K5:K34)</f>
         <v/>
       </c>
-      <c r="L36" s="14">
+      <c r="L36" s="9">
         <f>SUM(L5:L34)</f>
         <v/>
       </c>
-      <c r="N36" s="14">
+      <c r="N36" s="9">
         <f>SUM(N5:N34)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>Imprévus</t>
         </is>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="8">
         <f>G36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="H37" s="16">
+      <c r="H37" s="8">
         <f>H36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="8">
         <f>K36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="L37" s="16">
+      <c r="L37" s="8">
         <f>L36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="N37" s="16">
+      <c r="N37" s="8">
         <f>N36*Paramètres!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre</t>
         </is>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="8">
         <f>G36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="8">
         <f>H36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="8">
         <f>K36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="8">
         <f>L36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="N38" s="16">
+      <c r="N38" s="8">
         <f>N36*Paramètres!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="n"/>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="A39" s="20" t="n"/>
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>TOTAL ÉTAGE TTC</t>
         </is>
       </c>
-      <c r="C39" s="17" t="n"/>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="17" t="n"/>
-      <c r="G39" s="19">
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="22">
         <f>G36+G37+G38</f>
         <v/>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="22">
         <f>H36+H37+H38</f>
         <v/>
       </c>
-      <c r="I39" s="17" t="n"/>
-      <c r="J39" s="17" t="n"/>
-      <c r="K39" s="19">
+      <c r="I39" s="20" t="n"/>
+      <c r="J39" s="20" t="n"/>
+      <c r="K39" s="22">
         <f>K36+K37+K38</f>
         <v/>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="22">
         <f>L36+L37+L38</f>
         <v/>
       </c>
-      <c r="M39" s="17" t="n"/>
-      <c r="N39" s="19">
+      <c r="M39" s="20" t="n"/>
+      <c r="N39" s="22">
         <f>N36+N37+N38</f>
         <v/>
       </c>
-      <c r="O39" s="17" t="n"/>
+      <c r="O39" s="20" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Soit par m² (77 m²)</t>
         </is>
       </c>
-      <c r="G40" s="20">
+      <c r="G40" s="23">
         <f>G39/77</f>
         <v/>
       </c>
-      <c r="H40" s="20">
+      <c r="H40" s="23">
         <f>H39/77</f>
         <v/>
       </c>
-      <c r="K40" s="20">
+      <c r="K40" s="23">
         <f>K39/77</f>
         <v/>
       </c>
-      <c r="L40" s="20">
+      <c r="L40" s="23">
         <f>L39/77</f>
         <v/>
       </c>
-      <c r="N40" s="20">
+      <c r="N40" s="23">
         <f>N39/77</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>Postes hors budget (voir onglet Paramètres)</t>
-        </is>
-      </c>
-      <c r="G42" s="16">
-        <f>Paramètres!B15</f>
-        <v/>
-      </c>
-      <c r="H42" s="16">
-        <f>Paramètres!C15</f>
-        <v/>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Lecture : « Total min / max » = fourchette entreprise. « Auto min / max » = coût si vous réalisez vous-même les postes marqués « Oui »</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>(vous ne payez alors que la part matériaux). « Montant retenu » = devis reçu s'il est saisi, sinon la moyenne min/max.</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Lecture : « Total min / max » = fourchette entreprise. « Auto min / max » = coût si vous réalisez vous-même les postes marqués « Oui »</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>(vous ne payez alors que la part matériaux). « Montant retenu » = devis reçu s'il est saisi, sinon la moyenne min/max.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Source : estimations indicatives de prix moyens du marché (ordre de grandeur), à remplacer par les devis d'artisans.</t>
         </is>
@@ -2210,7 +2394,1121 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>La Marinka — Budget estimatif travaux du rez-de-chaussée (77 m²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Prix TTC indicatifs (marché France 2025-2026, entreprise), travaux seuls sans ameublement. Cellules en BLEU = à ajuster ; colonne JAUNE « Devis reçu » = à remplir au fil des devis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Qté</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>PU min €</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>PU max €</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Total min €</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Total max €</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Faisable soi-même</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Part matériaux</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Auto min €</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Auto max €</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Devis reçu €</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Montant retenu €</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Gros œuvre / structure</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="12" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Ouverture 4 m dans le pisé : étaiement, linteau béton ou acier, reprises</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G6" s="16">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="16">
+        <f>D6*F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K6" s="16">
+        <f>IF(I6="Oui",G6*J6,G6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="16">
+        <f>IF(I6="Oui",H6*J6,H6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="18" t="n"/>
+      <c r="N6" s="16">
+        <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
+        <v/>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Intervention la plus lourde du RDC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Étude BET structure (baie 4 m)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="16">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="16">
+        <f>D7*F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="16">
+        <f>IF(I7="Oui",G7*J7,G7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="16">
+        <f>IF(I7="Oui",H7*J7,H7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="18" t="n"/>
+      <c r="N7" s="16">
+        <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
+        <v/>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Obligatoire dans le pisé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Sol : décaissement, hérisson ventilé, dalle isolée (chaux ou béton)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="G8" s="16">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="16">
+        <f>D8*F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K8" s="16">
+        <f>IF(I8="Oui",G8*J8,G8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="16">
+        <f>IF(I8="Oui",H8*J8,H8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="16">
+        <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
+        <v/>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Sol de grange brut ; dalle respirante conseillée avec le pisé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Menuiseries extérieures</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Baie vitrée 4,00 m à galandage, 2 vantaux, posée</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G10" s="16">
+        <f>D10*E10</f>
+        <v/>
+      </c>
+      <c r="H10" s="16">
+        <f>D10*F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K10" s="16">
+        <f>IF(I10="Oui",G10*J10,G10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="16">
+        <f>IF(I10="Oui",H10*J10,H10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="18" t="n"/>
+      <c r="N10" s="16">
+        <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
+        <v/>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Alu ou bois-alu, double vitrage ; caissons compris.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Seuil, bavette, raccords d'étanchéité baie</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G11" s="16">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="H11" s="16">
+        <f>D11*F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="16">
+        <f>IF(I11="Oui",G11*J11,G11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="16">
+        <f>IF(I11="Oui",H11*J11,H11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="18" t="n"/>
+      <c r="N11" s="16">
+        <f>IF(N(M11)&gt;0,M11,(G11+H11)/2)</f>
+        <v/>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Isolation / doublage / plafond</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Doublage murs pisé (lame d'air + isolant perspirant + placo)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="G13" s="16">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="16">
+        <f>D13*F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" s="16">
+        <f>IF(I13="Oui",G13*J13,G13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="16">
+        <f>IF(I13="Oui",H13*J13,H13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="18" t="n"/>
+      <c r="N13" s="16">
+        <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
+        <v/>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>Périmètre 34 m × 2,60 m − baie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Doublage épaissi au droit des caissons galandage</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="16">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="H14" s="16">
+        <f>D14*F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="16">
+        <f>IF(I14="Oui",G14*J14,G14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="16">
+        <f>IF(I14="Oui",H14*J14,H14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="18" t="n"/>
+      <c r="N14" s="16">
+        <f>IF(N(M14)&gt;0,M14,(G14+H14)/2)</f>
+        <v/>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>2 × 2 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Plafond sous plancher étage + isolation phonique</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="G15" s="16">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f>D15*F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K15" s="16">
+        <f>IF(I15="Oui",G15*J15,G15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="16">
+        <f>IF(I15="Oui",H15*J15,H15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="18" t="n"/>
+      <c r="N15" s="16">
+        <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
+        <v/>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>Ou poutres apparentes traitées.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Électricité / chauffage</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Électricité séjour (prises, réseau, mur TV, éclairages table et billard)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="G17" s="16">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="H17" s="16">
+        <f>D17*F17</f>
+        <v/>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K17" s="16">
+        <f>IF(I17="Oui",G17*J17,G17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="16">
+        <f>IF(I17="Oui",H17*J17,H17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="18" t="n"/>
+      <c r="N17" s="16">
+        <f>IF(N(M17)&gt;0,M17,(G17+H17)/2)</f>
+        <v/>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Chauffage (poêle à bois ou PAC air/air)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G18" s="16">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>D18*F18</f>
+        <v/>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K18" s="16">
+        <f>IF(I18="Oui",G18*J18,G18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="16">
+        <f>IF(I18="Oui",H18*J18,H18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="18" t="n"/>
+      <c r="N18" s="16">
+        <f>IF(N(M18)&gt;0,M18,(G18+H18)/2)</f>
+        <v/>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>Poêle : conduit compris.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Revêtements / finitions</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Revêtement de sol (parquet massif ou terre cuite)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="G20" s="16">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+      <c r="H20" s="16">
+        <f>D20*F20</f>
+        <v/>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K20" s="16">
+        <f>IF(I20="Oui",G20*J20,G20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="16">
+        <f>IF(I20="Oui",H20*J20,H20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="18" t="n"/>
+      <c r="N20" s="16">
+        <f>IF(N(M20)&gt;0,M20,(G20+H20)/2)</f>
+        <v/>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Peinture / enduits murs + plafond</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="G21" s="16">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+      <c r="H21" s="16">
+        <f>D21*F21</f>
+        <v/>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K21" s="16">
+        <f>IF(I21="Oui",G21*J21,G21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="16">
+        <f>IF(I21="Oui",H21*J21,H21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="16">
+        <f>IF(N(M21)&gt;0,M21,(G21+H21)/2)</f>
+        <v/>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>Enduit chaux possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Plinthes, finitions, habillage escalier</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>600</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G22" s="16">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>D22*F22</f>
+        <v/>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K22" s="16">
+        <f>IF(I22="Oui",G22*J22,G22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="16">
+        <f>IF(I22="Oui",H22*J22,H22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="18" t="n"/>
+      <c r="N22" s="16">
+        <f>IF(N(M22)&gt;0,M22,(G22+H22)/2)</f>
+        <v/>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>Escalier : compté dans l'onglet étage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Sous-total travaux</t>
+        </is>
+      </c>
+      <c r="G24" s="9">
+        <f>SUM(G5:G22)</f>
+        <v/>
+      </c>
+      <c r="H24" s="9">
+        <f>SUM(H5:H22)</f>
+        <v/>
+      </c>
+      <c r="K24" s="9">
+        <f>SUM(K5:K22)</f>
+        <v/>
+      </c>
+      <c r="L24" s="9">
+        <f>SUM(L5:L22)</f>
+        <v/>
+      </c>
+      <c r="N24" s="9">
+        <f>SUM(N5:N22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Imprévus</t>
+        </is>
+      </c>
+      <c r="G25" s="8">
+        <f>G24*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="H25" s="8">
+        <f>H24*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="K25" s="8">
+        <f>K24*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="L25" s="8">
+        <f>L24*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="N25" s="8">
+        <f>N24*Paramètres!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Maîtrise d'œuvre</t>
+        </is>
+      </c>
+      <c r="G26" s="8">
+        <f>G24*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="H26" s="8">
+        <f>H24*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="K26" s="8">
+        <f>K24*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="L26" s="8">
+        <f>L24*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="N26" s="8">
+        <f>N24*Paramètres!$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="n"/>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>TOTAL RDC TTC</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="22">
+        <f>G24+G25+G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="22">
+        <f>H24+H25+H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="22">
+        <f>K24+K25+K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="22">
+        <f>L24+L25+L26</f>
+        <v/>
+      </c>
+      <c r="M27" s="20" t="n"/>
+      <c r="N27" s="22">
+        <f>N24+N25+N26</f>
+        <v/>
+      </c>
+      <c r="O27" s="20" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Soit par m² (77 m²)</t>
+        </is>
+      </c>
+      <c r="G28" s="23">
+        <f>G27/77</f>
+        <v/>
+      </c>
+      <c r="H28" s="23">
+        <f>H27/77</f>
+        <v/>
+      </c>
+      <c r="K28" s="23">
+        <f>K27/77</f>
+        <v/>
+      </c>
+      <c r="L28" s="23">
+        <f>L27/77</f>
+        <v/>
+      </c>
+      <c r="N28" s="23">
+        <f>N27/77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Lecture : « Total min / max » = fourchette entreprise. « Auto min / max » = coût si vous réalisez vous-même les postes marqués « Oui »</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>(vous ne payez alors que la part matériaux). « Montant retenu » = devis reçu s'il est saisi, sinon la moyenne min/max.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Source : estimations indicatives de prix moyens du marché (ordre de grandeur), à remplacer par les devis d'artisans.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="I6 I7 I8 I10 I11 I13 I14 I15 I17 I18 I20 I21 I22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Oui,Non"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2233,171 +3531,171 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Paramètre</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Imprévus (% des travaux)</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n">
+      <c r="B4" s="25" t="n">
         <v>0.1</v>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Usuel en rénovation de bâti ancien : 10 à 15 %.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre / architecte (% des travaux)</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>0 % si vous pilotez vous-même ; 8 à 12 % avec un maître d'œuvre.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>TVA : prix affichés TTC à 20 % (création de surface habitable dans une grange : taux réduit en principe non applicable).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Postes HORS budget étage (à chiffrer séparément)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Min €</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>Max €</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Couverture / charpente (si à reprendre)</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="27" t="n">
         <v>15000</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="27" t="n">
         <v>40000</v>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>À diagnostiquer en priorité.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Raccordements eau / électricité / assainissement individuel</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="27" t="n">
         <v>8000</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="27" t="n">
         <v>15000</v>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Selon raccordement existant de la grange.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Renfort du plancher / chape</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="27" t="n">
         <v>12000</v>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Si le plancher de l'étage est insuffisant.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Taxe d'aménagement + dossier changement de destination</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="27" t="n">
         <v>2000</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>Selon taux communal et départemental.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Total hors budget</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="9">
         <f>SUM(B11:B14)</f>
         <v/>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="9">
         <f>SUM(C11:C14)</f>
         <v/>
       </c>

--- a/la-marinka/La Marinka.xlsx
+++ b/la-marinka/La Marinka.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Synthèse" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Budget étage" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Budget RDC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Paramètres" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget Toiture" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Paramètres" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -119,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,24 +130,27 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -242,6 +246,21 @@
 </file>
 
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="M4" authorId="0" shapeId="0">
+      <text>
+        <t>Saisissez ici le montant TTC du devis : il remplace la moyenne dans « Montant retenu ».</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Claude</author>
@@ -545,10 +564,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -566,7 +585,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Niveau</t>
+          <t>Poste</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -650,66 +669,171 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL TRAVAUX TTC</t>
-        </is>
-      </c>
-      <c r="B6" s="6">
-        <f>SUM(B4:B5)</f>
-        <v/>
-      </c>
-      <c r="C6" s="6">
-        <f>SUM(C4:C5)</f>
-        <v/>
-      </c>
-      <c r="D6" s="6">
-        <f>SUM(D4:D5)</f>
-        <v/>
-      </c>
-      <c r="E6" s="6">
-        <f>SUM(E4:E5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="6">
-        <f>SUM(F4:F5)</f>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Toiture 260 m² (réfection complète)</t>
+        </is>
+      </c>
+      <c r="B6" s="4">
+        <f>'Budget Toiture'!G18</f>
+        <v/>
+      </c>
+      <c r="C6" s="4">
+        <f>'Budget Toiture'!H18</f>
+        <v/>
+      </c>
+      <c r="D6" s="4">
+        <f>'Budget Toiture'!K18</f>
+        <v/>
+      </c>
+      <c r="E6" s="4">
+        <f>'Budget Toiture'!L18</f>
+        <v/>
+      </c>
+      <c r="F6" s="4">
+        <f>'Budget Toiture'!N18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL TRAVAUX TTC — sans sarking</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>SUM(B4:B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="6">
+        <f>SUM(C4:C6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="6">
+        <f>SUM(D4:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="6">
+        <f>SUM(E4:E6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="6">
+        <f>SUM(F4:F6)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Option sarking : surcoût net (onglet Toiture)</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <f>'Budget Toiture'!G30</f>
+        <v/>
+      </c>
+      <c r="C8" s="4">
+        <f>'Budget Toiture'!H30</f>
+        <v/>
+      </c>
+      <c r="D8" s="4">
+        <f>'Budget Toiture'!K30</f>
+        <v/>
+      </c>
+      <c r="E8" s="4">
+        <f>'Budget Toiture'!L30</f>
+        <v/>
+      </c>
+      <c r="F8" s="4">
+        <f>'Budget Toiture'!N30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL TRAVAUX TTC — avec sarking</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>B7+B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="6">
+        <f>C7+C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="6">
+        <f>D7+D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="6">
+        <f>E7+E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="6">
+        <f>F7+F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Postes hors budget (Paramètres)</t>
         </is>
       </c>
-      <c r="B8" s="8">
-        <f>Paramètres!B15</f>
-        <v/>
-      </c>
-      <c r="C8" s="8">
-        <f>Paramètres!C15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Enveloppe globale (travaux + hors budget)</t>
-        </is>
-      </c>
-      <c r="B9" s="9">
-        <f>B6+B8</f>
-        <v/>
-      </c>
-      <c r="C9" s="9">
-        <f>C6+C8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Ameublement non compris. Escalier compté une seule fois (onglet étage).</t>
+      <c r="B11" s="4">
+        <f>Paramètres!B14</f>
+        <v/>
+      </c>
+      <c r="C11" s="4">
+        <f>Paramètres!C14</f>
+        <v/>
+      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Enveloppe globale sans sarking</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>B7+B11</f>
+        <v/>
+      </c>
+      <c r="C12" s="9">
+        <f>C7+C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Enveloppe globale avec sarking</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>B9+B11</f>
+        <v/>
+      </c>
+      <c r="C13" s="9">
+        <f>C9+C11</f>
+        <v/>
+      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Ameublement non compris. Escalier compté une seule fois (onglet étage). Prix TTC indicatifs, à remplacer par les devis.</t>
         </is>
       </c>
     </row>
@@ -857,7 +981,7 @@
       <c r="O5" s="12" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n"/>
+      <c r="A6" s="8" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Nouvelle trémie, reprise solivage, rebouchage ancienne trémie</t>
@@ -868,41 +992,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="14" t="n">
         <v>8000</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="15">
         <f>IF(I6="Oui",G6*J6,G6)</f>
         <v/>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="15">
         <f>IF(I6="Oui",H6*J6,H6)</f>
         <v/>
       </c>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="16">
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="15">
         <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
         <v/>
       </c>
@@ -913,7 +1037,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n"/>
+      <c r="A7" s="8" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Étude BET structure</t>
@@ -924,48 +1048,48 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <f>IF(I7="Oui",G7*J7,G7)</f>
         <v/>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="15">
         <f>IF(I7="Oui",H7*J7,H7)</f>
         <v/>
       </c>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="16">
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="15">
         <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
         <v/>
       </c>
       <c r="O7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n"/>
+      <c r="A8" s="8" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Escalier bois ¼ tournant sur mesure, posé</t>
@@ -976,41 +1100,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="14" t="n">
         <v>9000</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="15">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <f>IF(I8="Oui",G8*J8,G8)</f>
         <v/>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="15">
         <f>IF(I8="Oui",H8*J8,H8)</f>
         <v/>
       </c>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="16">
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="15">
         <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
         <v/>
       </c>
@@ -1042,7 +1166,7 @@
       <c r="O9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n"/>
+      <c r="A10" s="8" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Isolation rampants fibre de bois</t>
@@ -1053,41 +1177,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="15">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="16" t="n">
         <v>0.55</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="15">
         <f>IF(I10="Oui",G10*J10,G10)</f>
         <v/>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="15">
         <f>IF(I10="Oui",H10*J10,H10)</f>
         <v/>
       </c>
-      <c r="M10" s="18" t="n"/>
-      <c r="N10" s="16">
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="15">
         <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
         <v/>
       </c>
@@ -1098,7 +1222,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n"/>
+      <c r="A11" s="8" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Velux 78×98 posés + raccords</t>
@@ -1109,41 +1233,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="14" t="n">
         <v>1600</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <f>D11*E11</f>
         <v/>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="15">
         <f>IF(I11="Oui",G11*J11,G11)</f>
         <v/>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="15">
         <f>IF(I11="Oui",H11*J11,H11)</f>
         <v/>
       </c>
-      <c r="M11" s="18" t="n"/>
-      <c r="N11" s="16">
+      <c r="M11" s="17" t="n"/>
+      <c r="N11" s="15">
         <f>IF(N(M11)&gt;0,M11,(G11+H11)/2)</f>
         <v/>
       </c>
@@ -1154,7 +1278,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n"/>
+      <c r="A12" s="8" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Velux 55×78 posé (dégagement)</t>
@@ -1165,48 +1289,48 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="14" t="n">
         <v>800</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F12" s="14" t="n">
         <v>1300</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="15">
         <f>D12*E12</f>
         <v/>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="15">
         <f>D12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="15">
         <f>IF(I12="Oui",G12*J12,G12)</f>
         <v/>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="15">
         <f>IF(I12="Oui",H12*J12,H12)</f>
         <v/>
       </c>
-      <c r="M12" s="18" t="n"/>
-      <c r="N12" s="16">
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="15">
         <f>IF(N(M12)&gt;0,M12,(G12+H12)/2)</f>
         <v/>
       </c>
       <c r="O12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n"/>
+      <c r="A13" s="8" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Doublage murs pisé (lame d'air + isolant perspirant + placo)</t>
@@ -1217,41 +1341,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <f>D13*E13</f>
         <v/>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="15">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="15">
         <f>IF(I13="Oui",G13*J13,G13)</f>
         <v/>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="15">
         <f>IF(I13="Oui",H13*J13,H13)</f>
         <v/>
       </c>
-      <c r="M13" s="18" t="n"/>
-      <c r="N13" s="16">
+      <c r="M13" s="17" t="n"/>
+      <c r="N13" s="15">
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
@@ -1283,7 +1407,7 @@
       <c r="O14" s="12" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="n"/>
+      <c r="A15" s="8" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Cloisons placo 72/48 + laine (dont 2 en 10 cm galandage)</t>
@@ -1294,48 +1418,48 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="13" t="n">
         <v>75</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="15">
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="15">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="16" t="n">
         <v>0.45</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="15">
         <f>IF(I15="Oui",G15*J15,G15)</f>
         <v/>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="15">
         <f>IF(I15="Oui",H15*J15,H15)</f>
         <v/>
       </c>
-      <c r="M15" s="18" t="n"/>
-      <c r="N15" s="16">
+      <c r="M15" s="17" t="n"/>
+      <c r="N15" s="15">
         <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
         <v/>
       </c>
       <c r="O15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="n"/>
+      <c r="A16" s="8" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Finition plafonds / habillage sous rampant</t>
@@ -1346,41 +1470,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="15">
         <f>D16*E16</f>
         <v/>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="15">
         <f>D16*F16</f>
         <v/>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J16" s="17" t="n">
+      <c r="J16" s="16" t="n">
         <v>0.45</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="15">
         <f>IF(I16="Oui",G16*J16,G16)</f>
         <v/>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="15">
         <f>IF(I16="Oui",H16*J16,H16)</f>
         <v/>
       </c>
-      <c r="M16" s="18" t="n"/>
-      <c r="N16" s="16">
+      <c r="M16" s="17" t="n"/>
+      <c r="N16" s="15">
         <f>IF(N(M16)&gt;0,M16,(G16+H16)/2)</f>
         <v/>
       </c>
@@ -1408,7 +1532,7 @@
       <c r="O17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n"/>
+      <c r="A18" s="8" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Salle d'eau complète (douche 120×80, vasque, sèche-serviettes)</t>
@@ -1419,41 +1543,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="14" t="n">
         <v>9000</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="15">
         <f>D18*E18</f>
         <v/>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="15">
         <f>D18*F18</f>
         <v/>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="15">
         <f>IF(I18="Oui",G18*J18,G18)</f>
         <v/>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="15">
         <f>IF(I18="Oui",H18*J18,H18)</f>
         <v/>
       </c>
-      <c r="M18" s="18" t="n"/>
-      <c r="N18" s="16">
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="15">
         <f>IF(N(M18)&gt;0,M18,(G18+H18)/2)</f>
         <v/>
       </c>
@@ -1464,7 +1588,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="n"/>
+      <c r="A19" s="8" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>WC suspendu + lave-mains</t>
@@ -1475,48 +1599,48 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="14" t="n">
         <v>1500</v>
       </c>
-      <c r="F19" s="15" t="n">
+      <c r="F19" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="15">
         <f>D19*E19</f>
         <v/>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="15">
         <f>D19*F19</f>
         <v/>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="15">
         <f>IF(I19="Oui",G19*J19,G19)</f>
         <v/>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="15">
         <f>IF(I19="Oui",H19*J19,H19)</f>
         <v/>
       </c>
-      <c r="M19" s="18" t="n"/>
-      <c r="N19" s="16">
+      <c r="M19" s="17" t="n"/>
+      <c r="N19" s="15">
         <f>IF(N(M19)&gt;0,M19,(G19+H19)/2)</f>
         <v/>
       </c>
       <c r="O19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="n"/>
+      <c r="A20" s="8" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Réseaux alimentation / évacuations / chutes</t>
@@ -1527,41 +1651,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="F20" s="15" t="n">
+      <c r="F20" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="15">
         <f>D20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="15">
         <f>D20*F20</f>
         <v/>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="15">
         <f>IF(I20="Oui",G20*J20,G20)</f>
         <v/>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="15">
         <f>IF(I20="Oui",H20*J20,H20)</f>
         <v/>
       </c>
-      <c r="M20" s="18" t="n"/>
-      <c r="N20" s="16">
+      <c r="M20" s="17" t="n"/>
+      <c r="N20" s="15">
         <f>IF(N(M20)&gt;0,M20,(G20+H20)/2)</f>
         <v/>
       </c>
@@ -1572,7 +1696,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="n"/>
+      <c r="A21" s="8" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Production eau chaude (ballon 200-300 L)</t>
@@ -1583,41 +1707,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="15">
         <f>D21*E21</f>
         <v/>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="15">
         <f>D21*F21</f>
         <v/>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J21" s="17" t="n">
+      <c r="J21" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="15">
         <f>IF(I21="Oui",G21*J21,G21)</f>
         <v/>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="15">
         <f>IF(I21="Oui",H21*J21,H21)</f>
         <v/>
       </c>
-      <c r="M21" s="18" t="n"/>
-      <c r="N21" s="16">
+      <c r="M21" s="17" t="n"/>
+      <c r="N21" s="15">
         <f>IF(N(M21)&gt;0,M21,(G21+H21)/2)</f>
         <v/>
       </c>
@@ -1649,7 +1773,7 @@
       <c r="O22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="n"/>
+      <c r="A23" s="8" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Électricité neuve NF C 15-100</t>
@@ -1660,48 +1784,48 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="13" t="n">
         <v>77</v>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="E23" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="F23" s="15" t="n">
+      <c r="F23" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="15">
         <f>D23*E23</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="15">
         <f>D23*F23</f>
         <v/>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J23" s="17" t="n">
+      <c r="J23" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="15">
         <f>IF(I23="Oui",G23*J23,G23)</f>
         <v/>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="15">
         <f>IF(I23="Oui",H23*J23,H23)</f>
         <v/>
       </c>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="16">
+      <c r="M23" s="17" t="n"/>
+      <c r="N23" s="15">
         <f>IF(N(M23)&gt;0,M23,(G23+H23)/2)</f>
         <v/>
       </c>
       <c r="O23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="n"/>
+      <c r="A24" s="8" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
           <t>VMC hygro B (4 SdE + WC)</t>
@@ -1712,41 +1836,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="15" t="n">
+      <c r="E24" s="14" t="n">
         <v>1500</v>
       </c>
-      <c r="F24" s="15" t="n">
+      <c r="F24" s="14" t="n">
         <v>3000</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="15">
         <f>D24*E24</f>
         <v/>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="15">
         <f>D24*F24</f>
         <v/>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J24" s="17" t="n">
+      <c r="J24" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="15">
         <f>IF(I24="Oui",G24*J24,G24)</f>
         <v/>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="15">
         <f>IF(I24="Oui",H24*J24,H24)</f>
         <v/>
       </c>
-      <c r="M24" s="18" t="n"/>
-      <c r="N24" s="16">
+      <c r="M24" s="17" t="n"/>
+      <c r="N24" s="15">
         <f>IF(N(M24)&gt;0,M24,(G24+H24)/2)</f>
         <v/>
       </c>
@@ -1757,7 +1881,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="n"/>
+      <c r="A25" s="8" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Chauffage (radiateurs inertie ou PAC air/air)</t>
@@ -1768,41 +1892,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="15" t="n">
+      <c r="E25" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="F25" s="15" t="n">
+      <c r="F25" s="14" t="n">
         <v>12000</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="15">
         <f>D25*E25</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="15">
         <f>D25*F25</f>
         <v/>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J25" s="17" t="n">
+      <c r="J25" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="15">
         <f>IF(I25="Oui",G25*J25,G25)</f>
         <v/>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="15">
         <f>IF(I25="Oui",H25*J25,H25)</f>
         <v/>
       </c>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="16">
+      <c r="M25" s="17" t="n"/>
+      <c r="N25" s="15">
         <f>IF(N(M25)&gt;0,M25,(G25+H25)/2)</f>
         <v/>
       </c>
@@ -1830,7 +1954,7 @@
       <c r="O26" s="12" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="n"/>
+      <c r="A27" s="8" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Portes battantes posées</t>
@@ -1841,41 +1965,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E27" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="F27" s="15" t="n">
+      <c r="F27" s="14" t="n">
         <v>550</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="15">
         <f>D27*E27</f>
         <v/>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="15">
         <f>D27*F27</f>
         <v/>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="I27" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J27" s="17" t="n">
+      <c r="J27" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="15">
         <f>IF(I27="Oui",G27*J27,G27)</f>
         <v/>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="15">
         <f>IF(I27="Oui",H27*J27,H27)</f>
         <v/>
       </c>
-      <c r="M27" s="18" t="n"/>
-      <c r="N27" s="16">
+      <c r="M27" s="17" t="n"/>
+      <c r="N27" s="15">
         <f>IF(N(M27)&gt;0,M27,(G27+H27)/2)</f>
         <v/>
       </c>
@@ -1886,7 +2010,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="n"/>
+      <c r="A28" s="8" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Portes à galandage (SdE 1-2) avec caisson</t>
@@ -1897,48 +2021,48 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="14" t="n">
         <v>700</v>
       </c>
-      <c r="F28" s="15" t="n">
+      <c r="F28" s="14" t="n">
         <v>1200</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="15">
         <f>D28*E28</f>
         <v/>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="15">
         <f>D28*F28</f>
         <v/>
       </c>
-      <c r="I28" s="14" t="inlineStr">
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J28" s="17" t="n">
+      <c r="J28" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="15">
         <f>IF(I28="Oui",G28*J28,G28)</f>
         <v/>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="15">
         <f>IF(I28="Oui",H28*J28,H28)</f>
         <v/>
       </c>
-      <c r="M28" s="18" t="n"/>
-      <c r="N28" s="16">
+      <c r="M28" s="17" t="n"/>
+      <c r="N28" s="15">
         <f>IF(N(M28)&gt;0,M28,(G28+H28)/2)</f>
         <v/>
       </c>
       <c r="O28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n"/>
+      <c r="A29" s="8" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Façades rangements sous rampant</t>
@@ -1949,41 +2073,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="E29" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="F29" s="15" t="n">
+      <c r="F29" s="14" t="n">
         <v>700</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="15">
         <f>D29*E29</f>
         <v/>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="15">
         <f>D29*F29</f>
         <v/>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J29" s="17" t="n">
+      <c r="J29" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="15">
         <f>IF(I29="Oui",G29*J29,G29)</f>
         <v/>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="15">
         <f>IF(I29="Oui",H29*J29,H29)</f>
         <v/>
       </c>
-      <c r="M29" s="18" t="n"/>
-      <c r="N29" s="16">
+      <c r="M29" s="17" t="n"/>
+      <c r="N29" s="15">
         <f>IF(N(M29)&gt;0,M29,(G29+H29)/2)</f>
         <v/>
       </c>
@@ -2011,7 +2135,7 @@
       <c r="O30" s="12" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="n"/>
+      <c r="A31" s="8" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Parquet chambres + dégagement</t>
@@ -2022,48 +2146,48 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="13" t="n">
         <v>51</v>
       </c>
-      <c r="E31" s="15" t="n">
+      <c r="E31" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="F31" s="15" t="n">
+      <c r="F31" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="15">
         <f>D31*E31</f>
         <v/>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="15">
         <f>D31*F31</f>
         <v/>
       </c>
-      <c r="I31" s="14" t="inlineStr">
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J31" s="17" t="n">
+      <c r="J31" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="15">
         <f>IF(I31="Oui",G31*J31,G31)</f>
         <v/>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="15">
         <f>IF(I31="Oui",H31*J31,H31)</f>
         <v/>
       </c>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="16">
+      <c r="M31" s="17" t="n"/>
+      <c r="N31" s="15">
         <f>IF(N(M31)&gt;0,M31,(G31+H31)/2)</f>
         <v/>
       </c>
       <c r="O31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="n"/>
+      <c r="A32" s="8" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Carrelage sols SdE + WC</t>
@@ -2074,48 +2198,48 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D32" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="E32" s="15" t="n">
+      <c r="E32" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="F32" s="15" t="n">
+      <c r="F32" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="15">
         <f>D32*E32</f>
         <v/>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="15">
         <f>D32*F32</f>
         <v/>
       </c>
-      <c r="I32" s="14" t="inlineStr">
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J32" s="17" t="n">
+      <c r="J32" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="15">
         <f>IF(I32="Oui",G32*J32,G32)</f>
         <v/>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="15">
         <f>IF(I32="Oui",H32*J32,H32)</f>
         <v/>
       </c>
-      <c r="M32" s="18" t="n"/>
-      <c r="N32" s="16">
+      <c r="M32" s="17" t="n"/>
+      <c r="N32" s="15">
         <f>IF(N(M32)&gt;0,M32,(G32+H32)/2)</f>
         <v/>
       </c>
       <c r="O32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="n"/>
+      <c r="A33" s="8" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Faïence murale SdE</t>
@@ -2126,48 +2250,48 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="E33" s="15" t="n">
+      <c r="E33" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="F33" s="15" t="n">
+      <c r="F33" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="15">
         <f>D33*E33</f>
         <v/>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="15">
         <f>D33*F33</f>
         <v/>
       </c>
-      <c r="I33" s="14" t="inlineStr">
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J33" s="17" t="n">
+      <c r="J33" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="15">
         <f>IF(I33="Oui",G33*J33,G33)</f>
         <v/>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="15">
         <f>IF(I33="Oui",H33*J33,H33)</f>
         <v/>
       </c>
-      <c r="M33" s="18" t="n"/>
-      <c r="N33" s="16">
+      <c r="M33" s="17" t="n"/>
+      <c r="N33" s="15">
         <f>IF(N(M33)&gt;0,M33,(G33+H33)/2)</f>
         <v/>
       </c>
       <c r="O33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="n"/>
+      <c r="A34" s="8" t="n"/>
       <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Peinture murs + plafonds</t>
@@ -2178,186 +2302,186 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="13" t="n">
         <v>300</v>
       </c>
-      <c r="E34" s="15" t="n">
+      <c r="E34" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="F34" s="15" t="n">
+      <c r="F34" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="15">
         <f>D34*E34</f>
         <v/>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="15">
         <f>D34*F34</f>
         <v/>
       </c>
-      <c r="I34" s="14" t="inlineStr">
+      <c r="I34" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J34" s="17" t="n">
+      <c r="J34" s="16" t="n">
         <v>0.25</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="15">
         <f>IF(I34="Oui",G34*J34,G34)</f>
         <v/>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="15">
         <f>IF(I34="Oui",H34*J34,H34)</f>
         <v/>
       </c>
-      <c r="M34" s="18" t="n"/>
-      <c r="N34" s="16">
+      <c r="M34" s="17" t="n"/>
+      <c r="N34" s="15">
         <f>IF(N(M34)&gt;0,M34,(G34+H34)/2)</f>
         <v/>
       </c>
       <c r="O34" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="19">
         <f>SUM(G5:G34)</f>
         <v/>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="19">
         <f>SUM(H5:H34)</f>
         <v/>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="19">
         <f>SUM(K5:K34)</f>
         <v/>
       </c>
-      <c r="L36" s="9">
+      <c r="L36" s="19">
         <f>SUM(L5:L34)</f>
         <v/>
       </c>
-      <c r="N36" s="9">
+      <c r="N36" s="19">
         <f>SUM(N5:N34)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>Imprévus</t>
         </is>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="21">
         <f>G36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="21">
         <f>H36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="K37" s="8">
+      <c r="K37" s="21">
         <f>K36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="21">
         <f>L36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="N37" s="8">
+      <c r="N37" s="21">
         <f>N36*Paramètres!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="19" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre</t>
         </is>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="21">
         <f>G36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="21">
         <f>H36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="K38" s="8">
+      <c r="K38" s="21">
         <f>K36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="L38" s="8">
+      <c r="L38" s="21">
         <f>L36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="N38" s="8">
+      <c r="N38" s="21">
         <f>N36*Paramètres!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n"/>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="A39" s="22" t="n"/>
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>TOTAL ÉTAGE TTC</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="22">
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="24">
         <f>G36+G37+G38</f>
         <v/>
       </c>
-      <c r="H39" s="22">
+      <c r="H39" s="24">
         <f>H36+H37+H38</f>
         <v/>
       </c>
-      <c r="I39" s="20" t="n"/>
-      <c r="J39" s="20" t="n"/>
-      <c r="K39" s="22">
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="22" t="n"/>
+      <c r="K39" s="24">
         <f>K36+K37+K38</f>
         <v/>
       </c>
-      <c r="L39" s="22">
+      <c r="L39" s="24">
         <f>L36+L37+L38</f>
         <v/>
       </c>
-      <c r="M39" s="20" t="n"/>
-      <c r="N39" s="22">
+      <c r="M39" s="22" t="n"/>
+      <c r="N39" s="24">
         <f>N36+N37+N38</f>
         <v/>
       </c>
-      <c r="O39" s="20" t="n"/>
+      <c r="O39" s="22" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="19" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>Soit par m² (77 m²)</t>
         </is>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="25">
         <f>G39/77</f>
         <v/>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="25">
         <f>H39/77</f>
         <v/>
       </c>
-      <c r="K40" s="23">
+      <c r="K40" s="25">
         <f>K39/77</f>
         <v/>
       </c>
-      <c r="L40" s="23">
+      <c r="L40" s="25">
         <f>L39/77</f>
         <v/>
       </c>
-      <c r="N40" s="23">
+      <c r="N40" s="25">
         <f>N39/77</f>
         <v/>
       </c>
@@ -2533,7 +2657,7 @@
       <c r="O5" s="12" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n"/>
+      <c r="A6" s="8" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Ouverture 4 m dans le pisé : étaiement, linteau béton ou acier, reprises</t>
@@ -2544,41 +2668,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="14" t="n">
         <v>6000</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="15">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="15">
         <f>IF(I6="Oui",G6*J6,G6)</f>
         <v/>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="15">
         <f>IF(I6="Oui",H6*J6,H6)</f>
         <v/>
       </c>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="16">
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="15">
         <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
         <v/>
       </c>
@@ -2589,7 +2713,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n"/>
+      <c r="A7" s="8" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Étude BET structure (baie 4 m)</t>
@@ -2600,41 +2724,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>1000</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="14" t="n">
         <v>2500</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="15">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="15">
         <f>IF(I7="Oui",G7*J7,G7)</f>
         <v/>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="15">
         <f>IF(I7="Oui",H7*J7,H7)</f>
         <v/>
       </c>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="16">
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="15">
         <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
         <v/>
       </c>
@@ -2645,7 +2769,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n"/>
+      <c r="A8" s="8" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Sol : décaissement, hérisson ventilé, dalle isolée (chaux ou béton)</t>
@@ -2656,41 +2780,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="14" t="n">
         <v>180</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="15">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="16" t="n">
         <v>0.45</v>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="15">
         <f>IF(I8="Oui",G8*J8,G8)</f>
         <v/>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="15">
         <f>IF(I8="Oui",H8*J8,H8)</f>
         <v/>
       </c>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="16">
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="15">
         <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
         <v/>
       </c>
@@ -2722,7 +2846,7 @@
       <c r="O9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n"/>
+      <c r="A10" s="8" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Baie vitrée 4,00 m à galandage, 2 vantaux, posée</t>
@@ -2733,41 +2857,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="14" t="n">
         <v>12000</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="14" t="n">
         <v>25000</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="15">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="16" t="n">
         <v>0.7</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="15">
         <f>IF(I10="Oui",G10*J10,G10)</f>
         <v/>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="15">
         <f>IF(I10="Oui",H10*J10,H10)</f>
         <v/>
       </c>
-      <c r="M10" s="18" t="n"/>
-      <c r="N10" s="16">
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="15">
         <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
         <v/>
       </c>
@@ -2778,7 +2902,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n"/>
+      <c r="A11" s="8" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Seuil, bavette, raccords d'étanchéité baie</t>
@@ -2789,41 +2913,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="14" t="n">
         <v>800</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="14" t="n">
         <v>2000</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="15">
         <f>D11*E11</f>
         <v/>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="15">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="15">
         <f>IF(I11="Oui",G11*J11,G11)</f>
         <v/>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="15">
         <f>IF(I11="Oui",H11*J11,H11)</f>
         <v/>
       </c>
-      <c r="M11" s="18" t="n"/>
-      <c r="N11" s="16">
+      <c r="M11" s="17" t="n"/>
+      <c r="N11" s="15">
         <f>IF(N(M11)&gt;0,M11,(G11+H11)/2)</f>
         <v/>
       </c>
@@ -2851,7 +2975,7 @@
       <c r="O12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n"/>
+      <c r="A13" s="8" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Doublage murs pisé (lame d'air + isolant perspirant + placo)</t>
@@ -2862,41 +2986,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="13" t="n">
         <v>79</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="14" t="n">
         <v>130</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="15">
         <f>D13*E13</f>
         <v/>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="15">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="15">
         <f>IF(I13="Oui",G13*J13,G13)</f>
         <v/>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="15">
         <f>IF(I13="Oui",H13*J13,H13)</f>
         <v/>
       </c>
-      <c r="M13" s="18" t="n"/>
-      <c r="N13" s="16">
+      <c r="M13" s="17" t="n"/>
+      <c r="N13" s="15">
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
@@ -2907,7 +3031,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="n"/>
+      <c r="A14" s="8" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Doublage épaissi au droit des caissons galandage</t>
@@ -2918,41 +3042,41 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <f>D14*E14</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <f>D14*F14</f>
         <v/>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="15">
         <f>IF(I14="Oui",G14*J14,G14)</f>
         <v/>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="15">
         <f>IF(I14="Oui",H14*J14,H14)</f>
         <v/>
       </c>
-      <c r="M14" s="18" t="n"/>
-      <c r="N14" s="16">
+      <c r="M14" s="17" t="n"/>
+      <c r="N14" s="15">
         <f>IF(N(M14)&gt;0,M14,(G14+H14)/2)</f>
         <v/>
       </c>
@@ -2963,7 +3087,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="n"/>
+      <c r="A15" s="8" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Plafond sous plancher étage + isolation phonique</t>
@@ -2974,41 +3098,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="15">
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="15">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="16" t="n">
         <v>0.45</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="15">
         <f>IF(I15="Oui",G15*J15,G15)</f>
         <v/>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="15">
         <f>IF(I15="Oui",H15*J15,H15)</f>
         <v/>
       </c>
-      <c r="M15" s="18" t="n"/>
-      <c r="N15" s="16">
+      <c r="M15" s="17" t="n"/>
+      <c r="N15" s="15">
         <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
         <v/>
       </c>
@@ -3040,7 +3164,7 @@
       <c r="O16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="n"/>
+      <c r="A17" s="8" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Électricité séjour (prises, réseau, mur TV, éclairages table et billard)</t>
@@ -3051,48 +3175,48 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="15">
         <f>D17*E17</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="15">
         <f>D17*F17</f>
         <v/>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="15">
         <f>IF(I17="Oui",G17*J17,G17)</f>
         <v/>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="15">
         <f>IF(I17="Oui",H17*J17,H17)</f>
         <v/>
       </c>
-      <c r="M17" s="18" t="n"/>
-      <c r="N17" s="16">
+      <c r="M17" s="17" t="n"/>
+      <c r="N17" s="15">
         <f>IF(N(M17)&gt;0,M17,(G17+H17)/2)</f>
         <v/>
       </c>
       <c r="O17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n"/>
+      <c r="A18" s="8" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Chauffage (poêle à bois ou PAC air/air)</t>
@@ -3103,41 +3227,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="14" t="n">
         <v>12000</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="15">
         <f>D18*E18</f>
         <v/>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="15">
         <f>D18*F18</f>
         <v/>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="15">
         <f>IF(I18="Oui",G18*J18,G18)</f>
         <v/>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="15">
         <f>IF(I18="Oui",H18*J18,H18)</f>
         <v/>
       </c>
-      <c r="M18" s="18" t="n"/>
-      <c r="N18" s="16">
+      <c r="M18" s="17" t="n"/>
+      <c r="N18" s="15">
         <f>IF(N(M18)&gt;0,M18,(G18+H18)/2)</f>
         <v/>
       </c>
@@ -3169,7 +3293,7 @@
       <c r="O19" s="12" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="n"/>
+      <c r="A20" s="8" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Revêtement de sol (parquet massif ou terre cuite)</t>
@@ -3180,48 +3304,48 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="13" t="n">
         <v>72</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="15" t="n">
+      <c r="F20" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="15">
         <f>D20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="15">
         <f>D20*F20</f>
         <v/>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="15">
         <f>IF(I20="Oui",G20*J20,G20)</f>
         <v/>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="15">
         <f>IF(I20="Oui",H20*J20,H20)</f>
         <v/>
       </c>
-      <c r="M20" s="18" t="n"/>
-      <c r="N20" s="16">
+      <c r="M20" s="17" t="n"/>
+      <c r="N20" s="15">
         <f>IF(N(M20)&gt;0,M20,(G20+H20)/2)</f>
         <v/>
       </c>
       <c r="O20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="n"/>
+      <c r="A21" s="8" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Peinture / enduits murs + plafond</t>
@@ -3232,41 +3356,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="15">
         <f>D21*E21</f>
         <v/>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="15">
         <f>D21*F21</f>
         <v/>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J21" s="17" t="n">
+      <c r="J21" s="16" t="n">
         <v>0.25</v>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="15">
         <f>IF(I21="Oui",G21*J21,G21)</f>
         <v/>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="15">
         <f>IF(I21="Oui",H21*J21,H21)</f>
         <v/>
       </c>
-      <c r="M21" s="18" t="n"/>
-      <c r="N21" s="16">
+      <c r="M21" s="17" t="n"/>
+      <c r="N21" s="15">
         <f>IF(N(M21)&gt;0,M21,(G21+H21)/2)</f>
         <v/>
       </c>
@@ -3277,7 +3401,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="n"/>
+      <c r="A22" s="8" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Plinthes, finitions, habillage escalier</t>
@@ -3288,41 +3412,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="15" t="n">
+      <c r="E22" s="14" t="n">
         <v>600</v>
       </c>
-      <c r="F22" s="15" t="n">
+      <c r="F22" s="14" t="n">
         <v>1500</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="15">
         <f>D22*E22</f>
         <v/>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="15">
         <f>D22*F22</f>
         <v/>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="J22" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="15">
         <f>IF(I22="Oui",G22*J22,G22)</f>
         <v/>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="15">
         <f>IF(I22="Oui",H22*J22,H22)</f>
         <v/>
       </c>
-      <c r="M22" s="18" t="n"/>
-      <c r="N22" s="16">
+      <c r="M22" s="17" t="n"/>
+      <c r="N22" s="15">
         <f>IF(N(M22)&gt;0,M22,(G22+H22)/2)</f>
         <v/>
       </c>
@@ -3333,145 +3457,145 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="19">
         <f>SUM(G5:G22)</f>
         <v/>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="19">
         <f>SUM(H5:H22)</f>
         <v/>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="19">
         <f>SUM(K5:K22)</f>
         <v/>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="19">
         <f>SUM(L5:L22)</f>
         <v/>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="19">
         <f>SUM(N5:N22)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Imprévus</t>
         </is>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="21">
         <f>G24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="21">
         <f>H24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="21">
         <f>K24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="21">
         <f>L24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="N25" s="8">
+      <c r="N25" s="21">
         <f>N24*Paramètres!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre</t>
         </is>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="21">
         <f>G24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="21">
         <f>H24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="21">
         <f>K24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="21">
         <f>L24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="N26" s="8">
+      <c r="N26" s="21">
         <f>N24*Paramètres!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="n"/>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>TOTAL RDC TTC</t>
         </is>
       </c>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="22">
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="24">
         <f>G24+G25+G26</f>
         <v/>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="24">
         <f>H24+H25+H26</f>
         <v/>
       </c>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="22">
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="24">
         <f>K24+K25+K26</f>
         <v/>
       </c>
-      <c r="L27" s="22">
+      <c r="L27" s="24">
         <f>L24+L25+L26</f>
         <v/>
       </c>
-      <c r="M27" s="20" t="n"/>
-      <c r="N27" s="22">
+      <c r="M27" s="22" t="n"/>
+      <c r="N27" s="24">
         <f>N24+N25+N26</f>
         <v/>
       </c>
-      <c r="O27" s="20" t="n"/>
+      <c r="O27" s="22" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>Soit par m² (77 m²)</t>
         </is>
       </c>
-      <c r="G28" s="23">
+      <c r="G28" s="25">
         <f>G27/77</f>
         <v/>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="25">
         <f>H27/77</f>
         <v/>
       </c>
-      <c r="K28" s="23">
+      <c r="K28" s="25">
         <f>K27/77</f>
         <v/>
       </c>
-      <c r="L28" s="23">
+      <c r="L28" s="25">
         <f>L27/77</f>
         <v/>
       </c>
-      <c r="N28" s="23">
+      <c r="N28" s="25">
         <f>N27/77</f>
         <v/>
       </c>
@@ -3514,7 +3638,956 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>La Marinka — Budget estimatif réfection de toiture (260 m² de tuiles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Prix TTC indicatifs (marché France 2025-2026, entreprise), travaux seuls sans ameublement. Cellules en BLEU = à ajuster ; colonne JAUNE « Devis reçu » = à remplir au fil des devis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Unité</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Qté</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>PU min €</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>PU max €</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Total min €</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Total max €</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Faisable soi-même</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Part matériaux</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Auto min €</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Auto max €</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Devis reçu €</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Montant retenu €</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Couverture (260 m²)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="12" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="12" t="n"/>
+      <c r="N5" s="12" t="n"/>
+      <c r="O5" s="12" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Dépose de la couverture existante + évacuation</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="15">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="15">
+        <f>D6*F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K6" s="15">
+        <f>IF(I6="Oui",G6*J6,G6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="15">
+        <f>IF(I6="Oui",H6*J6,H6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="15">
+        <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
+        <v/>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Écran sous-toiture HPV + contre-liteaux + liteaux neufs</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G7" s="15">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="15">
+        <f>D7*F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="15">
+        <f>IF(I7="Oui",G7*J7,G7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="15">
+        <f>IF(I7="Oui",H7*J7,H7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="15">
+        <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
+        <v/>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Tuiles neuves terre cuite, fourniture + pose</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="G8" s="15">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="15">
+        <f>D8*F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K8" s="15">
+        <f>IF(I8="Oui",G8*J8,G8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="15">
+        <f>IF(I8="Oui",H8*J8,H8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="15">
+        <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
+        <v/>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Tuiles canal / anciennes : prendre le haut de fourchette ou plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Faîtage, rives, arêtiers (scellés ou à sec)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="G9" s="15">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="H9" s="15">
+        <f>D9*F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="15">
+        <f>IF(I9="Oui",G9*J9,G9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="15">
+        <f>IF(I9="Oui",H9*J9,H9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="15">
+        <f>IF(N(M9)&gt;0,M9,(G9+H9)/2)</f>
+        <v/>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>Linéaire à métrer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Zinguerie : gouttières, descentes, noues</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10" s="15">
+        <f>D10*E10</f>
+        <v/>
+      </c>
+      <c r="H10" s="15">
+        <f>D10*F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="15">
+        <f>IF(I10="Oui",G10*J10,G10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="15">
+        <f>IF(I10="Oui",H10*J10,H10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="17" t="n"/>
+      <c r="N10" s="15">
+        <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
+        <v/>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Zinc ou alu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Charpente / sécurité</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="12" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Reprise ponctuelle de charpente + traitement insectes / champignons</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G12" s="15">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="H12" s="15">
+        <f>D12*F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K12" s="15">
+        <f>IF(I12="Oui",G12*J12,G12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="15">
+        <f>IF(I12="Oui",H12*J12,H12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="17" t="n"/>
+      <c r="N12" s="15">
+        <f>IF(N(M12)&gt;0,M12,(G12+H12)/2)</f>
+        <v/>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Selon diagnostic ; reprise lourde non comprise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Échafaudage, protections, sécurité</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G13" s="15">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="15">
+        <f>D13*F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K13" s="15">
+        <f>IF(I13="Oui",G13*J13,G13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="15">
+        <f>IF(I13="Oui",H13*J13,H13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="17" t="n"/>
+      <c r="N13" s="15">
+        <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
+        <v/>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>Parfois inclus dans le devis du couvreur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Sous-total travaux</t>
+        </is>
+      </c>
+      <c r="G15" s="19">
+        <f>SUM(G5:G13)</f>
+        <v/>
+      </c>
+      <c r="H15" s="19">
+        <f>SUM(H5:H13)</f>
+        <v/>
+      </c>
+      <c r="K15" s="19">
+        <f>SUM(K5:K13)</f>
+        <v/>
+      </c>
+      <c r="L15" s="19">
+        <f>SUM(L5:L13)</f>
+        <v/>
+      </c>
+      <c r="N15" s="19">
+        <f>SUM(N5:N13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Imprévus</t>
+        </is>
+      </c>
+      <c r="G16" s="21">
+        <f>G15*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="H16" s="21">
+        <f>H15*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="K16" s="21">
+        <f>K15*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="L16" s="21">
+        <f>L15*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="N16" s="21">
+        <f>N15*Paramètres!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Maîtrise d'œuvre</t>
+        </is>
+      </c>
+      <c r="G17" s="21">
+        <f>G15*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="H17" s="21">
+        <f>H15*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="K17" s="21">
+        <f>K15*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="L17" s="21">
+        <f>L15*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="N17" s="21">
+        <f>N15*Paramètres!$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>TOTAL TOITURE TTC (sans sarking)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="24">
+        <f>G15+G16+G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="24">
+        <f>H15+H16+H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="24">
+        <f>K15+K16+K17</f>
+        <v/>
+      </c>
+      <c r="L18" s="24">
+        <f>L15+L16+L17</f>
+        <v/>
+      </c>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="24">
+        <f>N15+N16+N17</f>
+        <v/>
+      </c>
+      <c r="O18" s="22" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Soit par m² (260 m²)</t>
+        </is>
+      </c>
+      <c r="G19" s="25">
+        <f>G18/260</f>
+        <v/>
+      </c>
+      <c r="H19" s="25">
+        <f>H18/260</f>
+        <v/>
+      </c>
+      <c r="K19" s="25">
+        <f>K18/260</f>
+        <v/>
+      </c>
+      <c r="L19" s="25">
+        <f>L18/260</f>
+        <v/>
+      </c>
+      <c r="N19" s="25">
+        <f>N18/260</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Lecture : « Total min / max » = fourchette entreprise. « Auto min / max » = coût si vous réalisez vous-même les postes marqués « Oui »</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>(vous ne payez alors que la part matériaux). « Montant retenu » = devis reçu s'il est saisi, sinon la moyenne min/max.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Source : estimations indicatives de prix moyens du marché (ordre de grandeur), à remplacer par les devis d'artisans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>OPTION SARKING</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Isolation posée par l'extérieur pendant la réfection (remplace l'isolation intérieure des rampants de l'étage)</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="27" t="n"/>
+      <c r="I25" s="27" t="n"/>
+      <c r="J25" s="27" t="n"/>
+      <c r="K25" s="27" t="n"/>
+      <c r="L25" s="27" t="n"/>
+      <c r="M25" s="27" t="n"/>
+      <c r="N25" s="27" t="n"/>
+      <c r="O25" s="27" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Isolation sarking fibre de bois 160-200 mm + pare-pluie (sur chevrons)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="G26" s="15">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+      <c r="H26" s="15">
+        <f>D26*F26</f>
+        <v/>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K26" s="15">
+        <f>IF(I26="Oui",G26*J26,G26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="15">
+        <f>IF(I26="Oui",H26*J26,H26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="17" t="n"/>
+      <c r="N26" s="15">
+        <f>IF(N(M26)&gt;0,M26,(G26+H26)/2)</f>
+        <v/>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>Charpente apparente à l'étage, R ≈ 4 à 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Rehausse des rives et adaptation zinguerie à l'épaisseur d'isolant</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G27" s="15">
+        <f>D27*E27</f>
+        <v/>
+      </c>
+      <c r="H27" s="15">
+        <f>D27*F27</f>
+        <v/>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K27" s="15">
+        <f>IF(I27="Oui",G27*J27,G27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="15">
+        <f>IF(I27="Oui",H27*J27,H27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="17" t="n"/>
+      <c r="N27" s="15">
+        <f>IF(N(M27)&gt;0,M27,(G27+H27)/2)</f>
+        <v/>
+      </c>
+      <c r="O27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Sous-total option sarking</t>
+        </is>
+      </c>
+      <c r="G28" s="19">
+        <f>SUM(G26:G27)</f>
+        <v/>
+      </c>
+      <c r="H28" s="19">
+        <f>SUM(H26:H27)</f>
+        <v/>
+      </c>
+      <c r="K28" s="19">
+        <f>SUM(K26:K27)</f>
+        <v/>
+      </c>
+      <c r="L28" s="19">
+        <f>SUM(L26:L27)</f>
+        <v/>
+      </c>
+      <c r="N28" s="19">
+        <f>SUM(N26:N27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Économie : isolation intérieure des rampants supprimée (onglet étage)</t>
+        </is>
+      </c>
+      <c r="G29" s="21">
+        <f>-'Budget étage'!G10</f>
+        <v/>
+      </c>
+      <c r="H29" s="21">
+        <f>-'Budget étage'!H10</f>
+        <v/>
+      </c>
+      <c r="K29" s="21">
+        <f>-'Budget étage'!K10</f>
+        <v/>
+      </c>
+      <c r="L29" s="21">
+        <f>-'Budget étage'!L10</f>
+        <v/>
+      </c>
+      <c r="N29" s="21">
+        <f>-'Budget étage'!N10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>SURCOÛT NET OPTION SARKING TTC (imprévus + MOE inclus)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="24">
+        <f>(G28+G29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="H30" s="24">
+        <f>(H28+H29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="24">
+        <f>(K28+K29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="L30" s="24">
+        <f>(L28+L29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="M30" s="22" t="n"/>
+      <c r="N30" s="24">
+        <f>(N28+N29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="O30" s="22" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Le sarking garde la charpente apparente, libère quelques cm de hauteur sous rampant et facilite la pose étanche des Velux.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="I6 I7 I8 I9 I10 I12 I13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Oui,Non"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3531,172 +4604,154 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Paramètre</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Imprévus (% des travaux)</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Usuel en rénovation de bâti ancien : 10 à 15 %.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre / architecte (% des travaux)</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>0 % si vous pilotez vous-même ; 8 à 12 % avec un maître d'œuvre.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>TVA : prix affichés TTC à 20 % (création de surface habitable dans une grange : taux réduit en principe non applicable).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Postes HORS budget étage (à chiffrer séparément)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Min €</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Max €</t>
         </is>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>Couverture / charpente (si à reprendre)</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="n">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Raccordements eau / électricité / assainissement individuel</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C11" s="30" t="n">
         <v>15000</v>
       </c>
-      <c r="C11" s="27" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>À diagnostiquer en priorité.</t>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Selon raccordement existant de la grange.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Raccordements eau / électricité / assainissement individuel</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C12" s="27" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>Selon raccordement existant de la grange.</t>
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Renfort du plancher / chape</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>Si le plancher de l'étage est insuffisant.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>Renfort du plancher / chape</t>
-        </is>
-      </c>
-      <c r="B13" s="27" t="n">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>Taxe d'aménagement + dossier changement de destination</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C13" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="C13" s="27" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>Si le plancher de l'étage est insuffisant.</t>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Selon taux communal et départemental.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>Taxe d'aménagement + dossier changement de destination</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C14" s="27" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>Selon taux communal et départemental.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Total hors budget</t>
         </is>
       </c>
-      <c r="B15" s="9">
-        <f>SUM(B11:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="9">
-        <f>SUM(C11:C14)</f>
+      <c r="B14" s="19">
+        <f>SUM(B11:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="19">
+        <f>SUM(C11:C13)</f>
         <v/>
       </c>
     </row>

--- a/la-marinka/La Marinka.xlsx
+++ b/la-marinka/La Marinka.xlsx
@@ -671,27 +671,27 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Toiture 260 m² (réfection complète)</t>
+          <t>Toiture 260 m² + ravalement des façades</t>
         </is>
       </c>
       <c r="B6" s="4">
-        <f>'Budget Toiture'!G18</f>
+        <f>'Budget Toiture'!G21</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>'Budget Toiture'!H18</f>
+        <f>'Budget Toiture'!H21</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>'Budget Toiture'!K18</f>
+        <f>'Budget Toiture'!K21</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>'Budget Toiture'!L18</f>
+        <f>'Budget Toiture'!L21</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>'Budget Toiture'!N18</f>
+        <f>'Budget Toiture'!N21</f>
         <v/>
       </c>
     </row>
@@ -729,23 +729,23 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'Budget Toiture'!G30</f>
+        <f>'Budget Toiture'!G33</f>
         <v/>
       </c>
       <c r="C8" s="4">
-        <f>'Budget Toiture'!H30</f>
+        <f>'Budget Toiture'!H33</f>
         <v/>
       </c>
       <c r="D8" s="4">
-        <f>'Budget Toiture'!K30</f>
+        <f>'Budget Toiture'!K33</f>
         <v/>
       </c>
       <c r="E8" s="4">
-        <f>'Budget Toiture'!L30</f>
+        <f>'Budget Toiture'!L33</f>
         <v/>
       </c>
       <c r="F8" s="4">
-        <f>'Budget Toiture'!N30</f>
+        <f>'Budget Toiture'!N33</f>
         <v/>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3661,7 +3661,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>La Marinka — Budget estimatif réfection de toiture (260 m² de tuiles)</t>
+          <t>La Marinka — Budget estimatif toiture (260 m²) et ravalement des façades</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Charpente / sécurité</t>
+          <t>Façades (maison + grange)</t>
         </is>
       </c>
       <c r="B11" s="12" t="n"/>
@@ -4067,22 +4067,22 @@
       <c r="A12" s="8" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Reprise ponctuelle de charpente + traitement insectes / champignons</t>
+          <t>Ravalement sur pisé : piquage, réparations, enduit chaux 3 couches</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>forfait</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2000</v>
+        <v>60</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>10000</v>
+        <v>120</v>
       </c>
       <c r="G12" s="15">
         <f>D12*E12</f>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="J12" s="16" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="K12" s="15">
         <f>IF(I12="Oui",G12*J12,G12)</f>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Selon diagnostic ; reprise lourde non comprise.</t>
+          <t>Surface de façades à métrer (≈ 250 m² grange + 150 à 250 m² maison). Jamais d'enduit ciment sur le pisé.</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Échafaudage, protections, sécurité</t>
+          <t>Encadrements, appuis, soubassement drainant (anti-remontées)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -4135,10 +4135,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="G13" s="15">
         <f>D13*E13</f>
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="J13" s="16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K13" s="15">
         <f>IF(I13="Oui",G13*J13,G13)</f>
@@ -4169,402 +4169,531 @@
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>Parfois inclus dans le devis du couvreur.</t>
-        </is>
-      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Charpente / sécurité</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="18" t="inlineStr">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Reprise ponctuelle de charpente + traitement insectes / champignons</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G15" s="15">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="H15" s="15">
+        <f>D15*F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K15" s="15">
+        <f>IF(I15="Oui",G15*J15,G15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="15">
+        <f>IF(I15="Oui",H15*J15,H15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="17" t="n"/>
+      <c r="N15" s="15">
+        <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
+        <v/>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>Selon diagnostic ; reprise lourde non comprise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Échafaudage, protections, sécurité (toiture + façades)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>forfait</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G16" s="15">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="H16" s="15">
+        <f>D16*F16</f>
+        <v/>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K16" s="15">
+        <f>IF(I16="Oui",G16*J16,G16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="15">
+        <f>IF(I16="Oui",H16*J16,H16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="17" t="n"/>
+      <c r="N16" s="15">
+        <f>IF(N(M16)&gt;0,M16,(G16+H16)/2)</f>
+        <v/>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>À mutualiser entre couvreur et façadier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G15" s="19">
-        <f>SUM(G5:G13)</f>
-        <v/>
-      </c>
-      <c r="H15" s="19">
-        <f>SUM(H5:H13)</f>
-        <v/>
-      </c>
-      <c r="K15" s="19">
-        <f>SUM(K5:K13)</f>
-        <v/>
-      </c>
-      <c r="L15" s="19">
-        <f>SUM(L5:L13)</f>
-        <v/>
-      </c>
-      <c r="N15" s="19">
-        <f>SUM(N5:N13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>Imprévus</t>
-        </is>
-      </c>
-      <c r="G16" s="21">
-        <f>G15*Paramètres!$B$4</f>
-        <v/>
-      </c>
-      <c r="H16" s="21">
-        <f>H15*Paramètres!$B$4</f>
-        <v/>
-      </c>
-      <c r="K16" s="21">
-        <f>K15*Paramètres!$B$4</f>
-        <v/>
-      </c>
-      <c r="L16" s="21">
-        <f>L15*Paramètres!$B$4</f>
-        <v/>
-      </c>
-      <c r="N16" s="21">
-        <f>N15*Paramètres!$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>Maîtrise d'œuvre</t>
-        </is>
-      </c>
-      <c r="G17" s="21">
-        <f>G15*Paramètres!$B$5</f>
-        <v/>
-      </c>
-      <c r="H17" s="21">
-        <f>H15*Paramètres!$B$5</f>
-        <v/>
-      </c>
-      <c r="K17" s="21">
-        <f>K15*Paramètres!$B$5</f>
-        <v/>
-      </c>
-      <c r="L17" s="21">
-        <f>L15*Paramètres!$B$5</f>
-        <v/>
-      </c>
-      <c r="N17" s="21">
-        <f>N15*Paramètres!$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL TOITURE TTC (sans sarking)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="24">
-        <f>G15+G16+G17</f>
-        <v/>
-      </c>
-      <c r="H18" s="24">
-        <f>H15+H16+H17</f>
-        <v/>
-      </c>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="22" t="n"/>
-      <c r="K18" s="24">
-        <f>K15+K16+K17</f>
-        <v/>
-      </c>
-      <c r="L18" s="24">
-        <f>L15+L16+L17</f>
-        <v/>
-      </c>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="24">
-        <f>N15+N16+N17</f>
-        <v/>
-      </c>
-      <c r="O18" s="22" t="n"/>
+      <c r="G18" s="19">
+        <f>SUM(G5:G16)</f>
+        <v/>
+      </c>
+      <c r="H18" s="19">
+        <f>SUM(H5:H16)</f>
+        <v/>
+      </c>
+      <c r="K18" s="19">
+        <f>SUM(K5:K16)</f>
+        <v/>
+      </c>
+      <c r="L18" s="19">
+        <f>SUM(L5:L16)</f>
+        <v/>
+      </c>
+      <c r="N18" s="19">
+        <f>SUM(N5:N16)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="20" t="inlineStr">
         <is>
+          <t>Imprévus</t>
+        </is>
+      </c>
+      <c r="G19" s="21">
+        <f>G18*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="H19" s="21">
+        <f>H18*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="K19" s="21">
+        <f>K18*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="L19" s="21">
+        <f>L18*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="N19" s="21">
+        <f>N18*Paramètres!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Maîtrise d'œuvre</t>
+        </is>
+      </c>
+      <c r="G20" s="21">
+        <f>G18*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="H20" s="21">
+        <f>H18*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="K20" s="21">
+        <f>K18*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="L20" s="21">
+        <f>L18*Paramètres!$B$5</f>
+        <v/>
+      </c>
+      <c r="N20" s="21">
+        <f>N18*Paramètres!$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n"/>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>TOTAL TOITURE + FAÇADES TTC (sans sarking)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="24">
+        <f>G18+G19+G20</f>
+        <v/>
+      </c>
+      <c r="H21" s="24">
+        <f>H18+H19+H20</f>
+        <v/>
+      </c>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="24">
+        <f>K18+K19+K20</f>
+        <v/>
+      </c>
+      <c r="L21" s="24">
+        <f>L18+L19+L20</f>
+        <v/>
+      </c>
+      <c r="M21" s="22" t="n"/>
+      <c r="N21" s="24">
+        <f>N18+N19+N20</f>
+        <v/>
+      </c>
+      <c r="O21" s="22" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
+        <is>
           <t>Soit par m² (260 m²)</t>
         </is>
       </c>
-      <c r="G19" s="25">
-        <f>G18/260</f>
-        <v/>
-      </c>
-      <c r="H19" s="25">
-        <f>H18/260</f>
-        <v/>
-      </c>
-      <c r="K19" s="25">
-        <f>K18/260</f>
-        <v/>
-      </c>
-      <c r="L19" s="25">
-        <f>L18/260</f>
-        <v/>
-      </c>
-      <c r="N19" s="25">
-        <f>N18/260</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="10" t="inlineStr">
+      <c r="G22" s="25">
+        <f>G21/260</f>
+        <v/>
+      </c>
+      <c r="H22" s="25">
+        <f>H21/260</f>
+        <v/>
+      </c>
+      <c r="K22" s="25">
+        <f>K21/260</f>
+        <v/>
+      </c>
+      <c r="L22" s="25">
+        <f>L21/260</f>
+        <v/>
+      </c>
+      <c r="N22" s="25">
+        <f>N21/260</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Lecture : « Total min / max » = fourchette entreprise. « Auto min / max » = coût si vous réalisez vous-même les postes marqués « Oui »</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="10" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>(vous ne payez alors que la part matériaux). « Montant retenu » = devis reçu s'il est saisi, sinon la moyenne min/max.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="10" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Source : estimations indicatives de prix moyens du marché (ordre de grandeur), à remplacer par les devis d'artisans.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>OPTION SARKING</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Isolation posée par l'extérieur pendant la réfection (remplace l'isolation intérieure des rampants de l'étage)</t>
         </is>
       </c>
-      <c r="C25" s="27" t="n"/>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
-      <c r="H25" s="27" t="n"/>
-      <c r="I25" s="27" t="n"/>
-      <c r="J25" s="27" t="n"/>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="27" t="n"/>
-      <c r="M25" s="27" t="n"/>
-      <c r="N25" s="27" t="n"/>
-      <c r="O25" s="27" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="27" t="n"/>
+      <c r="H28" s="27" t="n"/>
+      <c r="I28" s="27" t="n"/>
+      <c r="J28" s="27" t="n"/>
+      <c r="K28" s="27" t="n"/>
+      <c r="L28" s="27" t="n"/>
+      <c r="M28" s="27" t="n"/>
+      <c r="N28" s="27" t="n"/>
+      <c r="O28" s="27" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Isolation sarking fibre de bois 160-200 mm + pare-pluie (sur chevrons)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D29" s="13" t="n">
         <v>260</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E29" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F29" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="G26" s="15">
-        <f>D26*E26</f>
-        <v/>
-      </c>
-      <c r="H26" s="15">
-        <f>D26*F26</f>
-        <v/>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="G29" s="15">
+        <f>D29*E29</f>
+        <v/>
+      </c>
+      <c r="H29" s="15">
+        <f>D29*F29</f>
+        <v/>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J26" s="16" t="n">
+      <c r="J29" s="16" t="n">
         <v>0.55</v>
       </c>
-      <c r="K26" s="15">
-        <f>IF(I26="Oui",G26*J26,G26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="15">
-        <f>IF(I26="Oui",H26*J26,H26)</f>
-        <v/>
-      </c>
-      <c r="M26" s="17" t="n"/>
-      <c r="N26" s="15">
-        <f>IF(N(M26)&gt;0,M26,(G26+H26)/2)</f>
-        <v/>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
+      <c r="K29" s="15">
+        <f>IF(I29="Oui",G29*J29,G29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="15">
+        <f>IF(I29="Oui",H29*J29,H29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="17" t="n"/>
+      <c r="N29" s="15">
+        <f>IF(N(M29)&gt;0,M29,(G29+H29)/2)</f>
+        <v/>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
         <is>
           <t>Charpente apparente à l'étage, R ≈ 4 à 5.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Rehausse des rives et adaptation zinguerie à l'épaisseur d'isolant</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>forfait</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E30" s="14" t="n">
         <v>1500</v>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F30" s="14" t="n">
         <v>4000</v>
       </c>
-      <c r="G27" s="15">
-        <f>D27*E27</f>
-        <v/>
-      </c>
-      <c r="H27" s="15">
-        <f>D27*F27</f>
-        <v/>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="G30" s="15">
+        <f>D30*E30</f>
+        <v/>
+      </c>
+      <c r="H30" s="15">
+        <f>D30*F30</f>
+        <v/>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J27" s="16" t="n">
+      <c r="J30" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="K27" s="15">
-        <f>IF(I27="Oui",G27*J27,G27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="15">
-        <f>IF(I27="Oui",H27*J27,H27)</f>
-        <v/>
-      </c>
-      <c r="M27" s="17" t="n"/>
-      <c r="N27" s="15">
-        <f>IF(N(M27)&gt;0,M27,(G27+H27)/2)</f>
-        <v/>
-      </c>
-      <c r="O27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="18" t="inlineStr">
+      <c r="K30" s="15">
+        <f>IF(I30="Oui",G30*J30,G30)</f>
+        <v/>
+      </c>
+      <c r="L30" s="15">
+        <f>IF(I30="Oui",H30*J30,H30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="17" t="n"/>
+      <c r="N30" s="15">
+        <f>IF(N(M30)&gt;0,M30,(G30+H30)/2)</f>
+        <v/>
+      </c>
+      <c r="O30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>Sous-total option sarking</t>
         </is>
       </c>
-      <c r="G28" s="19">
-        <f>SUM(G26:G27)</f>
-        <v/>
-      </c>
-      <c r="H28" s="19">
-        <f>SUM(H26:H27)</f>
-        <v/>
-      </c>
-      <c r="K28" s="19">
-        <f>SUM(K26:K27)</f>
-        <v/>
-      </c>
-      <c r="L28" s="19">
-        <f>SUM(L26:L27)</f>
-        <v/>
-      </c>
-      <c r="N28" s="19">
-        <f>SUM(N26:N27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="20" t="inlineStr">
+      <c r="G31" s="19">
+        <f>SUM(G29:G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="19">
+        <f>SUM(H29:H30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="19">
+        <f>SUM(K29:K30)</f>
+        <v/>
+      </c>
+      <c r="L31" s="19">
+        <f>SUM(L29:L30)</f>
+        <v/>
+      </c>
+      <c r="N31" s="19">
+        <f>SUM(N29:N30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>Économie : isolation intérieure des rampants supprimée (onglet étage)</t>
         </is>
       </c>
-      <c r="G29" s="21">
+      <c r="G32" s="21">
         <f>-'Budget étage'!G10</f>
         <v/>
       </c>
-      <c r="H29" s="21">
+      <c r="H32" s="21">
         <f>-'Budget étage'!H10</f>
         <v/>
       </c>
-      <c r="K29" s="21">
+      <c r="K32" s="21">
         <f>-'Budget étage'!K10</f>
         <v/>
       </c>
-      <c r="L29" s="21">
+      <c r="L32" s="21">
         <f>-'Budget étage'!L10</f>
         <v/>
       </c>
-      <c r="N29" s="21">
+      <c r="N32" s="21">
         <f>-'Budget étage'!N10</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="22" t="n"/>
-      <c r="B30" s="23" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="22" t="n"/>
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>SURCOÛT NET OPTION SARKING TTC (imprévus + MOE inclus)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-      <c r="E30" s="22" t="n"/>
-      <c r="F30" s="22" t="n"/>
-      <c r="G30" s="24">
-        <f>(G28+G29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H30" s="24">
-        <f>(H28+H29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I30" s="22" t="n"/>
-      <c r="J30" s="22" t="n"/>
-      <c r="K30" s="24">
-        <f>(K28+K29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
-        <v/>
-      </c>
-      <c r="L30" s="24">
-        <f>(L28+L29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
-        <v/>
-      </c>
-      <c r="M30" s="22" t="n"/>
-      <c r="N30" s="24">
-        <f>(N28+N29)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
-        <v/>
-      </c>
-      <c r="O30" s="22" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="10" t="inlineStr">
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="24">
+        <f>(G31+G32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="H33" s="24">
+        <f>(H31+H32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="22" t="n"/>
+      <c r="K33" s="24">
+        <f>(K31+K32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="L33" s="24">
+        <f>(L31+L32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="M33" s="22" t="n"/>
+      <c r="N33" s="24">
+        <f>(N31+N32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
+        <v/>
+      </c>
+      <c r="O33" s="22" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Le sarking garde la charpente apparente, libère quelques cm de hauteur sous rampant et facilite la pose étanche des Velux.</t>
         </is>
@@ -4572,7 +4701,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I6 I7 I8 I9 I10 I12 I13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I6 I7 I8 I9 I10 I12 I13 I15 I16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Oui,Non"</formula1>
     </dataValidation>
   </dataValidations>

--- a/la-marinka/La Marinka.xlsx
+++ b/la-marinka/La Marinka.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Budget étage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Budget RDC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Budget Toiture" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Paramètres" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Estimation revente" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Budget étage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Budget RDC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Budget Toiture" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Paramètres" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +21,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0 €;-#,##0 €;&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0 &quot;€/m²&quot;;;&quot;n.c.&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0 &quot;€/m²&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0 €;[Red]-#,##0 €"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +68,17 @@
     <font>
       <name val="Arial"/>
       <color rgb="00008000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005B4636"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="6">
@@ -120,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -134,6 +149,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -848,6 +907,1859 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>La Marinka — Estimation de la valeur de revente après travaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>139 impasse du Brézet, 38440 Sainte-Anne-sur-Gervonde. Estimation indicative (octobre 2026), établie à partir des prix publiés et d'annonces ; à confirmer par des ventes réelles (DVF) et des avis de valeur d'agences locales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>1. Hypothèses du bien</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Paramètre</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Valeur</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Surface habitable finale (m²)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>232</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>90 m² maison + 72 m² RDC grange + 69 m² étage ; l'étage sous rampant peut descendre à 55-62 m² légaux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Terrain (m²)</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Norme haute du secteur rural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Prix d'achat frais de notaire compris (€)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Donnée fournie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Extérieurs hors budget travaux (€) : piscine, jacuzzi, pergola, paysager, irrigation</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Hypothèse centrale (60 à 110 k€) : non chiffrés dans les onglets travaux.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Grange indépendante : surface utile (m²)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>≈ 300 m² au sol + 200 m² en R+1, toiture neuve, dalle béton. Non habitable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>2. Prix du marché local (maisons)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Commune</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>€/m² maison</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nature de la donnée</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Sainte-Anne-sur-Gervonde</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>1 983 (DVF 2025, 6 ventes) à 2 286-2 458</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Ventes réelles / estimations agrégateurs ; tendance 12 mois en baisse</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Châtonnay</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>2 301-2 362</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Estimation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Saint-Jean-de-Bournay</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>2 223-2 458</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Estimation ; pic 2 589 en 2022 puis repli</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Meyrieu-les-Étangs</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2 321</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Estimation ; -12,6 % sur un an</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Villeneuve-de-Marc</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>2 333</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Estimation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Savas-Mépin</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2 504</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Estimation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Artas</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>2 742</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Estimation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Beauvoir-de-Marc</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>2 952</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Estimation ; commune plus proche de Lyon</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Grandes maisons vendues à Saint-Jean-de-Bournay (202-235 m²)</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>1 213-1 906</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Ventes réelles : forte décote au m² des grandes surfaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>3. Biens comparables</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Commune</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Habitable</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Terrain</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Dépendances</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Piscine</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>État</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Prix €</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>€/m²</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Comparabilité</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Saint-Jean-de-Bournay</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>293 m², 6 ch.</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>4 800 m²</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Bon (présumé)</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>580000</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>1980</v>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>Élevée : plafond affiché du secteur</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Saint-Jean-de-Bournay</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>169 m², 6 ch.</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>2 513 m²</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>383000</v>
+      </c>
+      <c r="I27" s="16" t="n">
+        <v>2266</v>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>Moyenne (plus petit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Beauvoir-de-Marc</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>1 514 m²</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Oui (creusée)</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>502000</v>
+      </c>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>Moyenne (commune plus chère)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Collines dauphinoises (Safer)</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>≈ 250 m², pisé</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>1,9 ha</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Bâtiment agricole pisé aménagé</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Rénové</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Affiché HFS</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>570000</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>2280</v>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>Moyenne à élevée (pisé + grande dépendance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Secteur Vienne (3 min A7)</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>220 m², 6 ch.</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>1 125 m²</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>Pierre, rénové</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>630000</v>
+      </c>
+      <c r="I30" s="16" t="n">
+        <v>2864</v>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>Faible à moyenne (emplacement supérieur)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Châtonnay</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>≈ 300 m²</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>1 000 m²</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Tout à rénover</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>275000</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>917</v>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>Faible (illustre la décote travaux)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Saint-Jean-de-Bournay</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>202 m²</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Vendu</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>385000</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>1906</v>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>Moyenne (vente réelle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Lieudieu</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>300 m², 6 ch.</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>9 702 m²</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Domaine</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Exception</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <v>4300</v>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>Très faible (hors norme)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Satolas (Nord-Isère) — dépendance seule</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Hangars 2 680 m²</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>230000</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <v>86</v>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>Référence grange</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Isère — dépendance seule</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Grange 727 m²</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>165</v>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>Référence grange</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Aucune vente réelle documentée &gt; 500 000 € dans la commune ni dans les communes limitrophes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>4. Construction de la valeur (approche par composantes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Composante</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Bas €</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Central €</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Haut €</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Maison rénovée ≈ 230 m² (hors extérieurs)</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>450000</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>485000</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>530000</v>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>2 050-2 350 €/m² : grande maison de caractère rénovée, décote des grandes surfaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Piscine enterrée 3 × 5 m</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Atout réel mais perçu aussi comme une charge d'entretien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Pergola bioclimatique + espace repas</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Jacuzzi, pétanque, brasero, barbecue</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Équipements, pas de valeur foncière.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Calme absolu (impasse de 3 maisons)</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>Prime réelle mais fréquente en secteur rural.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Puits fonctionnel + irrigation du jardin</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Utile sur 1 700 m² ; usage limitable par arrêtés sécheresse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Façades neuves (enduit chaux)</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>12500</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Évite la décote « ravalement à prévoir ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Grange indépendante ≈ 500 m² utiles</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>80-200 €/m² utile ; acheteurs ciblés (collectionneur, artisan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Ajustement plafond de marché local / délai</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>-66000</v>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>Bien au sommet du marché local : peu d'acheteurs, négociation 5-10 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>VALEUR ESTIMÉE</t>
+        </is>
+      </c>
+      <c r="B49" s="18">
+        <f>SUM(B40:B48)</f>
+        <v/>
+      </c>
+      <c r="C49" s="18">
+        <f>SUM(C40:C48)</f>
+        <v/>
+      </c>
+      <c r="D49" s="18">
+        <f>SUM(D40:D48)</f>
+        <v/>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>Bas ≈ vente rapide ; central = valeur retenue ; haut = annonce ambitieuse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Option non comprise : grange identifiée « changement de destination » au PLUi</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>À ne compter que si confirmé en mairie (PLUi Région Saint-Jeannaise + avis CDPENAF en zone A).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>5. Scénarios de vente</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Scénario</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Prix €</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>€/m² habitable</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>€/m² hors grange</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Délai probable</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Vente rapide</t>
+        </is>
+      </c>
+      <c r="B54" s="15">
+        <f>B49</f>
+        <v/>
+      </c>
+      <c r="C54" s="20">
+        <f>B54/$B$6</f>
+        <v/>
+      </c>
+      <c r="D54" s="20">
+        <f>(B54-$C$47)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>&lt; 3 mois</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Valeur de marché réaliste</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="n">
+        <v>580000</v>
+      </c>
+      <c r="C55" s="20">
+        <f>B55/$B$6</f>
+        <v/>
+      </c>
+      <c r="D55" s="20">
+        <f>(B55-$C$47)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>6 à 9 mois</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>Fourchette réaliste 570-600 k€.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Annonce ambitieuse mais défendable</t>
+        </is>
+      </c>
+      <c r="B56" s="15">
+        <f>D49</f>
+        <v/>
+      </c>
+      <c r="C56" s="20">
+        <f>B56/$B$6</f>
+        <v/>
+      </c>
+      <c r="D56" s="20">
+        <f>(B56-$C$47)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>9 à 18 mois</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Négociation probable vers 590-600 k€.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>VALEUR CENTRALE RETENUE</t>
+        </is>
+      </c>
+      <c r="B57" s="18">
+        <f>C49</f>
+        <v/>
+      </c>
+      <c r="C57" s="21">
+        <f>B57/$B$6</f>
+        <v/>
+      </c>
+      <c r="D57" s="21">
+        <f>(B57-$C$47)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E57" s="19" t="inlineStr"/>
+      <c r="F57" s="19" t="inlineStr">
+        <is>
+          <t>Maison ≈ 515 k€ + calme / puits / façades + grange ≈ 65 k€, après plafond de marché.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>6. Ces prix sont-ils réalistes ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Prix</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>€/m² habitable</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Pourquoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="n">
+        <v>600000</v>
+      </c>
+      <c r="B61" s="20">
+        <f>A61/$B$6</f>
+        <v/>
+      </c>
+      <c r="C61" s="22" t="inlineStr">
+        <is>
+          <t>Objectif haut atteignable</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Exécution parfaite + acheteur qui valorise la grange ; haut de la fourchette, pas le cas de base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="n">
+        <v>650000</v>
+      </c>
+      <c r="B62" s="20">
+        <f>A62/$B$6</f>
+        <v/>
+      </c>
+      <c r="C62" s="22" t="inlineStr">
+        <is>
+          <t>Prix d'annonce, pas de vente</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>Au-dessus de tout ce qui s'affiche localement hors cas d'exception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="n">
+        <v>700000</v>
+      </c>
+      <c r="B63" s="20">
+        <f>A63/$B$6</f>
+        <v/>
+      </c>
+      <c r="C63" s="22" t="inlineStr">
+        <is>
+          <t>Irréaliste aujourd'hui</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>≈ 3 000 €/m², &gt; 50 % au-dessus des ventes réelles de la commune ; aucun comparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>7. Coût total du projet face à la valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Élément</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Montant €</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Prix d'achat</t>
+        </is>
+      </c>
+      <c r="B67" s="23">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Hypothèses</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>Travaux (étage + RDC + toiture + façades), montant retenu sans sarking</t>
+        </is>
+      </c>
+      <c r="B68" s="23">
+        <f>Synthèse!F7</f>
+        <v/>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>Onglet Synthèse</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>Postes hors budget (moyenne)</t>
+        </is>
+      </c>
+      <c r="B69" s="23">
+        <f>(Paramètres!B14+Paramètres!C14)/2</f>
+        <v/>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Onglet Paramètres</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>Extérieurs (piscine, jacuzzi, pergola, paysager…)</t>
+        </is>
+      </c>
+      <c r="B70" s="23">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>Hypothèses</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>COÛT TOTAL DU PROJET</t>
+        </is>
+      </c>
+      <c r="B71" s="24">
+        <f>SUM(B67:B70)</f>
+        <v/>
+      </c>
+      <c r="C71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>Valeur centrale retenue</t>
+        </is>
+      </c>
+      <c r="B72" s="23">
+        <f>B57</f>
+        <v/>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Section 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>PLUS / MOINS-VALUE LATENTE</t>
+        </is>
+      </c>
+      <c r="B73" s="25">
+        <f>B72-B71</f>
+        <v/>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>Négatif = le marché ne rembourse pas tout l'investissement</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>8. Ce qui peut faire varier la valeur de ± 50 k€ ou plus</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Facteur</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Sens</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Impact estimé</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>Grange identifiée « changement de destination » au PLUi</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>+20 à +50 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>DPE A/B (sarking, PAC, pisé sain)</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>+10 à +30 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>Maison existante rénovée au même niveau, cuisine ouverte vers le séjour</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>+15 à +40 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>Historique Airbnb 12-24 mois avec comptes certifiés</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>+10 à +40 k€ (acheteur investisseur)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>Acheteur collectionneur / artisan valorisant la grange</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>+20 à +50 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>Maison existante pas au niveau de la grange (effet « deux bâtiments »)</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>−30 à −60 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>Surface habitable légale réduite par les rampants</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>−10 à −30 k€ (lecture de l'annonce)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>DPE D ou pire, humidité dans le pisé</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>−20 à −50 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Assainissement non conforme (SPANC)</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>−10 à −25 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>Dossiers incomplets : changement de destination, DAACT, amiante grange</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Blocage ou −20 à −50 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>Hausse des taux de crédit</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>−5 à −10 % de la valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>Bien perçu comme « gîte » plutôt que maison familiale</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>−10 à −30 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>9. Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="26" t="inlineStr">
+        <is>
+          <t>Square Habitat – Sainte-Anne-sur-Gervonde</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>PAP – Sainte-Anne-sur-Gervonde</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>Immovrai – Sainte-Anne-sur-Gervonde (DVF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="26" t="inlineStr">
+        <is>
+          <t>Immovrai – Châtonnay</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="26" t="inlineStr">
+        <is>
+          <t>Immovrai – Meyrieu-les-Étangs</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="26" t="inlineStr">
+        <is>
+          <t>PAP – Saint-Jean-de-Bournay</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="26" t="inlineStr">
+        <is>
+          <t>MeilleursAgents – Saint-Jean-de-Bournay</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="26" t="inlineStr">
+        <is>
+          <t>PAP – Beauvoir-de-Marc</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="26" t="inlineStr">
+        <is>
+          <t>Logic-immo – maisons avec piscine à Saint-Jean-de-Bournay</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="26" t="inlineStr">
+        <is>
+          <t>Nestenn – Beauvoir-de-Marc, maison avec piscine</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="26" t="inlineStr">
+        <is>
+          <t>Propriétés Rurales – corps de ferme rénové</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="26" t="inlineStr">
+        <is>
+          <t>Belles Demeures – secteur Vienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>Zimo – hangars à vendre en Isère</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="26" t="inlineStr">
+        <is>
+          <t>French Property – hangars Nord-Isère</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t>MRAe – PLUi Bièvre Isère, secteur Région Saint-Jeannaise</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="26" t="inlineStr">
+        <is>
+          <t>DVF officiel (ventes réelles, à consulter)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId16"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -960,25 +2872,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Gros œuvre</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="12" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="28" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -992,41 +2904,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="30" t="n">
         <v>3000</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="30" t="n">
         <v>8000</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="31">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="31">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
+      <c r="J6" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="31">
         <f>IF(I6="Oui",G6*J6,G6)</f>
         <v/>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="31">
         <f>IF(I6="Oui",H6*J6,H6)</f>
         <v/>
       </c>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="15">
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="31">
         <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
         <v/>
       </c>
@@ -1048,41 +2960,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="31">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="31">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="J7" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="31">
         <f>IF(I7="Oui",G7*J7,G7)</f>
         <v/>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="31">
         <f>IF(I7="Oui",H7*J7,H7)</f>
         <v/>
       </c>
-      <c r="M7" s="17" t="n"/>
-      <c r="N7" s="15">
+      <c r="M7" s="33" t="n"/>
+      <c r="N7" s="31">
         <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
         <v/>
       </c>
@@ -1100,41 +3012,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="30" t="n">
         <v>4000</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="30" t="n">
         <v>9000</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="31">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="31">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="31">
         <f>IF(I8="Oui",G8*J8,G8)</f>
         <v/>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="31">
         <f>IF(I8="Oui",H8*J8,H8)</f>
         <v/>
       </c>
-      <c r="M8" s="17" t="n"/>
-      <c r="N8" s="15">
+      <c r="M8" s="33" t="n"/>
+      <c r="N8" s="31">
         <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
         <v/>
       </c>
@@ -1145,25 +3057,25 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Enveloppe / isolation</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="28" t="n"/>
+      <c r="O9" s="28" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
@@ -1177,41 +3089,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="30" t="n">
         <v>120</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="30" t="n">
         <v>250</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="31">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="31">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J10" s="16" t="n">
+      <c r="J10" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="31">
         <f>IF(I10="Oui",G10*J10,G10)</f>
         <v/>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="31">
         <f>IF(I10="Oui",H10*J10,H10)</f>
         <v/>
       </c>
-      <c r="M10" s="17" t="n"/>
-      <c r="N10" s="15">
+      <c r="M10" s="33" t="n"/>
+      <c r="N10" s="31">
         <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
         <v/>
       </c>
@@ -1233,41 +3145,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="30" t="n">
         <v>1600</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="31">
         <f>D11*E11</f>
         <v/>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="31">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J11" s="16" t="n">
+      <c r="J11" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="31">
         <f>IF(I11="Oui",G11*J11,G11)</f>
         <v/>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="31">
         <f>IF(I11="Oui",H11*J11,H11)</f>
         <v/>
       </c>
-      <c r="M11" s="17" t="n"/>
-      <c r="N11" s="15">
+      <c r="M11" s="33" t="n"/>
+      <c r="N11" s="31">
         <f>IF(N(M11)&gt;0,M11,(G11+H11)/2)</f>
         <v/>
       </c>
@@ -1289,41 +3201,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="30" t="n">
         <v>800</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="30" t="n">
         <v>1300</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="31">
         <f>D12*E12</f>
         <v/>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="31">
         <f>D12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J12" s="16" t="n">
+      <c r="J12" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="31">
         <f>IF(I12="Oui",G12*J12,G12)</f>
         <v/>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="31">
         <f>IF(I12="Oui",H12*J12,H12)</f>
         <v/>
       </c>
-      <c r="M12" s="17" t="n"/>
-      <c r="N12" s="15">
+      <c r="M12" s="33" t="n"/>
+      <c r="N12" s="31">
         <f>IF(N(M12)&gt;0,M12,(G12+H12)/2)</f>
         <v/>
       </c>
@@ -1341,41 +3253,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="29" t="n">
         <v>70</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="30" t="n">
         <v>130</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="31">
         <f>D13*E13</f>
         <v/>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="31">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="31">
         <f>IF(I13="Oui",G13*J13,G13)</f>
         <v/>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="31">
         <f>IF(I13="Oui",H13*J13,H13)</f>
         <v/>
       </c>
-      <c r="M13" s="17" t="n"/>
-      <c r="N13" s="15">
+      <c r="M13" s="33" t="n"/>
+      <c r="N13" s="31">
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
@@ -1386,25 +3298,25 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Cloisons / plafonds</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="12" t="n"/>
-      <c r="O14" s="12" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="28" t="n"/>
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="28" t="n"/>
+      <c r="M14" s="28" t="n"/>
+      <c r="N14" s="28" t="n"/>
+      <c r="O14" s="28" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -1418,41 +3330,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="29" t="n">
         <v>75</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="30" t="n">
         <v>55</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="31">
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="31">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J15" s="16" t="n">
+      <c r="J15" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="31">
         <f>IF(I15="Oui",G15*J15,G15)</f>
         <v/>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="31">
         <f>IF(I15="Oui",H15*J15,H15)</f>
         <v/>
       </c>
-      <c r="M15" s="17" t="n"/>
-      <c r="N15" s="15">
+      <c r="M15" s="33" t="n"/>
+      <c r="N15" s="31">
         <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
         <v/>
       </c>
@@ -1470,66 +3382,66 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="29" t="n">
         <v>100</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="31">
         <f>D16*E16</f>
         <v/>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="31">
         <f>D16*F16</f>
         <v/>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J16" s="16" t="n">
+      <c r="J16" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="31">
         <f>IF(I16="Oui",G16*J16,G16)</f>
         <v/>
       </c>
-      <c r="L16" s="15">
+      <c r="L16" s="31">
         <f>IF(I16="Oui",H16*J16,H16)</f>
         <v/>
       </c>
-      <c r="M16" s="17" t="n"/>
-      <c r="N16" s="15">
+      <c r="M16" s="33" t="n"/>
+      <c r="N16" s="31">
         <f>IF(N(M16)&gt;0,M16,(G16+H16)/2)</f>
         <v/>
       </c>
       <c r="O16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Plomberie</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="12" t="n"/>
+      <c r="B17" s="28" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="28" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
@@ -1543,41 +3455,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="30" t="n">
         <v>9000</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="31">
         <f>D18*E18</f>
         <v/>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="31">
         <f>D18*F18</f>
         <v/>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J18" s="16" t="n">
+      <c r="J18" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="31">
         <f>IF(I18="Oui",G18*J18,G18)</f>
         <v/>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="31">
         <f>IF(I18="Oui",H18*J18,H18)</f>
         <v/>
       </c>
-      <c r="M18" s="17" t="n"/>
-      <c r="N18" s="15">
+      <c r="M18" s="33" t="n"/>
+      <c r="N18" s="31">
         <f>IF(N(M18)&gt;0,M18,(G18+H18)/2)</f>
         <v/>
       </c>
@@ -1599,41 +3511,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="30" t="n">
         <v>1500</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="30" t="n">
         <v>3000</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="31">
         <f>D19*E19</f>
         <v/>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="31">
         <f>D19*F19</f>
         <v/>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I19" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J19" s="16" t="n">
+      <c r="J19" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K19" s="15">
+      <c r="K19" s="31">
         <f>IF(I19="Oui",G19*J19,G19)</f>
         <v/>
       </c>
-      <c r="L19" s="15">
+      <c r="L19" s="31">
         <f>IF(I19="Oui",H19*J19,H19)</f>
         <v/>
       </c>
-      <c r="M19" s="17" t="n"/>
-      <c r="N19" s="15">
+      <c r="M19" s="33" t="n"/>
+      <c r="N19" s="31">
         <f>IF(N(M19)&gt;0,M19,(G19+H19)/2)</f>
         <v/>
       </c>
@@ -1651,41 +3563,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="30" t="n">
         <v>500</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="31">
         <f>D20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="31">
         <f>D20*F20</f>
         <v/>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I20" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J20" s="16" t="n">
+      <c r="J20" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="31">
         <f>IF(I20="Oui",G20*J20,G20)</f>
         <v/>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="31">
         <f>IF(I20="Oui",H20*J20,H20)</f>
         <v/>
       </c>
-      <c r="M20" s="17" t="n"/>
-      <c r="N20" s="15">
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="31">
         <f>IF(N(M20)&gt;0,M20,(G20+H20)/2)</f>
         <v/>
       </c>
@@ -1707,41 +3619,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="30" t="n">
         <v>4000</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="31">
         <f>D21*E21</f>
         <v/>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="31">
         <f>D21*F21</f>
         <v/>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I21" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J21" s="16" t="n">
+      <c r="J21" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="31">
         <f>IF(I21="Oui",G21*J21,G21)</f>
         <v/>
       </c>
-      <c r="L21" s="15">
+      <c r="L21" s="31">
         <f>IF(I21="Oui",H21*J21,H21)</f>
         <v/>
       </c>
-      <c r="M21" s="17" t="n"/>
-      <c r="N21" s="15">
+      <c r="M21" s="33" t="n"/>
+      <c r="N21" s="31">
         <f>IF(N(M21)&gt;0,M21,(G21+H21)/2)</f>
         <v/>
       </c>
@@ -1752,25 +3664,25 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Électricité / ventilation / chauffage</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
-      <c r="L22" s="12" t="n"/>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="12" t="n"/>
-      <c r="O22" s="12" t="n"/>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="28" t="n"/>
+      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="28" t="n"/>
+      <c r="M22" s="28" t="n"/>
+      <c r="N22" s="28" t="n"/>
+      <c r="O22" s="28" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -1784,41 +3696,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="29" t="n">
         <v>77</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="F23" s="14" t="n">
+      <c r="F23" s="30" t="n">
         <v>130</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="31">
         <f>D23*E23</f>
         <v/>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="31">
         <f>D23*F23</f>
         <v/>
       </c>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="I23" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J23" s="16" t="n">
+      <c r="J23" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="31">
         <f>IF(I23="Oui",G23*J23,G23)</f>
         <v/>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="31">
         <f>IF(I23="Oui",H23*J23,H23)</f>
         <v/>
       </c>
-      <c r="M23" s="17" t="n"/>
-      <c r="N23" s="15">
+      <c r="M23" s="33" t="n"/>
+      <c r="N23" s="31">
         <f>IF(N(M23)&gt;0,M23,(G23+H23)/2)</f>
         <v/>
       </c>
@@ -1836,41 +3748,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="30" t="n">
         <v>1500</v>
       </c>
-      <c r="F24" s="14" t="n">
+      <c r="F24" s="30" t="n">
         <v>3000</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="31">
         <f>D24*E24</f>
         <v/>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="31">
         <f>D24*F24</f>
         <v/>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I24" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J24" s="16" t="n">
+      <c r="J24" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K24" s="15">
+      <c r="K24" s="31">
         <f>IF(I24="Oui",G24*J24,G24)</f>
         <v/>
       </c>
-      <c r="L24" s="15">
+      <c r="L24" s="31">
         <f>IF(I24="Oui",H24*J24,H24)</f>
         <v/>
       </c>
-      <c r="M24" s="17" t="n"/>
-      <c r="N24" s="15">
+      <c r="M24" s="33" t="n"/>
+      <c r="N24" s="31">
         <f>IF(N(M24)&gt;0,M24,(G24+H24)/2)</f>
         <v/>
       </c>
@@ -1892,66 +3804,66 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="30" t="n">
         <v>4000</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F25" s="30" t="n">
         <v>12000</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="31">
         <f>D25*E25</f>
         <v/>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="31">
         <f>D25*F25</f>
         <v/>
       </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I25" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J25" s="16" t="n">
+      <c r="J25" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K25" s="15">
+      <c r="K25" s="31">
         <f>IF(I25="Oui",G25*J25,G25)</f>
         <v/>
       </c>
-      <c r="L25" s="15">
+      <c r="L25" s="31">
         <f>IF(I25="Oui",H25*J25,H25)</f>
         <v/>
       </c>
-      <c r="M25" s="17" t="n"/>
-      <c r="N25" s="15">
+      <c r="M25" s="33" t="n"/>
+      <c r="N25" s="31">
         <f>IF(N(M25)&gt;0,M25,(G25+H25)/2)</f>
         <v/>
       </c>
       <c r="O25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Menuiseries intérieures</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
-      <c r="O26" s="12" t="n"/>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="28" t="n"/>
+      <c r="J26" s="28" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="28" t="n"/>
+      <c r="M26" s="28" t="n"/>
+      <c r="N26" s="28" t="n"/>
+      <c r="O26" s="28" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -1965,41 +3877,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F27" s="30" t="n">
         <v>550</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="31">
         <f>D27*E27</f>
         <v/>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="31">
         <f>D27*F27</f>
         <v/>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I27" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J27" s="16" t="n">
+      <c r="J27" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="31">
         <f>IF(I27="Oui",G27*J27,G27)</f>
         <v/>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="31">
         <f>IF(I27="Oui",H27*J27,H27)</f>
         <v/>
       </c>
-      <c r="M27" s="17" t="n"/>
-      <c r="N27" s="15">
+      <c r="M27" s="33" t="n"/>
+      <c r="N27" s="31">
         <f>IF(N(M27)&gt;0,M27,(G27+H27)/2)</f>
         <v/>
       </c>
@@ -2021,41 +3933,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="30" t="n">
         <v>700</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="30" t="n">
         <v>1200</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="31">
         <f>D28*E28</f>
         <v/>
       </c>
-      <c r="H28" s="15">
+      <c r="H28" s="31">
         <f>D28*F28</f>
         <v/>
       </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I28" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J28" s="16" t="n">
+      <c r="J28" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="31">
         <f>IF(I28="Oui",G28*J28,G28)</f>
         <v/>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="31">
         <f>IF(I28="Oui",H28*J28,H28)</f>
         <v/>
       </c>
-      <c r="M28" s="17" t="n"/>
-      <c r="N28" s="15">
+      <c r="M28" s="33" t="n"/>
+      <c r="N28" s="31">
         <f>IF(N(M28)&gt;0,M28,(G28+H28)/2)</f>
         <v/>
       </c>
@@ -2073,66 +3985,66 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="30" t="n">
         <v>700</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="31">
         <f>D29*E29</f>
         <v/>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="31">
         <f>D29*F29</f>
         <v/>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I29" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="J29" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="31">
         <f>IF(I29="Oui",G29*J29,G29)</f>
         <v/>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="31">
         <f>IF(I29="Oui",H29*J29,H29)</f>
         <v/>
       </c>
-      <c r="M29" s="17" t="n"/>
-      <c r="N29" s="15">
+      <c r="M29" s="33" t="n"/>
+      <c r="N29" s="31">
         <f>IF(N(M29)&gt;0,M29,(G29+H29)/2)</f>
         <v/>
       </c>
       <c r="O29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>Revêtements / finitions</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="28" t="n"/>
+      <c r="H30" s="28" t="n"/>
+      <c r="I30" s="28" t="n"/>
+      <c r="J30" s="28" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="28" t="n"/>
+      <c r="M30" s="28" t="n"/>
+      <c r="N30" s="28" t="n"/>
+      <c r="O30" s="28" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -2146,41 +4058,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="29" t="n">
         <v>51</v>
       </c>
-      <c r="E31" s="14" t="n">
+      <c r="E31" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="F31" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="31">
         <f>D31*E31</f>
         <v/>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="31">
         <f>D31*F31</f>
         <v/>
       </c>
-      <c r="I31" s="13" t="inlineStr">
+      <c r="I31" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J31" s="16" t="n">
+      <c r="J31" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="31">
         <f>IF(I31="Oui",G31*J31,G31)</f>
         <v/>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="31">
         <f>IF(I31="Oui",H31*J31,H31)</f>
         <v/>
       </c>
-      <c r="M31" s="17" t="n"/>
-      <c r="N31" s="15">
+      <c r="M31" s="33" t="n"/>
+      <c r="N31" s="31">
         <f>IF(N(M31)&gt;0,M31,(G31+H31)/2)</f>
         <v/>
       </c>
@@ -2198,41 +4110,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="E32" s="14" t="n">
+      <c r="E32" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="F32" s="14" t="n">
+      <c r="F32" s="30" t="n">
         <v>130</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="31">
         <f>D32*E32</f>
         <v/>
       </c>
-      <c r="H32" s="15">
+      <c r="H32" s="31">
         <f>D32*F32</f>
         <v/>
       </c>
-      <c r="I32" s="13" t="inlineStr">
+      <c r="I32" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J32" s="16" t="n">
+      <c r="J32" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="31">
         <f>IF(I32="Oui",G32*J32,G32)</f>
         <v/>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="31">
         <f>IF(I32="Oui",H32*J32,H32)</f>
         <v/>
       </c>
-      <c r="M32" s="17" t="n"/>
-      <c r="N32" s="15">
+      <c r="M32" s="33" t="n"/>
+      <c r="N32" s="31">
         <f>IF(N(M32)&gt;0,M32,(G32+H32)/2)</f>
         <v/>
       </c>
@@ -2250,41 +4162,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E33" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="30" t="n">
         <v>130</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="31">
         <f>D33*E33</f>
         <v/>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="31">
         <f>D33*F33</f>
         <v/>
       </c>
-      <c r="I33" s="13" t="inlineStr">
+      <c r="I33" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J33" s="16" t="n">
+      <c r="J33" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="31">
         <f>IF(I33="Oui",G33*J33,G33)</f>
         <v/>
       </c>
-      <c r="L33" s="15">
+      <c r="L33" s="31">
         <f>IF(I33="Oui",H33*J33,H33)</f>
         <v/>
       </c>
-      <c r="M33" s="17" t="n"/>
-      <c r="N33" s="15">
+      <c r="M33" s="33" t="n"/>
+      <c r="N33" s="31">
         <f>IF(N(M33)&gt;0,M33,(G33+H33)/2)</f>
         <v/>
       </c>
@@ -2302,186 +4214,186 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="29" t="n">
         <v>300</v>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E34" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="F34" s="14" t="n">
+      <c r="F34" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="31">
         <f>D34*E34</f>
         <v/>
       </c>
-      <c r="H34" s="15">
+      <c r="H34" s="31">
         <f>D34*F34</f>
         <v/>
       </c>
-      <c r="I34" s="13" t="inlineStr">
+      <c r="I34" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J34" s="16" t="n">
+      <c r="J34" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="31">
         <f>IF(I34="Oui",G34*J34,G34)</f>
         <v/>
       </c>
-      <c r="L34" s="15">
+      <c r="L34" s="31">
         <f>IF(I34="Oui",H34*J34,H34)</f>
         <v/>
       </c>
-      <c r="M34" s="17" t="n"/>
-      <c r="N34" s="15">
+      <c r="M34" s="33" t="n"/>
+      <c r="N34" s="31">
         <f>IF(N(M34)&gt;0,M34,(G34+H34)/2)</f>
         <v/>
       </c>
       <c r="O34" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="34" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="35">
         <f>SUM(G5:G34)</f>
         <v/>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="35">
         <f>SUM(H5:H34)</f>
         <v/>
       </c>
-      <c r="K36" s="19">
+      <c r="K36" s="35">
         <f>SUM(K5:K34)</f>
         <v/>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="35">
         <f>SUM(L5:L34)</f>
         <v/>
       </c>
-      <c r="N36" s="19">
+      <c r="N36" s="35">
         <f>SUM(N5:N34)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
         <is>
           <t>Imprévus</t>
         </is>
       </c>
-      <c r="G37" s="21">
+      <c r="G37" s="37">
         <f>G36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="37">
         <f>H36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="K37" s="21">
+      <c r="K37" s="37">
         <f>K36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="L37" s="21">
+      <c r="L37" s="37">
         <f>L36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="N37" s="21">
+      <c r="N37" s="37">
         <f>N36*Paramètres!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre</t>
         </is>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="37">
         <f>G36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="37">
         <f>H36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="K38" s="21">
+      <c r="K38" s="37">
         <f>K36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="L38" s="21">
+      <c r="L38" s="37">
         <f>L36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="N38" s="21">
+      <c r="N38" s="37">
         <f>N36*Paramètres!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="n"/>
-      <c r="B39" s="23" t="inlineStr">
+      <c r="A39" s="38" t="n"/>
+      <c r="B39" s="39" t="inlineStr">
         <is>
           <t>TOTAL ÉTAGE TTC</t>
         </is>
       </c>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="22" t="n"/>
-      <c r="G39" s="24">
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="40">
         <f>G36+G37+G38</f>
         <v/>
       </c>
-      <c r="H39" s="24">
+      <c r="H39" s="40">
         <f>H36+H37+H38</f>
         <v/>
       </c>
-      <c r="I39" s="22" t="n"/>
-      <c r="J39" s="22" t="n"/>
-      <c r="K39" s="24">
+      <c r="I39" s="38" t="n"/>
+      <c r="J39" s="38" t="n"/>
+      <c r="K39" s="40">
         <f>K36+K37+K38</f>
         <v/>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="40">
         <f>L36+L37+L38</f>
         <v/>
       </c>
-      <c r="M39" s="22" t="n"/>
-      <c r="N39" s="24">
+      <c r="M39" s="38" t="n"/>
+      <c r="N39" s="40">
         <f>N36+N37+N38</f>
         <v/>
       </c>
-      <c r="O39" s="22" t="n"/>
+      <c r="O39" s="38" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>Soit par m² (77 m²)</t>
         </is>
       </c>
-      <c r="G40" s="25">
+      <c r="G40" s="41">
         <f>G39/77</f>
         <v/>
       </c>
-      <c r="H40" s="25">
+      <c r="H40" s="41">
         <f>H39/77</f>
         <v/>
       </c>
-      <c r="K40" s="25">
+      <c r="K40" s="41">
         <f>K39/77</f>
         <v/>
       </c>
-      <c r="L40" s="25">
+      <c r="L40" s="41">
         <f>L39/77</f>
         <v/>
       </c>
-      <c r="N40" s="25">
+      <c r="N40" s="41">
         <f>N39/77</f>
         <v/>
       </c>
@@ -2518,7 +4430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2636,25 +4548,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Gros œuvre / structure</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="12" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="28" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -2668,41 +4580,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="30" t="n">
         <v>6000</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="30" t="n">
         <v>15000</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="31">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="31">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
+      <c r="J6" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="31">
         <f>IF(I6="Oui",G6*J6,G6)</f>
         <v/>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="31">
         <f>IF(I6="Oui",H6*J6,H6)</f>
         <v/>
       </c>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="15">
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="31">
         <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
         <v/>
       </c>
@@ -2724,41 +4636,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="30" t="n">
         <v>1000</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="30" t="n">
         <v>2500</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="31">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="31">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="J7" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="31">
         <f>IF(I7="Oui",G7*J7,G7)</f>
         <v/>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="31">
         <f>IF(I7="Oui",H7*J7,H7)</f>
         <v/>
       </c>
-      <c r="M7" s="17" t="n"/>
-      <c r="N7" s="15">
+      <c r="M7" s="33" t="n"/>
+      <c r="N7" s="31">
         <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
         <v/>
       </c>
@@ -2780,41 +4692,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="29" t="n">
         <v>72</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="30" t="n">
         <v>180</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="31">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="31">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="31">
         <f>IF(I8="Oui",G8*J8,G8)</f>
         <v/>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="31">
         <f>IF(I8="Oui",H8*J8,H8)</f>
         <v/>
       </c>
-      <c r="M8" s="17" t="n"/>
-      <c r="N8" s="15">
+      <c r="M8" s="33" t="n"/>
+      <c r="N8" s="31">
         <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
         <v/>
       </c>
@@ -2825,25 +4737,25 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Menuiseries extérieures</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="28" t="n"/>
+      <c r="O9" s="28" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
@@ -2857,41 +4769,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="30" t="n">
         <v>12000</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="30" t="n">
         <v>25000</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="31">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="31">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J10" s="16" t="n">
+      <c r="J10" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="31">
         <f>IF(I10="Oui",G10*J10,G10)</f>
         <v/>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="31">
         <f>IF(I10="Oui",H10*J10,H10)</f>
         <v/>
       </c>
-      <c r="M10" s="17" t="n"/>
-      <c r="N10" s="15">
+      <c r="M10" s="33" t="n"/>
+      <c r="N10" s="31">
         <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
         <v/>
       </c>
@@ -2913,66 +4825,66 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="30" t="n">
         <v>800</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="31">
         <f>D11*E11</f>
         <v/>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="31">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J11" s="16" t="n">
+      <c r="J11" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="31">
         <f>IF(I11="Oui",G11*J11,G11)</f>
         <v/>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="31">
         <f>IF(I11="Oui",H11*J11,H11)</f>
         <v/>
       </c>
-      <c r="M11" s="17" t="n"/>
-      <c r="N11" s="15">
+      <c r="M11" s="33" t="n"/>
+      <c r="N11" s="31">
         <f>IF(N(M11)&gt;0,M11,(G11+H11)/2)</f>
         <v/>
       </c>
       <c r="O11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Isolation / doublage / plafond</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="28" t="n"/>
+      <c r="N12" s="28" t="n"/>
+      <c r="O12" s="28" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -2986,41 +4898,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="29" t="n">
         <v>79</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="30" t="n">
         <v>130</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="31">
         <f>D13*E13</f>
         <v/>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="31">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="31">
         <f>IF(I13="Oui",G13*J13,G13)</f>
         <v/>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="31">
         <f>IF(I13="Oui",H13*J13,H13)</f>
         <v/>
       </c>
-      <c r="M13" s="17" t="n"/>
-      <c r="N13" s="15">
+      <c r="M13" s="33" t="n"/>
+      <c r="N13" s="31">
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
@@ -3042,41 +4954,41 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="30" t="n">
         <v>150</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="31">
         <f>D14*E14</f>
         <v/>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="31">
         <f>D14*F14</f>
         <v/>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J14" s="16" t="n">
+      <c r="J14" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="31">
         <f>IF(I14="Oui",G14*J14,G14)</f>
         <v/>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="31">
         <f>IF(I14="Oui",H14*J14,H14)</f>
         <v/>
       </c>
-      <c r="M14" s="17" t="n"/>
-      <c r="N14" s="15">
+      <c r="M14" s="33" t="n"/>
+      <c r="N14" s="31">
         <f>IF(N(M14)&gt;0,M14,(G14+H14)/2)</f>
         <v/>
       </c>
@@ -3098,41 +5010,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="29" t="n">
         <v>72</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="31">
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="31">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J15" s="16" t="n">
+      <c r="J15" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="31">
         <f>IF(I15="Oui",G15*J15,G15)</f>
         <v/>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="31">
         <f>IF(I15="Oui",H15*J15,H15)</f>
         <v/>
       </c>
-      <c r="M15" s="17" t="n"/>
-      <c r="N15" s="15">
+      <c r="M15" s="33" t="n"/>
+      <c r="N15" s="31">
         <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
         <v/>
       </c>
@@ -3143,25 +5055,25 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Électricité / chauffage</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="12" t="n"/>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="28" t="n"/>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="28" t="n"/>
+      <c r="M16" s="28" t="n"/>
+      <c r="N16" s="28" t="n"/>
+      <c r="O16" s="28" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -3175,41 +5087,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="29" t="n">
         <v>72</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="30" t="n">
         <v>110</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="31">
         <f>D17*E17</f>
         <v/>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="31">
         <f>D17*F17</f>
         <v/>
       </c>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J17" s="16" t="n">
+      <c r="J17" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="31">
         <f>IF(I17="Oui",G17*J17,G17)</f>
         <v/>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="31">
         <f>IF(I17="Oui",H17*J17,H17)</f>
         <v/>
       </c>
-      <c r="M17" s="17" t="n"/>
-      <c r="N17" s="15">
+      <c r="M17" s="33" t="n"/>
+      <c r="N17" s="31">
         <f>IF(N(M17)&gt;0,M17,(G17+H17)/2)</f>
         <v/>
       </c>
@@ -3227,41 +5139,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="30" t="n">
         <v>4000</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="30" t="n">
         <v>12000</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="31">
         <f>D18*E18</f>
         <v/>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="31">
         <f>D18*F18</f>
         <v/>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J18" s="16" t="n">
+      <c r="J18" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K18" s="15">
+      <c r="K18" s="31">
         <f>IF(I18="Oui",G18*J18,G18)</f>
         <v/>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="31">
         <f>IF(I18="Oui",H18*J18,H18)</f>
         <v/>
       </c>
-      <c r="M18" s="17" t="n"/>
-      <c r="N18" s="15">
+      <c r="M18" s="33" t="n"/>
+      <c r="N18" s="31">
         <f>IF(N(M18)&gt;0,M18,(G18+H18)/2)</f>
         <v/>
       </c>
@@ -3272,25 +5184,25 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Revêtements / finitions</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
-      <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
-      <c r="N19" s="12" t="n"/>
-      <c r="O19" s="12" t="n"/>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="28" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="28" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="28" t="n"/>
+      <c r="I19" s="28" t="n"/>
+      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="28" t="n"/>
+      <c r="L19" s="28" t="n"/>
+      <c r="M19" s="28" t="n"/>
+      <c r="N19" s="28" t="n"/>
+      <c r="O19" s="28" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -3304,41 +5216,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="29" t="n">
         <v>72</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="30" t="n">
         <v>110</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="31">
         <f>D20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="31">
         <f>D20*F20</f>
         <v/>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I20" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J20" s="16" t="n">
+      <c r="J20" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="31">
         <f>IF(I20="Oui",G20*J20,G20)</f>
         <v/>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="31">
         <f>IF(I20="Oui",H20*J20,H20)</f>
         <v/>
       </c>
-      <c r="M20" s="17" t="n"/>
-      <c r="N20" s="15">
+      <c r="M20" s="33" t="n"/>
+      <c r="N20" s="31">
         <f>IF(N(M20)&gt;0,M20,(G20+H20)/2)</f>
         <v/>
       </c>
@@ -3356,41 +5268,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="29" t="n">
         <v>150</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="31">
         <f>D21*E21</f>
         <v/>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="31">
         <f>D21*F21</f>
         <v/>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I21" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J21" s="16" t="n">
+      <c r="J21" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="K21" s="15">
+      <c r="K21" s="31">
         <f>IF(I21="Oui",G21*J21,G21)</f>
         <v/>
       </c>
-      <c r="L21" s="15">
+      <c r="L21" s="31">
         <f>IF(I21="Oui",H21*J21,H21)</f>
         <v/>
       </c>
-      <c r="M21" s="17" t="n"/>
-      <c r="N21" s="15">
+      <c r="M21" s="33" t="n"/>
+      <c r="N21" s="31">
         <f>IF(N(M21)&gt;0,M21,(G21+H21)/2)</f>
         <v/>
       </c>
@@ -3412,41 +5324,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="30" t="n">
         <v>1500</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="31">
         <f>D22*E22</f>
         <v/>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="31">
         <f>D22*F22</f>
         <v/>
       </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I22" s="29" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J22" s="16" t="n">
+      <c r="J22" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="31">
         <f>IF(I22="Oui",G22*J22,G22)</f>
         <v/>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="31">
         <f>IF(I22="Oui",H22*J22,H22)</f>
         <v/>
       </c>
-      <c r="M22" s="17" t="n"/>
-      <c r="N22" s="15">
+      <c r="M22" s="33" t="n"/>
+      <c r="N22" s="31">
         <f>IF(N(M22)&gt;0,M22,(G22+H22)/2)</f>
         <v/>
       </c>
@@ -3457,145 +5369,145 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="35">
         <f>SUM(G5:G22)</f>
         <v/>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="35">
         <f>SUM(H5:H22)</f>
         <v/>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="35">
         <f>SUM(K5:K22)</f>
         <v/>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="35">
         <f>SUM(L5:L22)</f>
         <v/>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="35">
         <f>SUM(N5:N22)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>Imprévus</t>
         </is>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="37">
         <f>G24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="37">
         <f>H24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="K25" s="21">
+      <c r="K25" s="37">
         <f>K24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="L25" s="21">
+      <c r="L25" s="37">
         <f>L24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="N25" s="21">
+      <c r="N25" s="37">
         <f>N24*Paramètres!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre</t>
         </is>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="37">
         <f>G24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="H26" s="21">
+      <c r="H26" s="37">
         <f>H24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="K26" s="21">
+      <c r="K26" s="37">
         <f>K24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="L26" s="21">
+      <c r="L26" s="37">
         <f>L24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="N26" s="21">
+      <c r="N26" s="37">
         <f>N24*Paramètres!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="n"/>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="A27" s="38" t="n"/>
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>TOTAL RDC TTC</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="24">
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="40">
         <f>G24+G25+G26</f>
         <v/>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="40">
         <f>H24+H25+H26</f>
         <v/>
       </c>
-      <c r="I27" s="22" t="n"/>
-      <c r="J27" s="22" t="n"/>
-      <c r="K27" s="24">
+      <c r="I27" s="38" t="n"/>
+      <c r="J27" s="38" t="n"/>
+      <c r="K27" s="40">
         <f>K24+K25+K26</f>
         <v/>
       </c>
-      <c r="L27" s="24">
+      <c r="L27" s="40">
         <f>L24+L25+L26</f>
         <v/>
       </c>
-      <c r="M27" s="22" t="n"/>
-      <c r="N27" s="24">
+      <c r="M27" s="38" t="n"/>
+      <c r="N27" s="40">
         <f>N24+N25+N26</f>
         <v/>
       </c>
-      <c r="O27" s="22" t="n"/>
+      <c r="O27" s="38" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>Soit par m² (77 m²)</t>
         </is>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="41">
         <f>G27/77</f>
         <v/>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="41">
         <f>H27/77</f>
         <v/>
       </c>
-      <c r="K28" s="25">
+      <c r="K28" s="41">
         <f>K27/77</f>
         <v/>
       </c>
-      <c r="L28" s="25">
+      <c r="L28" s="41">
         <f>L27/77</f>
         <v/>
       </c>
-      <c r="N28" s="25">
+      <c r="N28" s="41">
         <f>N27/77</f>
         <v/>
       </c>
@@ -3632,7 +5544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3750,25 +5662,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Couverture (260 m²)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n"/>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="12" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
+      <c r="G5" s="28" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
+      <c r="J5" s="28" t="n"/>
+      <c r="K5" s="28" t="n"/>
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -3782,41 +5694,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="29" t="n">
         <v>260</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="31">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="31">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
+      <c r="J6" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="31">
         <f>IF(I6="Oui",G6*J6,G6)</f>
         <v/>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="31">
         <f>IF(I6="Oui",H6*J6,H6)</f>
         <v/>
       </c>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="15">
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="31">
         <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
         <v/>
       </c>
@@ -3834,41 +5746,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="29" t="n">
         <v>260</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="31">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="31">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="J7" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="31">
         <f>IF(I7="Oui",G7*J7,G7)</f>
         <v/>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="31">
         <f>IF(I7="Oui",H7*J7,H7)</f>
         <v/>
       </c>
-      <c r="M7" s="17" t="n"/>
-      <c r="N7" s="15">
+      <c r="M7" s="33" t="n"/>
+      <c r="N7" s="31">
         <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
         <v/>
       </c>
@@ -3886,41 +5798,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="29" t="n">
         <v>260</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="31">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="31">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="31">
         <f>IF(I8="Oui",G8*J8,G8)</f>
         <v/>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="31">
         <f>IF(I8="Oui",H8*J8,H8)</f>
         <v/>
       </c>
-      <c r="M8" s="17" t="n"/>
-      <c r="N8" s="15">
+      <c r="M8" s="33" t="n"/>
+      <c r="N8" s="31">
         <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
         <v/>
       </c>
@@ -3942,41 +5854,41 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="31">
         <f>D9*E9</f>
         <v/>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="31">
         <f>D9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J9" s="16" t="n">
+      <c r="J9" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="31">
         <f>IF(I9="Oui",G9*J9,G9)</f>
         <v/>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="31">
         <f>IF(I9="Oui",H9*J9,H9)</f>
         <v/>
       </c>
-      <c r="M9" s="17" t="n"/>
-      <c r="N9" s="15">
+      <c r="M9" s="33" t="n"/>
+      <c r="N9" s="31">
         <f>IF(N(M9)&gt;0,M9,(G9+H9)/2)</f>
         <v/>
       </c>
@@ -3998,41 +5910,41 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="31">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="31">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J10" s="16" t="n">
+      <c r="J10" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="31">
         <f>IF(I10="Oui",G10*J10,G10)</f>
         <v/>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="31">
         <f>IF(I10="Oui",H10*J10,H10)</f>
         <v/>
       </c>
-      <c r="M10" s="17" t="n"/>
-      <c r="N10" s="15">
+      <c r="M10" s="33" t="n"/>
+      <c r="N10" s="31">
         <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
         <v/>
       </c>
@@ -4043,25 +5955,25 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Façades (maison + grange)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
-      <c r="O11" s="12" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="28" t="n"/>
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="28" t="n"/>
+      <c r="N11" s="28" t="n"/>
+      <c r="O11" s="28" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
@@ -4075,41 +5987,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="29" t="n">
         <v>400</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="30" t="n">
         <v>120</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="31">
         <f>D12*E12</f>
         <v/>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="31">
         <f>D12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J12" s="16" t="n">
+      <c r="J12" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="31">
         <f>IF(I12="Oui",G12*J12,G12)</f>
         <v/>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="31">
         <f>IF(I12="Oui",H12*J12,H12)</f>
         <v/>
       </c>
-      <c r="M12" s="17" t="n"/>
-      <c r="N12" s="15">
+      <c r="M12" s="33" t="n"/>
+      <c r="N12" s="31">
         <f>IF(N(M12)&gt;0,M12,(G12+H12)/2)</f>
         <v/>
       </c>
@@ -4131,66 +6043,66 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="30" t="n">
         <v>6000</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="31">
         <f>D13*E13</f>
         <v/>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="31">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="31">
         <f>IF(I13="Oui",G13*J13,G13)</f>
         <v/>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="31">
         <f>IF(I13="Oui",H13*J13,H13)</f>
         <v/>
       </c>
-      <c r="M13" s="17" t="n"/>
-      <c r="N13" s="15">
+      <c r="M13" s="33" t="n"/>
+      <c r="N13" s="31">
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
       <c r="O13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Charpente / sécurité</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="12" t="n"/>
-      <c r="O14" s="12" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="28" t="n"/>
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="28" t="n"/>
+      <c r="M14" s="28" t="n"/>
+      <c r="N14" s="28" t="n"/>
+      <c r="O14" s="28" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -4204,41 +6116,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="30" t="n">
         <v>2000</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="31">
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="31">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J15" s="16" t="n">
+      <c r="J15" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="31">
         <f>IF(I15="Oui",G15*J15,G15)</f>
         <v/>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="31">
         <f>IF(I15="Oui",H15*J15,H15)</f>
         <v/>
       </c>
-      <c r="M15" s="17" t="n"/>
-      <c r="N15" s="15">
+      <c r="M15" s="33" t="n"/>
+      <c r="N15" s="31">
         <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
         <v/>
       </c>
@@ -4260,41 +6172,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="30" t="n">
         <v>4000</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="31">
         <f>D16*E16</f>
         <v/>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="31">
         <f>D16*F16</f>
         <v/>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J16" s="16" t="n">
+      <c r="J16" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="31">
         <f>IF(I16="Oui",G16*J16,G16)</f>
         <v/>
       </c>
-      <c r="L16" s="15">
+      <c r="L16" s="31">
         <f>IF(I16="Oui",H16*J16,H16)</f>
         <v/>
       </c>
-      <c r="M16" s="17" t="n"/>
-      <c r="N16" s="15">
+      <c r="M16" s="33" t="n"/>
+      <c r="N16" s="31">
         <f>IF(N(M16)&gt;0,M16,(G16+H16)/2)</f>
         <v/>
       </c>
@@ -4305,145 +6217,145 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="35">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="35">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="35">
         <f>SUM(K5:K16)</f>
         <v/>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="35">
         <f>SUM(L5:L16)</f>
         <v/>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="35">
         <f>SUM(N5:N16)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Imprévus</t>
         </is>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="37">
         <f>G18*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="H19" s="21">
+      <c r="H19" s="37">
         <f>H18*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="K19" s="21">
+      <c r="K19" s="37">
         <f>K18*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="L19" s="21">
+      <c r="L19" s="37">
         <f>L18*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="N19" s="21">
+      <c r="N19" s="37">
         <f>N18*Paramètres!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre</t>
         </is>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="37">
         <f>G18*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="37">
         <f>H18*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="K20" s="21">
+      <c r="K20" s="37">
         <f>K18*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="L20" s="21">
+      <c r="L20" s="37">
         <f>L18*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="N20" s="21">
+      <c r="N20" s="37">
         <f>N18*Paramètres!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n"/>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="A21" s="38" t="n"/>
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>TOTAL TOITURE + FAÇADES TTC (sans sarking)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="24">
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="38" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="40">
         <f>G18+G19+G20</f>
         <v/>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="40">
         <f>H18+H19+H20</f>
         <v/>
       </c>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
-      <c r="K21" s="24">
+      <c r="I21" s="38" t="n"/>
+      <c r="J21" s="38" t="n"/>
+      <c r="K21" s="40">
         <f>K18+K19+K20</f>
         <v/>
       </c>
-      <c r="L21" s="24">
+      <c r="L21" s="40">
         <f>L18+L19+L20</f>
         <v/>
       </c>
-      <c r="M21" s="22" t="n"/>
-      <c r="N21" s="24">
+      <c r="M21" s="38" t="n"/>
+      <c r="N21" s="40">
         <f>N18+N19+N20</f>
         <v/>
       </c>
-      <c r="O21" s="22" t="n"/>
+      <c r="O21" s="38" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>Soit par m² (260 m²)</t>
         </is>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="41">
         <f>G21/260</f>
         <v/>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="41">
         <f>H21/260</f>
         <v/>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="41">
         <f>K21/260</f>
         <v/>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="41">
         <f>L21/260</f>
         <v/>
       </c>
-      <c r="N22" s="25">
+      <c r="N22" s="41">
         <f>N21/260</f>
         <v/>
       </c>
@@ -4470,29 +6382,29 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>OPTION SARKING</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="42" t="inlineStr">
         <is>
           <t>Isolation posée par l'extérieur pendant la réfection (remplace l'isolation intérieure des rampants de l'étage)</t>
         </is>
       </c>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
-      <c r="H28" s="27" t="n"/>
-      <c r="I28" s="27" t="n"/>
-      <c r="J28" s="27" t="n"/>
-      <c r="K28" s="27" t="n"/>
-      <c r="L28" s="27" t="n"/>
-      <c r="M28" s="27" t="n"/>
-      <c r="N28" s="27" t="n"/>
-      <c r="O28" s="27" t="n"/>
+      <c r="C28" s="43" t="n"/>
+      <c r="D28" s="43" t="n"/>
+      <c r="E28" s="43" t="n"/>
+      <c r="F28" s="43" t="n"/>
+      <c r="G28" s="43" t="n"/>
+      <c r="H28" s="43" t="n"/>
+      <c r="I28" s="43" t="n"/>
+      <c r="J28" s="43" t="n"/>
+      <c r="K28" s="43" t="n"/>
+      <c r="L28" s="43" t="n"/>
+      <c r="M28" s="43" t="n"/>
+      <c r="N28" s="43" t="n"/>
+      <c r="O28" s="43" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -4506,41 +6418,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="29" t="n">
         <v>260</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="30" t="n">
         <v>150</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="31">
         <f>D29*E29</f>
         <v/>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="31">
         <f>D29*F29</f>
         <v/>
       </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="I29" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="J29" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="K29" s="15">
+      <c r="K29" s="31">
         <f>IF(I29="Oui",G29*J29,G29)</f>
         <v/>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="31">
         <f>IF(I29="Oui",H29*J29,H29)</f>
         <v/>
       </c>
-      <c r="M29" s="17" t="n"/>
-      <c r="N29" s="15">
+      <c r="M29" s="33" t="n"/>
+      <c r="N29" s="31">
         <f>IF(N(M29)&gt;0,M29,(G29+H29)/2)</f>
         <v/>
       </c>
@@ -4562,135 +6474,135 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="30" t="n">
         <v>1500</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F30" s="30" t="n">
         <v>4000</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="31">
         <f>D30*E30</f>
         <v/>
       </c>
-      <c r="H30" s="15">
+      <c r="H30" s="31">
         <f>D30*F30</f>
         <v/>
       </c>
-      <c r="I30" s="13" t="inlineStr">
+      <c r="I30" s="29" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J30" s="16" t="n">
+      <c r="J30" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="K30" s="15">
+      <c r="K30" s="31">
         <f>IF(I30="Oui",G30*J30,G30)</f>
         <v/>
       </c>
-      <c r="L30" s="15">
+      <c r="L30" s="31">
         <f>IF(I30="Oui",H30*J30,H30)</f>
         <v/>
       </c>
-      <c r="M30" s="17" t="n"/>
-      <c r="N30" s="15">
+      <c r="M30" s="33" t="n"/>
+      <c r="N30" s="31">
         <f>IF(N(M30)&gt;0,M30,(G30+H30)/2)</f>
         <v/>
       </c>
       <c r="O30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>Sous-total option sarking</t>
         </is>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="35">
         <f>SUM(G29:G30)</f>
         <v/>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="35">
         <f>SUM(H29:H30)</f>
         <v/>
       </c>
-      <c r="K31" s="19">
+      <c r="K31" s="35">
         <f>SUM(K29:K30)</f>
         <v/>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="35">
         <f>SUM(L29:L30)</f>
         <v/>
       </c>
-      <c r="N31" s="19">
+      <c r="N31" s="35">
         <f>SUM(N29:N30)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>Économie : isolation intérieure des rampants supprimée (onglet étage)</t>
         </is>
       </c>
-      <c r="G32" s="21">
+      <c r="G32" s="37">
         <f>-'Budget étage'!G10</f>
         <v/>
       </c>
-      <c r="H32" s="21">
+      <c r="H32" s="37">
         <f>-'Budget étage'!H10</f>
         <v/>
       </c>
-      <c r="K32" s="21">
+      <c r="K32" s="37">
         <f>-'Budget étage'!K10</f>
         <v/>
       </c>
-      <c r="L32" s="21">
+      <c r="L32" s="37">
         <f>-'Budget étage'!L10</f>
         <v/>
       </c>
-      <c r="N32" s="21">
+      <c r="N32" s="37">
         <f>-'Budget étage'!N10</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="n"/>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="A33" s="38" t="n"/>
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>SURCOÛT NET OPTION SARKING TTC (imprévus + MOE inclus)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
-      <c r="F33" s="22" t="n"/>
-      <c r="G33" s="24">
+      <c r="C33" s="38" t="n"/>
+      <c r="D33" s="38" t="n"/>
+      <c r="E33" s="38" t="n"/>
+      <c r="F33" s="38" t="n"/>
+      <c r="G33" s="40">
         <f>(G31+G32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="40">
         <f>(H31+H32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="I33" s="22" t="n"/>
-      <c r="J33" s="22" t="n"/>
-      <c r="K33" s="24">
+      <c r="I33" s="38" t="n"/>
+      <c r="J33" s="38" t="n"/>
+      <c r="K33" s="40">
         <f>(K31+K32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="L33" s="24">
+      <c r="L33" s="40">
         <f>(L31+L32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="M33" s="22" t="n"/>
-      <c r="N33" s="24">
+      <c r="M33" s="38" t="n"/>
+      <c r="N33" s="40">
         <f>(N31+N32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="O33" s="22" t="n"/>
+      <c r="O33" s="38" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="10" t="inlineStr">
@@ -4710,7 +6622,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4733,153 +6645,153 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>Paramètre</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>Imprévus (% des travaux)</t>
         </is>
       </c>
-      <c r="B4" s="28" t="n">
+      <c r="B4" s="44" t="n">
         <v>0.1</v>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>Usuel en rénovation de bâti ancien : 10 à 15 %.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre / architecte (% des travaux)</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>0 % si vous pilotez vous-même ; 8 à 12 % avec un maître d'œuvre.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="45" t="inlineStr">
         <is>
           <t>TVA : prix affichés TTC à 20 % (création de surface habitable dans une grange : taux réduit en principe non applicable).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Postes HORS budget étage (à chiffrer séparément)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>Min €</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="42" t="inlineStr">
         <is>
           <t>Max €</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Raccordements eau / électricité / assainissement individuel</t>
         </is>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="46" t="n">
         <v>8000</v>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="46" t="n">
         <v>15000</v>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>Selon raccordement existant de la grange.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Renfort du plancher / chape</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="46" t="n">
         <v>5000</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="46" t="n">
         <v>12000</v>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>Si le plancher de l'étage est insuffisant.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Taxe d'aménagement + dossier changement de destination</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n">
+      <c r="B13" s="46" t="n">
         <v>2000</v>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="46" t="n">
         <v>5000</v>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Selon taux communal et départemental.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Total hors budget</t>
         </is>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="35">
         <f>SUM(B11:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="35">
         <f>SUM(C11:C13)</f>
         <v/>
       </c>

--- a/la-marinka/La Marinka.xlsx
+++ b/la-marinka/La Marinka.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -157,6 +157,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -842,11 +845,11 @@
         </is>
       </c>
       <c r="B11" s="4">
-        <f>Paramètres!B14</f>
+        <f>Paramètres!B17</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>Paramètres!C14</f>
+        <f>Paramètres!C17</f>
         <v/>
       </c>
       <c r="D11" s="8" t="n"/>
@@ -907,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -982,11 +985,11 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>1700</v>
+        <v>1987</v>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Norme haute du secteur rural.</t>
+          <t>Cadastre B1861+1860 = 1 487 m² d'un seul tenant autour de la maison ; B1160+1163 = 500 m² détachés de l'autre côté de l'impasse (servitude d'écoulement).</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1026,7 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Grange indépendante : surface utile (m²)</t>
+          <t>Grange attenante, partie non aménagée : surface utile (m²)</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
@@ -1031,128 +1034,128 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>≈ 300 m² au sol + 200 m² en R+1, toiture neuve, dalle béton. Non habitable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+          <t>≈ 300 m² au sol + 200 m² à l'étage (écuries, granges, combles). Sol terre battue, plafonds paille ; 70 m² de toiture refaits en 2024 seulement. Non habitable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>DPE maison existante</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>E (258 kWh/m².an) — GES B</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Diagnostic 09/2025 ; audit 2023 : G avant isolation des combles et poêle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>2. Prix du marché local (maisons)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Commune</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>€/m² maison</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Nature de la donnée</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Sainte-Anne-sur-Gervonde</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>1 983 (DVF 2025, 6 ventes) à 2 286-2 458</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Ventes réelles / estimations agrégateurs ; tendance 12 mois en baisse</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Châtonnay</t>
+          <t>Sainte-Anne-sur-Gervonde</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2 301-2 362</t>
+          <t>1 983 (DVF 2025, 6 ventes) à 2 286-2 458</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Estimation</t>
+          <t>Ventes réelles / estimations agrégateurs ; tendance 12 mois en baisse</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Saint-Jean-de-Bournay</t>
+          <t>Châtonnay</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>2 223-2 458</t>
+          <t>2 301-2 362</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Estimation ; pic 2 589 en 2022 puis repli</t>
+          <t>Estimation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Meyrieu-les-Étangs</t>
+          <t>Saint-Jean-de-Bournay</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>2 321</t>
+          <t>2 223-2 458</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Estimation ; -12,6 % sur un an</t>
+          <t>Estimation ; pic 2 589 en 2022 puis repli</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Villeneuve-de-Marc</t>
+          <t>Meyrieu-les-Étangs</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>2 333</t>
+          <t>2 321</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Estimation</t>
+          <t>Estimation ; -12,6 % sur un an</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Savas-Mépin</t>
+          <t>Villeneuve-de-Marc</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>2 504</t>
+          <t>2 333</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -1164,12 +1167,12 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Artas</t>
+          <t>Savas-Mépin</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>2 742</t>
+          <t>2 504</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -1181,141 +1184,110 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Beauvoir-de-Marc</t>
+          <t>Artas</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>2 952</t>
+          <t>2 742</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Estimation ; commune plus proche de Lyon</t>
+          <t>Estimation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
+          <t>Beauvoir-de-Marc</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>2 952</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Estimation ; commune plus proche de Lyon</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
           <t>Grandes maisons vendues à Saint-Jean-de-Bournay (202-235 m²)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>1 213-1 906</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Ventes réelles : forte décote au m² des grandes surfaces</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>3. Biens comparables</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Commune</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Habitable</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Terrain</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Dépendances</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Piscine</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>État</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Prix €</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>€/m²</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Comparabilité</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Saint-Jean-de-Bournay</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>293 m², 6 ch.</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>4 800 m²</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>Bon (présumé)</t>
-        </is>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
-        <is>
-          <t>Affiché</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>580000</v>
-      </c>
-      <c r="I26" s="16" t="n">
-        <v>1980</v>
-      </c>
-      <c r="J26" s="12" t="inlineStr">
-        <is>
-          <t>Élevée : plafond affiché du secteur</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1299,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>169 m², 6 ch.</t>
+          <t>293 m², 6 ch.</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>2 513 m²</t>
+          <t>4 800 m²</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1347,7 +1319,7 @@
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Bon (présumé)</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -1355,47 +1327,47 @@
           <t>Affiché</t>
         </is>
       </c>
-      <c r="H27" s="15" t="n">
-        <v>383000</v>
-      </c>
-      <c r="I27" s="16" t="n">
-        <v>2266</v>
+      <c r="H27" s="16" t="n">
+        <v>580000</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>1980</v>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>Moyenne (plus petit)</t>
+          <t>Élevée : plafond affiché du secteur</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Beauvoir-de-Marc</t>
+          <t>Saint-Jean-de-Bournay</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
+          <t>169 m², 6 ch.</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>2 513 m²</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>1 514 m²</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Oui (creusée)</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -1403,126 +1375,126 @@
           <t>Affiché</t>
         </is>
       </c>
-      <c r="H28" s="15" t="n">
-        <v>502000</v>
-      </c>
-      <c r="I28" s="16" t="n"/>
+      <c r="H28" s="16" t="n">
+        <v>383000</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>2266</v>
+      </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>Moyenne (commune plus chère)</t>
+          <t>Moyenne (plus petit)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Collines dauphinoises (Safer)</t>
+          <t>Beauvoir-de-Marc</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>≈ 250 m², pisé</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>1,9 ha</t>
+          <t>1 514 m²</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Bâtiment agricole pisé aménagé</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
+          <t>Oui (creusée)</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>Rénové</t>
-        </is>
-      </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Affiché HFS</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>570000</v>
-      </c>
-      <c r="I29" s="16" t="n">
-        <v>2280</v>
-      </c>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="n">
+        <v>502000</v>
+      </c>
+      <c r="I29" s="17" t="n"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>Moyenne à élevée (pisé + grande dépendance)</t>
+          <t>Moyenne (commune plus chère)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Secteur Vienne (3 min A7)</t>
+          <t>Collines dauphinoises (Safer)</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>220 m², 6 ch.</t>
+          <t>≈ 250 m², pisé</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>1 125 m²</t>
+          <t>1,9 ha</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
+          <t>Bâtiment agricole pisé aménagé</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Pierre, rénové</t>
+          <t>Rénové</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Affiché</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>630000</v>
-      </c>
-      <c r="I30" s="16" t="n">
-        <v>2864</v>
+          <t>Affiché HFS</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="n">
+        <v>570000</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>2280</v>
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>Faible à moyenne (emplacement supérieur)</t>
+          <t>Moyenne à élevée (pisé + grande dépendance)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Châtonnay</t>
+          <t>Secteur Vienne (3 min A7)</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>≈ 300 m²</t>
+          <t>220 m², 6 ch.</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>1 000 m²</t>
+          <t>1 125 m²</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1537,7 +1509,7 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Tout à rénover</t>
+          <t>Pierre, rénové</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -1545,85 +1517,85 @@
           <t>Affiché</t>
         </is>
       </c>
-      <c r="H31" s="15" t="n">
-        <v>275000</v>
-      </c>
-      <c r="I31" s="16" t="n">
-        <v>917</v>
+      <c r="H31" s="16" t="n">
+        <v>630000</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>2864</v>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>Faible (illustre la décote travaux)</t>
+          <t>Faible à moyenne (emplacement supérieur)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Saint-Jean-de-Bournay</t>
+          <t>Châtonnay</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>202 m²</t>
+          <t>≈ 300 m²</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
+          <t>1 000 m²</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>Tout à rénover</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Vendu</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>385000</v>
-      </c>
-      <c r="I32" s="16" t="n">
-        <v>1906</v>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="n">
+        <v>275000</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>917</v>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Moyenne (vente réelle)</t>
+          <t>Faible (illustre la décote travaux)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Lieudieu</t>
+          <t>Saint-Jean-de-Bournay</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>300 m², 6 ch.</t>
+          <t>202 m²</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>9 702 m²</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Domaine</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
@@ -1633,55 +1605,55 @@
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Exception</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Affiché</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="I33" s="16" t="n">
-        <v>4300</v>
+          <t>Vendu</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="n">
+        <v>385000</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>1906</v>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>Très faible (hors norme)</t>
+          <t>Moyenne (vente réelle)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Satolas (Nord-Isère) — dépendance seule</t>
+          <t>Lieudieu</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300 m², 6 ch.</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9 702 m²</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Hangars 2 680 m²</t>
+          <t>Domaine</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Exception</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -1689,466 +1661,464 @@
           <t>Affiché</t>
         </is>
       </c>
-      <c r="H34" s="15" t="n">
-        <v>230000</v>
-      </c>
-      <c r="I34" s="16" t="n">
-        <v>86</v>
+      <c r="H34" s="16" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>4300</v>
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>Référence grange</t>
+          <t>Très faible (hors norme)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
+          <t>Satolas (Nord-Isère) — dépendance seule</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Hangars 2 680 m²</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Affiché</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>230000</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>86</v>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>Référence grange</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
           <t>Isère — dépendance seule</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>Grange 727 m²</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>Affiché</t>
         </is>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H36" s="16" t="n">
         <v>120000</v>
       </c>
-      <c r="I35" s="16" t="n">
+      <c r="I36" s="17" t="n">
         <v>165</v>
       </c>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>Référence grange</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Aucune vente réelle documentée &gt; 500 000 € dans la commune ni dans les communes limitrophes.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Points relevés dans la promesse de vente (10/2025) : mitoyenneté avec la parcelle voisine dont le propriétaire envisage une démolition ; servitude d'eau (bélier hydraulique) ; absence de puits déclaré ; sismicité 3/5 ; commune en zone inondation (CatNat 1982-1993).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>4. Construction de la valeur (approche par composantes)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Composante</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Bas €</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Central €</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Haut €</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Justification</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Maison rénovée ≈ 230 m² (hors extérieurs)</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="n">
-        <v>450000</v>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>485000</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>530000</v>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>2 050-2 350 €/m² : grande maison de caractère rénovée, décote des grandes surfaces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>Piscine enterrée 3 × 5 m</t>
-        </is>
-      </c>
-      <c r="B41" s="14" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>Atout réel mais perçu aussi comme une charge d'entretien.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Pergola bioclimatique + espace repas</t>
+          <t>Maison rénovée ≈ 230 m² (hors extérieurs)</t>
         </is>
       </c>
       <c r="B42" s="14" t="n">
-        <v>5000</v>
+        <v>450000</v>
       </c>
       <c r="C42" s="14" t="n">
-        <v>7500</v>
+        <v>485000</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E42" s="12" t="inlineStr"/>
+        <v>530000</v>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>2 050-2 350 €/m² : grande maison de caractère rénovée, décote des grandes surfaces.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Jacuzzi, pétanque, brasero, barbecue</t>
+          <t>Piscine enterrée 3 × 5 m</t>
         </is>
       </c>
       <c r="B43" s="14" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="C43" s="14" t="n">
-        <v>2500</v>
+        <v>20000</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Équipements, pas de valeur foncière.</t>
+          <t>Atout réel mais perçu aussi comme une charge d'entretien.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Calme absolu (impasse de 3 maisons)</t>
+          <t>Pergola bioclimatique + espace repas</t>
         </is>
       </c>
       <c r="B44" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>7500</v>
+      </c>
+      <c r="D44" s="14" t="n">
         <v>10000</v>
       </c>
-      <c r="C44" s="14" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>Prime réelle mais fréquente en secteur rural.</t>
-        </is>
-      </c>
+      <c r="E44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Puits fonctionnel + irrigation du jardin</t>
+          <t>Jacuzzi, pétanque, brasero, barbecue</t>
         </is>
       </c>
       <c r="B45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D45" s="14" t="n">
         <v>5000</v>
       </c>
-      <c r="C45" s="14" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>10000</v>
-      </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Utile sur 1 700 m² ; usage limitable par arrêtés sécheresse.</t>
+          <t>Équipements, pas de valeur foncière.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Façades neuves (enduit chaux)</t>
+          <t>Calme absolu (impasse de 3 maisons)</t>
         </is>
       </c>
       <c r="B46" s="14" t="n">
         <v>10000</v>
       </c>
       <c r="C46" s="14" t="n">
-        <v>12500</v>
+        <v>15000</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Évite la décote « ravalement à prévoir ».</t>
+          <t>Prime réelle mais fréquente en secteur rural.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Grange indépendante ≈ 500 m² utiles</t>
+          <t>Puits fonctionnel + irrigation du jardin</t>
         </is>
       </c>
       <c r="B47" s="14" t="n">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="C47" s="14" t="n">
-        <v>65000</v>
+        <v>7500</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>80-200 €/m² utile ; acheteurs ciblés (collectionneur, artisan).</t>
+          <t>Utile sur 1 700 m² ; usage limitable par arrêtés sécheresse.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Ajustement plafond de marché local / délai</t>
+          <t>Façades neuves (enduit chaux)</t>
         </is>
       </c>
       <c r="B48" s="14" t="n">
-        <v>-25000</v>
+        <v>10000</v>
       </c>
       <c r="C48" s="14" t="n">
-        <v>-30000</v>
+        <v>12500</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>-66000</v>
+        <v>15000</v>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Bien au sommet du marché local : peu d'acheteurs, négociation 5-10 %.</t>
+          <t>Évite la décote « ravalement à prévoir ».</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>VALEUR ESTIMÉE</t>
-        </is>
-      </c>
-      <c r="B49" s="18">
-        <f>SUM(B40:B48)</f>
-        <v/>
-      </c>
-      <c r="C49" s="18">
-        <f>SUM(C40:C48)</f>
-        <v/>
-      </c>
-      <c r="D49" s="18">
-        <f>SUM(D40:D48)</f>
-        <v/>
-      </c>
-      <c r="E49" s="19" t="inlineStr">
-        <is>
-          <t>Bas ≈ vente rapide ; central = valeur retenue ; haut = annonce ambitieuse.</t>
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Partie non aménagée de la grange ≈ 500 m² utiles (sol terre, pas de dalle)</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>50-140 €/m² utile en l'état ; +20 à +30 k€ si dalle béton et toiture complète. Acheteurs ciblés.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
+          <t>Ajustement plafond de marché local / délai</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="C50" s="14" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>-66000</v>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>Bien au sommet du marché local : peu d'acheteurs, négociation 5-10 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>VALEUR ESTIMÉE</t>
+        </is>
+      </c>
+      <c r="B51" s="19">
+        <f>SUM(B42:B50)</f>
+        <v/>
+      </c>
+      <c r="C51" s="19">
+        <f>SUM(C42:C50)</f>
+        <v/>
+      </c>
+      <c r="D51" s="19">
+        <f>SUM(D42:D50)</f>
+        <v/>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>Bas ≈ vente rapide ; central = valeur retenue ; haut = annonce ambitieuse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
           <t>Option non comprise : grange identifiée « changement de destination » au PLUi</t>
         </is>
       </c>
-      <c r="B50" s="14" t="n">
+      <c r="B52" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C50" s="14" t="n">
+      <c r="C52" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="14" t="n">
+      <c r="D52" s="14" t="n">
         <v>50000</v>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>À ne compter que si confirmé en mairie (PLUi Région Saint-Jeannaise + avis CDPENAF en zone A).</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>5. Scénarios de vente</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Scénario</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Prix €</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>€/m² habitable</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>€/m² hors grange</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Délai probable</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Commentaire</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>Vente rapide</t>
-        </is>
-      </c>
-      <c r="B54" s="15">
-        <f>B49</f>
-        <v/>
-      </c>
-      <c r="C54" s="20">
-        <f>B54/$B$6</f>
-        <v/>
-      </c>
-      <c r="D54" s="20">
-        <f>(B54-$C$47)/$B$6</f>
-        <v/>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>&lt; 3 mois</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>Valeur de marché réaliste</t>
-        </is>
-      </c>
-      <c r="B55" s="14" t="n">
-        <v>580000</v>
-      </c>
-      <c r="C55" s="20">
-        <f>B55/$B$6</f>
-        <v/>
-      </c>
-      <c r="D55" s="20">
-        <f>(B55-$C$47)/$B$6</f>
-        <v/>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>6 à 9 mois</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>Fourchette réaliste 570-600 k€.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>Annonce ambitieuse mais défendable</t>
-        </is>
-      </c>
-      <c r="B56" s="15">
-        <f>D49</f>
-        <v/>
-      </c>
-      <c r="C56" s="20">
+          <t>Vente rapide</t>
+        </is>
+      </c>
+      <c r="B56" s="16">
+        <f>B51</f>
+        <v/>
+      </c>
+      <c r="C56" s="21">
         <f>B56/$B$6</f>
         <v/>
       </c>
-      <c r="D56" s="20">
-        <f>(B56-$C$47)/$B$6</f>
+      <c r="D56" s="21">
+        <f>(B56-$C$49)/$B$6</f>
         <v/>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>9 à 18 mois</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>Négociation probable vers 590-600 k€.</t>
-        </is>
-      </c>
+          <t>&lt; 3 mois</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>VALEUR CENTRALE RETENUE</t>
-        </is>
-      </c>
-      <c r="B57" s="18">
-        <f>C49</f>
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Valeur de marché réaliste</t>
+        </is>
+      </c>
+      <c r="B57" s="16">
+        <f>C51</f>
         <v/>
       </c>
       <c r="C57" s="21">
@@ -2156,576 +2126,633 @@
         <v/>
       </c>
       <c r="D57" s="21">
-        <f>(B57-$C$47)/$B$6</f>
-        <v/>
-      </c>
-      <c r="E57" s="19" t="inlineStr"/>
-      <c r="F57" s="19" t="inlineStr">
+        <f>(B57-$C$49)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>6 à 9 mois</t>
+        </is>
+      </c>
+      <c r="F57" s="12">
+        <f> valeur centrale ; fourchette ± 15 k€.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Annonce ambitieuse mais défendable</t>
+        </is>
+      </c>
+      <c r="B58" s="16">
+        <f>D51</f>
+        <v/>
+      </c>
+      <c r="C58" s="21">
+        <f>B58/$B$6</f>
+        <v/>
+      </c>
+      <c r="D58" s="21">
+        <f>(B58-$C$49)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>9 à 18 mois</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>Négociation probable vers 590-600 k€.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>VALEUR CENTRALE RETENUE</t>
+        </is>
+      </c>
+      <c r="B59" s="19">
+        <f>C51</f>
+        <v/>
+      </c>
+      <c r="C59" s="22">
+        <f>B59/$B$6</f>
+        <v/>
+      </c>
+      <c r="D59" s="22">
+        <f>(B59-$C$49)/$B$6</f>
+        <v/>
+      </c>
+      <c r="E59" s="20" t="inlineStr"/>
+      <c r="F59" s="20" t="inlineStr">
         <is>
           <t>Maison ≈ 515 k€ + calme / puits / façades + grange ≈ 65 k€, après plafond de marché.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>6. Ces prix sont-ils réalistes ?</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Prix</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>€/m² habitable</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Pourquoi</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="14" t="n">
-        <v>600000</v>
-      </c>
-      <c r="B61" s="20">
-        <f>A61/$B$6</f>
-        <v/>
-      </c>
-      <c r="C61" s="22" t="inlineStr">
-        <is>
-          <t>Objectif haut atteignable</t>
-        </is>
-      </c>
-      <c r="D61" s="12" t="inlineStr">
-        <is>
-          <t>Exécution parfaite + acheteur qui valorise la grange ; haut de la fourchette, pas le cas de base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="n">
-        <v>650000</v>
-      </c>
-      <c r="B62" s="20">
-        <f>A62/$B$6</f>
-        <v/>
-      </c>
-      <c r="C62" s="22" t="inlineStr">
-        <is>
-          <t>Prix d'annonce, pas de vente</t>
-        </is>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>Au-dessus de tout ce qui s'affiche localement hors cas d'exception.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n">
+        <v>600000</v>
+      </c>
+      <c r="B63" s="21">
+        <f>A63/$B$6</f>
+        <v/>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>Objectif haut atteignable</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Exécution parfaite + acheteur qui valorise la grange ; haut de la fourchette, pas le cas de base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="n">
+        <v>650000</v>
+      </c>
+      <c r="B64" s="21">
+        <f>A64/$B$6</f>
+        <v/>
+      </c>
+      <c r="C64" s="23" t="inlineStr">
+        <is>
+          <t>Prix d'annonce, pas de vente</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>Au-dessus de tout ce qui s'affiche localement hors cas d'exception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="n">
         <v>700000</v>
       </c>
-      <c r="B63" s="20">
-        <f>A63/$B$6</f>
-        <v/>
-      </c>
-      <c r="C63" s="22" t="inlineStr">
+      <c r="B65" s="21">
+        <f>A65/$B$6</f>
+        <v/>
+      </c>
+      <c r="C65" s="23" t="inlineStr">
         <is>
           <t>Irréaliste aujourd'hui</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>≈ 3 000 €/m², &gt; 50 % au-dessus des ventes réelles de la commune ; aucun comparable.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>7. Coût total du projet face à la valeur</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Élément</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Montant €</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Prix d'achat</t>
-        </is>
-      </c>
-      <c r="B67" s="23">
-        <f>B8</f>
-        <v/>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>Hypothèses</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>Travaux (étage + RDC + toiture + façades), montant retenu sans sarking</t>
-        </is>
-      </c>
-      <c r="B68" s="23">
-        <f>Synthèse!F7</f>
-        <v/>
-      </c>
-      <c r="C68" s="12" t="inlineStr">
-        <is>
-          <t>Onglet Synthèse</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>Postes hors budget (moyenne)</t>
-        </is>
-      </c>
-      <c r="B69" s="23">
-        <f>(Paramètres!B14+Paramètres!C14)/2</f>
+          <t>Prix d'achat</t>
+        </is>
+      </c>
+      <c r="B69" s="24">
+        <f>B8</f>
         <v/>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Onglet Paramètres</t>
+          <t>Hypothèses</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>Extérieurs (piscine, jacuzzi, pergola, paysager…)</t>
-        </is>
-      </c>
-      <c r="B70" s="23">
-        <f>B9</f>
+          <t>Travaux (étage + RDC + toiture + façades), montant retenu sans sarking</t>
+        </is>
+      </c>
+      <c r="B70" s="24">
+        <f>Synthèse!F7</f>
         <v/>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>Hypothèses</t>
+          <t>Onglet Synthèse</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="inlineStr">
-        <is>
-          <t>COÛT TOTAL DU PROJET</t>
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>Postes hors budget (moyenne)</t>
         </is>
       </c>
       <c r="B71" s="24">
-        <f>SUM(B67:B70)</f>
-        <v/>
-      </c>
-      <c r="C71" s="12" t="inlineStr"/>
+        <f>(Paramètres!B17+Paramètres!C17)/2</f>
+        <v/>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Onglet Paramètres</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
+          <t>Extérieurs (piscine, jacuzzi, pergola, paysager…)</t>
+        </is>
+      </c>
+      <c r="B72" s="24">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Hypothèses</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>COÛT TOTAL DU PROJET</t>
+        </is>
+      </c>
+      <c r="B73" s="25">
+        <f>SUM(B69:B72)</f>
+        <v/>
+      </c>
+      <c r="C73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
           <t>Valeur centrale retenue</t>
         </is>
       </c>
-      <c r="B72" s="23">
-        <f>B57</f>
-        <v/>
-      </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="B74" s="24">
+        <f>B59</f>
+        <v/>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
         <is>
           <t>Section 5</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
         <is>
           <t>PLUS / MOINS-VALUE LATENTE</t>
         </is>
       </c>
-      <c r="B73" s="25">
-        <f>B72-B71</f>
-        <v/>
-      </c>
-      <c r="C73" s="19" t="inlineStr">
+      <c r="B75" s="26">
+        <f>B74-B73</f>
+        <v/>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
         <is>
           <t>Négatif = le marché ne rembourse pas tout l'investissement</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>8. Ce qui peut faire varier la valeur de ± 50 k€ ou plus</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Facteur</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Sens</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Impact estimé</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="12" t="inlineStr">
-        <is>
-          <t>Grange identifiée « changement de destination » au PLUi</t>
-        </is>
-      </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>+20 à +50 k€</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t>DPE A/B (sarking, PAC, pisé sain)</t>
-        </is>
-      </c>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="C78" s="12" t="inlineStr">
-        <is>
-          <t>+10 à +30 k€</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>Maison existante rénovée au même niveau, cuisine ouverte vers le séjour</t>
-        </is>
-      </c>
-      <c r="B79" s="22" t="inlineStr">
+          <t>Grange identifiée « changement de destination » au PLUi</t>
+        </is>
+      </c>
+      <c r="B79" s="23" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>+15 à +40 k€</t>
+          <t>+20 à +50 k€</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>Historique Airbnb 12-24 mois avec comptes certifiés</t>
-        </is>
-      </c>
-      <c r="B80" s="22" t="inlineStr">
+          <t>DPE A/B (sarking, PAC, pisé sain)</t>
+        </is>
+      </c>
+      <c r="B80" s="23" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>+10 à +40 k€ (acheteur investisseur)</t>
+          <t>+10 à +30 k€</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>Acheteur collectionneur / artisan valorisant la grange</t>
-        </is>
-      </c>
-      <c r="B81" s="22" t="inlineStr">
+          <t>Maison existante rénovée au même niveau, cuisine ouverte vers le séjour</t>
+        </is>
+      </c>
+      <c r="B81" s="23" t="inlineStr">
         <is>
           <t>+</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>+20 à +50 k€</t>
+          <t>+15 à +40 k€</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>Maison existante pas au niveau de la grange (effet « deux bâtiments »)</t>
-        </is>
-      </c>
-      <c r="B82" s="22" t="inlineStr">
-        <is>
-          <t>−</t>
+          <t>Historique Airbnb 12-24 mois avec comptes certifiés</t>
+        </is>
+      </c>
+      <c r="B82" s="23" t="inlineStr">
+        <is>
+          <t>+</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>−30 à −60 k€</t>
+          <t>+10 à +40 k€ (acheteur investisseur)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>Surface habitable légale réduite par les rampants</t>
-        </is>
-      </c>
-      <c r="B83" s="22" t="inlineStr">
-        <is>
-          <t>−</t>
+          <t>Acheteur collectionneur / artisan valorisant la grange</t>
+        </is>
+      </c>
+      <c r="B83" s="23" t="inlineStr">
+        <is>
+          <t>+</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>−10 à −30 k€ (lecture de l'annonce)</t>
+          <t>+20 à +50 k€</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>DPE D ou pire, humidité dans le pisé</t>
-        </is>
-      </c>
-      <c r="B84" s="22" t="inlineStr">
+          <t>Maison existante pas au niveau de la grange (effet « deux bâtiments »)</t>
+        </is>
+      </c>
+      <c r="B84" s="23" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>−20 à −50 k€</t>
+          <t>−30 à −60 k€</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>Assainissement non conforme (SPANC)</t>
-        </is>
-      </c>
-      <c r="B85" s="22" t="inlineStr">
+          <t>Surface habitable légale réduite par les rampants</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>−10 à −25 k€</t>
+          <t>−10 à −30 k€ (lecture de l'annonce)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>Dossiers incomplets : changement de destination, DAACT, amiante grange</t>
-        </is>
-      </c>
-      <c r="B86" s="22" t="inlineStr">
+          <t>DPE D ou pire, humidité dans le pisé</t>
+        </is>
+      </c>
+      <c r="B86" s="23" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>Blocage ou −20 à −50 k€</t>
+          <t>−20 à −50 k€</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>Hausse des taux de crédit</t>
-        </is>
-      </c>
-      <c r="B87" s="22" t="inlineStr">
+          <t>Assainissement non conforme (SPANC)</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>−5 à −10 % de la valeur</t>
+          <t>−10 à −25 k€</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
+          <t>Dossiers incomplets : changement de destination, DAACT, amiante grange</t>
+        </is>
+      </c>
+      <c r="B88" s="23" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Blocage ou −20 à −50 k€</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>Hausse des taux de crédit</t>
+        </is>
+      </c>
+      <c r="B89" s="23" t="inlineStr">
+        <is>
+          <t>−</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>−5 à −10 % de la valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
           <t>Bien perçu comme « gîte » plutôt que maison familiale</t>
         </is>
       </c>
-      <c r="B88" s="22" t="inlineStr">
+      <c r="B90" s="23" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C90" s="12" t="inlineStr">
         <is>
           <t>−10 à −30 k€</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="11" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>9. Sources</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="26" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="27" t="inlineStr">
         <is>
           <t>Square Habitat – Sainte-Anne-sur-Gervonde</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="26" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="27" t="inlineStr">
         <is>
           <t>PAP – Sainte-Anne-sur-Gervonde</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="26" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="27" t="inlineStr">
         <is>
           <t>Immovrai – Sainte-Anne-sur-Gervonde (DVF)</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="26" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="27" t="inlineStr">
         <is>
           <t>Immovrai – Châtonnay</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="26" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="27" t="inlineStr">
         <is>
           <t>Immovrai – Meyrieu-les-Étangs</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="26" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="27" t="inlineStr">
         <is>
           <t>PAP – Saint-Jean-de-Bournay</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="26" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="27" t="inlineStr">
         <is>
           <t>MeilleursAgents – Saint-Jean-de-Bournay</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="26" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="27" t="inlineStr">
         <is>
           <t>PAP – Beauvoir-de-Marc</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="26" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="27" t="inlineStr">
         <is>
           <t>Logic-immo – maisons avec piscine à Saint-Jean-de-Bournay</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="26" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="27" t="inlineStr">
         <is>
           <t>Nestenn – Beauvoir-de-Marc, maison avec piscine</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="26" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="27" t="inlineStr">
         <is>
           <t>Propriétés Rurales – corps de ferme rénové</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="26" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="27" t="inlineStr">
         <is>
           <t>Belles Demeures – secteur Vienne</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="26" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="27" t="inlineStr">
         <is>
           <t>Zimo – hangars à vendre en Isère</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="26" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="27" t="inlineStr">
         <is>
           <t>French Property – hangars Nord-Isère</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="26" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="27" t="inlineStr">
         <is>
           <t>MRAe – PLUi Bièvre Isère, secteur Région Saint-Jeannaise</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="26" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="27" t="inlineStr">
         <is>
           <t>DVF officiel (ventes réelles, à consulter)</t>
         </is>
@@ -2733,22 +2760,22 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2872,25 +2899,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Gros œuvre</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="28" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="28" t="n"/>
-      <c r="J5" s="28" t="n"/>
-      <c r="K5" s="28" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="28" t="n"/>
-      <c r="N5" s="28" t="n"/>
-      <c r="O5" s="28" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="29" t="n"/>
+      <c r="O5" s="29" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -2904,41 +2931,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="31" t="n">
         <v>3000</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="31" t="n">
         <v>8000</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="32">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J6" s="32" t="n">
+      <c r="J6" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="32">
         <f>IF(I6="Oui",G6*J6,G6)</f>
         <v/>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="32">
         <f>IF(I6="Oui",H6*J6,H6)</f>
         <v/>
       </c>
-      <c r="M6" s="33" t="n"/>
-      <c r="N6" s="31">
+      <c r="M6" s="34" t="n"/>
+      <c r="N6" s="32">
         <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
         <v/>
       </c>
@@ -2960,41 +2987,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="31" t="n">
         <v>2000</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J7" s="32" t="n">
+      <c r="J7" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="32">
         <f>IF(I7="Oui",G7*J7,G7)</f>
         <v/>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="32">
         <f>IF(I7="Oui",H7*J7,H7)</f>
         <v/>
       </c>
-      <c r="M7" s="33" t="n"/>
-      <c r="N7" s="31">
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="32">
         <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
         <v/>
       </c>
@@ -3012,41 +3039,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="31" t="n">
         <v>4000</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="31" t="n">
         <v>9000</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J8" s="32" t="n">
+      <c r="J8" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="32">
         <f>IF(I8="Oui",G8*J8,G8)</f>
         <v/>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="32">
         <f>IF(I8="Oui",H8*J8,H8)</f>
         <v/>
       </c>
-      <c r="M8" s="33" t="n"/>
-      <c r="N8" s="31">
+      <c r="M8" s="34" t="n"/>
+      <c r="N8" s="32">
         <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
         <v/>
       </c>
@@ -3057,25 +3084,25 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Enveloppe / isolation</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n"/>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="28" t="n"/>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="28" t="n"/>
-      <c r="H9" s="28" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="28" t="n"/>
-      <c r="K9" s="28" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="28" t="n"/>
-      <c r="N9" s="28" t="n"/>
-      <c r="O9" s="28" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="29" t="n"/>
+      <c r="I9" s="29" t="n"/>
+      <c r="J9" s="29" t="n"/>
+      <c r="K9" s="29" t="n"/>
+      <c r="L9" s="29" t="n"/>
+      <c r="M9" s="29" t="n"/>
+      <c r="N9" s="29" t="n"/>
+      <c r="O9" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
@@ -3089,41 +3116,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="31" t="n">
         <v>120</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="31" t="n">
         <v>250</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="29" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J10" s="32" t="n">
+      <c r="J10" s="33" t="n">
         <v>0.55</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="32">
         <f>IF(I10="Oui",G10*J10,G10)</f>
         <v/>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="32">
         <f>IF(I10="Oui",H10*J10,H10)</f>
         <v/>
       </c>
-      <c r="M10" s="33" t="n"/>
-      <c r="N10" s="31">
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="32">
         <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
         <v/>
       </c>
@@ -3145,41 +3172,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="31" t="n">
         <v>1600</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="32">
         <f>D11*E11</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="29" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J11" s="32" t="n">
+      <c r="J11" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="32">
         <f>IF(I11="Oui",G11*J11,G11)</f>
         <v/>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="32">
         <f>IF(I11="Oui",H11*J11,H11)</f>
         <v/>
       </c>
-      <c r="M11" s="33" t="n"/>
-      <c r="N11" s="31">
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="32">
         <f>IF(N(M11)&gt;0,M11,(G11+H11)/2)</f>
         <v/>
       </c>
@@ -3201,41 +3228,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="31" t="n">
         <v>800</v>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F12" s="31" t="n">
         <v>1300</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="32">
         <f>D12*E12</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="32">
         <f>D12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J12" s="32" t="n">
+      <c r="J12" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="32">
         <f>IF(I12="Oui",G12*J12,G12)</f>
         <v/>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="32">
         <f>IF(I12="Oui",H12*J12,H12)</f>
         <v/>
       </c>
-      <c r="M12" s="33" t="n"/>
-      <c r="N12" s="31">
+      <c r="M12" s="34" t="n"/>
+      <c r="N12" s="32">
         <f>IF(N(M12)&gt;0,M12,(G12+H12)/2)</f>
         <v/>
       </c>
@@ -3253,41 +3280,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="31" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="31" t="n">
         <v>130</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>D13*E13</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J13" s="32" t="n">
+      <c r="J13" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="32">
         <f>IF(I13="Oui",G13*J13,G13)</f>
         <v/>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="32">
         <f>IF(I13="Oui",H13*J13,H13)</f>
         <v/>
       </c>
-      <c r="M13" s="33" t="n"/>
-      <c r="N13" s="31">
+      <c r="M13" s="34" t="n"/>
+      <c r="N13" s="32">
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
@@ -3298,25 +3325,25 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Cloisons / plafonds</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="28" t="n"/>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="28" t="n"/>
-      <c r="J14" s="28" t="n"/>
-      <c r="K14" s="28" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="28" t="n"/>
-      <c r="N14" s="28" t="n"/>
-      <c r="O14" s="28" t="n"/>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="29" t="n"/>
+      <c r="I14" s="29" t="n"/>
+      <c r="J14" s="29" t="n"/>
+      <c r="K14" s="29" t="n"/>
+      <c r="L14" s="29" t="n"/>
+      <c r="M14" s="29" t="n"/>
+      <c r="N14" s="29" t="n"/>
+      <c r="O14" s="29" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -3330,41 +3357,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="31" t="n">
         <v>90</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="32">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="29" t="inlineStr">
+      <c r="I15" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J15" s="32" t="n">
+      <c r="J15" s="33" t="n">
         <v>0.45</v>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="32">
         <f>IF(I15="Oui",G15*J15,G15)</f>
         <v/>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="32">
         <f>IF(I15="Oui",H15*J15,H15)</f>
         <v/>
       </c>
-      <c r="M15" s="33" t="n"/>
-      <c r="N15" s="31">
+      <c r="M15" s="34" t="n"/>
+      <c r="N15" s="32">
         <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
         <v/>
       </c>
@@ -3382,66 +3409,66 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>D16*E16</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>D16*F16</f>
         <v/>
       </c>
-      <c r="I16" s="29" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J16" s="32" t="n">
+      <c r="J16" s="33" t="n">
         <v>0.45</v>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="32">
         <f>IF(I16="Oui",G16*J16,G16)</f>
         <v/>
       </c>
-      <c r="L16" s="31">
+      <c r="L16" s="32">
         <f>IF(I16="Oui",H16*J16,H16)</f>
         <v/>
       </c>
-      <c r="M16" s="33" t="n"/>
-      <c r="N16" s="31">
+      <c r="M16" s="34" t="n"/>
+      <c r="N16" s="32">
         <f>IF(N(M16)&gt;0,M16,(G16+H16)/2)</f>
         <v/>
       </c>
       <c r="O16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Plomberie</t>
         </is>
       </c>
-      <c r="B17" s="28" t="n"/>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="28" t="n"/>
-      <c r="F17" s="28" t="n"/>
-      <c r="G17" s="28" t="n"/>
-      <c r="H17" s="28" t="n"/>
-      <c r="I17" s="28" t="n"/>
-      <c r="J17" s="28" t="n"/>
-      <c r="K17" s="28" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="28" t="n"/>
-      <c r="N17" s="28" t="n"/>
-      <c r="O17" s="28" t="n"/>
+      <c r="B17" s="29" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="29" t="n"/>
+      <c r="H17" s="29" t="n"/>
+      <c r="I17" s="29" t="n"/>
+      <c r="J17" s="29" t="n"/>
+      <c r="K17" s="29" t="n"/>
+      <c r="L17" s="29" t="n"/>
+      <c r="M17" s="29" t="n"/>
+      <c r="N17" s="29" t="n"/>
+      <c r="O17" s="29" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
@@ -3455,41 +3482,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="31" t="n">
         <v>9000</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="32">
         <f>D18*E18</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="32">
         <f>D18*F18</f>
         <v/>
       </c>
-      <c r="I18" s="29" t="inlineStr">
+      <c r="I18" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J18" s="32" t="n">
+      <c r="J18" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="32">
         <f>IF(I18="Oui",G18*J18,G18)</f>
         <v/>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="32">
         <f>IF(I18="Oui",H18*J18,H18)</f>
         <v/>
       </c>
-      <c r="M18" s="33" t="n"/>
-      <c r="N18" s="31">
+      <c r="M18" s="34" t="n"/>
+      <c r="N18" s="32">
         <f>IF(N(M18)&gt;0,M18,(G18+H18)/2)</f>
         <v/>
       </c>
@@ -3511,41 +3538,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="E19" s="31" t="n">
         <v>1500</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="31" t="n">
         <v>3000</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="32">
         <f>D19*E19</f>
         <v/>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="32">
         <f>D19*F19</f>
         <v/>
       </c>
-      <c r="I19" s="29" t="inlineStr">
+      <c r="I19" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J19" s="32" t="n">
+      <c r="J19" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="32">
         <f>IF(I19="Oui",G19*J19,G19)</f>
         <v/>
       </c>
-      <c r="L19" s="31">
+      <c r="L19" s="32">
         <f>IF(I19="Oui",H19*J19,H19)</f>
         <v/>
       </c>
-      <c r="M19" s="33" t="n"/>
-      <c r="N19" s="31">
+      <c r="M19" s="34" t="n"/>
+      <c r="N19" s="32">
         <f>IF(N(M19)&gt;0,M19,(G19+H19)/2)</f>
         <v/>
       </c>
@@ -3563,41 +3590,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="31" t="n">
         <v>500</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="32">
         <f>D20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="32">
         <f>D20*F20</f>
         <v/>
       </c>
-      <c r="I20" s="29" t="inlineStr">
+      <c r="I20" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J20" s="32" t="n">
+      <c r="J20" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="32">
         <f>IF(I20="Oui",G20*J20,G20)</f>
         <v/>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="32">
         <f>IF(I20="Oui",H20*J20,H20)</f>
         <v/>
       </c>
-      <c r="M20" s="33" t="n"/>
-      <c r="N20" s="31">
+      <c r="M20" s="34" t="n"/>
+      <c r="N20" s="32">
         <f>IF(N(M20)&gt;0,M20,(G20+H20)/2)</f>
         <v/>
       </c>
@@ -3619,41 +3646,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="31" t="n">
         <v>2000</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="31" t="n">
         <v>4000</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <f>D21*E21</f>
         <v/>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <f>D21*F21</f>
         <v/>
       </c>
-      <c r="I21" s="29" t="inlineStr">
+      <c r="I21" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J21" s="32" t="n">
+      <c r="J21" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <f>IF(I21="Oui",G21*J21,G21)</f>
         <v/>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <f>IF(I21="Oui",H21*J21,H21)</f>
         <v/>
       </c>
-      <c r="M21" s="33" t="n"/>
-      <c r="N21" s="31">
+      <c r="M21" s="34" t="n"/>
+      <c r="N21" s="32">
         <f>IF(N(M21)&gt;0,M21,(G21+H21)/2)</f>
         <v/>
       </c>
@@ -3664,25 +3691,25 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>Électricité / ventilation / chauffage</t>
         </is>
       </c>
-      <c r="B22" s="28" t="n"/>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
-      <c r="G22" s="28" t="n"/>
-      <c r="H22" s="28" t="n"/>
-      <c r="I22" s="28" t="n"/>
-      <c r="J22" s="28" t="n"/>
-      <c r="K22" s="28" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="28" t="n"/>
-      <c r="N22" s="28" t="n"/>
-      <c r="O22" s="28" t="n"/>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="29" t="n"/>
+      <c r="I22" s="29" t="n"/>
+      <c r="J22" s="29" t="n"/>
+      <c r="K22" s="29" t="n"/>
+      <c r="L22" s="29" t="n"/>
+      <c r="M22" s="29" t="n"/>
+      <c r="N22" s="29" t="n"/>
+      <c r="O22" s="29" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -3696,41 +3723,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="30" t="n">
         <v>77</v>
       </c>
-      <c r="E23" s="30" t="n">
+      <c r="E23" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="31" t="n">
         <v>130</v>
       </c>
-      <c r="G23" s="31">
+      <c r="G23" s="32">
         <f>D23*E23</f>
         <v/>
       </c>
-      <c r="H23" s="31">
+      <c r="H23" s="32">
         <f>D23*F23</f>
         <v/>
       </c>
-      <c r="I23" s="29" t="inlineStr">
+      <c r="I23" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J23" s="32" t="n">
+      <c r="J23" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="K23" s="31">
+      <c r="K23" s="32">
         <f>IF(I23="Oui",G23*J23,G23)</f>
         <v/>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="32">
         <f>IF(I23="Oui",H23*J23,H23)</f>
         <v/>
       </c>
-      <c r="M23" s="33" t="n"/>
-      <c r="N23" s="31">
+      <c r="M23" s="34" t="n"/>
+      <c r="N23" s="32">
         <f>IF(N(M23)&gt;0,M23,(G23+H23)/2)</f>
         <v/>
       </c>
@@ -3748,41 +3775,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="E24" s="31" t="n">
         <v>1500</v>
       </c>
-      <c r="F24" s="30" t="n">
+      <c r="F24" s="31" t="n">
         <v>3000</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <f>D24*E24</f>
         <v/>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <f>D24*F24</f>
         <v/>
       </c>
-      <c r="I24" s="29" t="inlineStr">
+      <c r="I24" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J24" s="32" t="n">
+      <c r="J24" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <f>IF(I24="Oui",G24*J24,G24)</f>
         <v/>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <f>IF(I24="Oui",H24*J24,H24)</f>
         <v/>
       </c>
-      <c r="M24" s="33" t="n"/>
-      <c r="N24" s="31">
+      <c r="M24" s="34" t="n"/>
+      <c r="N24" s="32">
         <f>IF(N(M24)&gt;0,M24,(G24+H24)/2)</f>
         <v/>
       </c>
@@ -3804,66 +3831,66 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="30" t="n">
+      <c r="E25" s="31" t="n">
         <v>4000</v>
       </c>
-      <c r="F25" s="30" t="n">
+      <c r="F25" s="31" t="n">
         <v>12000</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <f>D25*E25</f>
         <v/>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <f>D25*F25</f>
         <v/>
       </c>
-      <c r="I25" s="29" t="inlineStr">
+      <c r="I25" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J25" s="32" t="n">
+      <c r="J25" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <f>IF(I25="Oui",G25*J25,G25)</f>
         <v/>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <f>IF(I25="Oui",H25*J25,H25)</f>
         <v/>
       </c>
-      <c r="M25" s="33" t="n"/>
-      <c r="N25" s="31">
+      <c r="M25" s="34" t="n"/>
+      <c r="N25" s="32">
         <f>IF(N(M25)&gt;0,M25,(G25+H25)/2)</f>
         <v/>
       </c>
       <c r="O25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>Menuiseries intérieures</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n"/>
-      <c r="C26" s="28" t="n"/>
-      <c r="D26" s="28" t="n"/>
-      <c r="E26" s="28" t="n"/>
-      <c r="F26" s="28" t="n"/>
-      <c r="G26" s="28" t="n"/>
-      <c r="H26" s="28" t="n"/>
-      <c r="I26" s="28" t="n"/>
-      <c r="J26" s="28" t="n"/>
-      <c r="K26" s="28" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="28" t="n"/>
-      <c r="N26" s="28" t="n"/>
-      <c r="O26" s="28" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="29" t="n"/>
+      <c r="H26" s="29" t="n"/>
+      <c r="I26" s="29" t="n"/>
+      <c r="J26" s="29" t="n"/>
+      <c r="K26" s="29" t="n"/>
+      <c r="L26" s="29" t="n"/>
+      <c r="M26" s="29" t="n"/>
+      <c r="N26" s="29" t="n"/>
+      <c r="O26" s="29" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -3877,41 +3904,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="30" t="n">
+      <c r="E27" s="31" t="n">
         <v>300</v>
       </c>
-      <c r="F27" s="30" t="n">
+      <c r="F27" s="31" t="n">
         <v>550</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <f>D27*E27</f>
         <v/>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <f>D27*F27</f>
         <v/>
       </c>
-      <c r="I27" s="29" t="inlineStr">
+      <c r="I27" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J27" s="32" t="n">
+      <c r="J27" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <f>IF(I27="Oui",G27*J27,G27)</f>
         <v/>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <f>IF(I27="Oui",H27*J27,H27)</f>
         <v/>
       </c>
-      <c r="M27" s="33" t="n"/>
-      <c r="N27" s="31">
+      <c r="M27" s="34" t="n"/>
+      <c r="N27" s="32">
         <f>IF(N(M27)&gt;0,M27,(G27+H27)/2)</f>
         <v/>
       </c>
@@ -3933,41 +3960,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="30" t="n">
+      <c r="E28" s="31" t="n">
         <v>700</v>
       </c>
-      <c r="F28" s="30" t="n">
+      <c r="F28" s="31" t="n">
         <v>1200</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <f>D28*E28</f>
         <v/>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="32">
         <f>D28*F28</f>
         <v/>
       </c>
-      <c r="I28" s="29" t="inlineStr">
+      <c r="I28" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J28" s="32" t="n">
+      <c r="J28" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="32">
         <f>IF(I28="Oui",G28*J28,G28)</f>
         <v/>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="32">
         <f>IF(I28="Oui",H28*J28,H28)</f>
         <v/>
       </c>
-      <c r="M28" s="33" t="n"/>
-      <c r="N28" s="31">
+      <c r="M28" s="34" t="n"/>
+      <c r="N28" s="32">
         <f>IF(N(M28)&gt;0,M28,(G28+H28)/2)</f>
         <v/>
       </c>
@@ -3985,66 +4012,66 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="30" t="n">
+      <c r="E29" s="31" t="n">
         <v>300</v>
       </c>
-      <c r="F29" s="30" t="n">
+      <c r="F29" s="31" t="n">
         <v>700</v>
       </c>
-      <c r="G29" s="31">
+      <c r="G29" s="32">
         <f>D29*E29</f>
         <v/>
       </c>
-      <c r="H29" s="31">
+      <c r="H29" s="32">
         <f>D29*F29</f>
         <v/>
       </c>
-      <c r="I29" s="29" t="inlineStr">
+      <c r="I29" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J29" s="32" t="n">
+      <c r="J29" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K29" s="31">
+      <c r="K29" s="32">
         <f>IF(I29="Oui",G29*J29,G29)</f>
         <v/>
       </c>
-      <c r="L29" s="31">
+      <c r="L29" s="32">
         <f>IF(I29="Oui",H29*J29,H29)</f>
         <v/>
       </c>
-      <c r="M29" s="33" t="n"/>
-      <c r="N29" s="31">
+      <c r="M29" s="34" t="n"/>
+      <c r="N29" s="32">
         <f>IF(N(M29)&gt;0,M29,(G29+H29)/2)</f>
         <v/>
       </c>
       <c r="O29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>Revêtements / finitions</t>
         </is>
       </c>
-      <c r="B30" s="28" t="n"/>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="28" t="n"/>
-      <c r="G30" s="28" t="n"/>
-      <c r="H30" s="28" t="n"/>
-      <c r="I30" s="28" t="n"/>
-      <c r="J30" s="28" t="n"/>
-      <c r="K30" s="28" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="28" t="n"/>
-      <c r="N30" s="28" t="n"/>
-      <c r="O30" s="28" t="n"/>
+      <c r="B30" s="29" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="29" t="n"/>
+      <c r="G30" s="29" t="n"/>
+      <c r="H30" s="29" t="n"/>
+      <c r="I30" s="29" t="n"/>
+      <c r="J30" s="29" t="n"/>
+      <c r="K30" s="29" t="n"/>
+      <c r="L30" s="29" t="n"/>
+      <c r="M30" s="29" t="n"/>
+      <c r="N30" s="29" t="n"/>
+      <c r="O30" s="29" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -4058,41 +4085,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="30" t="n">
         <v>51</v>
       </c>
-      <c r="E31" s="30" t="n">
+      <c r="E31" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="F31" s="30" t="n">
+      <c r="F31" s="31" t="n">
         <v>90</v>
       </c>
-      <c r="G31" s="31">
+      <c r="G31" s="32">
         <f>D31*E31</f>
         <v/>
       </c>
-      <c r="H31" s="31">
+      <c r="H31" s="32">
         <f>D31*F31</f>
         <v/>
       </c>
-      <c r="I31" s="29" t="inlineStr">
+      <c r="I31" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J31" s="32" t="n">
+      <c r="J31" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K31" s="31">
+      <c r="K31" s="32">
         <f>IF(I31="Oui",G31*J31,G31)</f>
         <v/>
       </c>
-      <c r="L31" s="31">
+      <c r="L31" s="32">
         <f>IF(I31="Oui",H31*J31,H31)</f>
         <v/>
       </c>
-      <c r="M31" s="33" t="n"/>
-      <c r="N31" s="31">
+      <c r="M31" s="34" t="n"/>
+      <c r="N31" s="32">
         <f>IF(N(M31)&gt;0,M31,(G31+H31)/2)</f>
         <v/>
       </c>
@@ -4110,41 +4137,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="E32" s="30" t="n">
+      <c r="E32" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="F32" s="30" t="n">
+      <c r="F32" s="31" t="n">
         <v>130</v>
       </c>
-      <c r="G32" s="31">
+      <c r="G32" s="32">
         <f>D32*E32</f>
         <v/>
       </c>
-      <c r="H32" s="31">
+      <c r="H32" s="32">
         <f>D32*F32</f>
         <v/>
       </c>
-      <c r="I32" s="29" t="inlineStr">
+      <c r="I32" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J32" s="32" t="n">
+      <c r="J32" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K32" s="31">
+      <c r="K32" s="32">
         <f>IF(I32="Oui",G32*J32,G32)</f>
         <v/>
       </c>
-      <c r="L32" s="31">
+      <c r="L32" s="32">
         <f>IF(I32="Oui",H32*J32,H32)</f>
         <v/>
       </c>
-      <c r="M32" s="33" t="n"/>
-      <c r="N32" s="31">
+      <c r="M32" s="34" t="n"/>
+      <c r="N32" s="32">
         <f>IF(N(M32)&gt;0,M32,(G32+H32)/2)</f>
         <v/>
       </c>
@@ -4162,41 +4189,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="E33" s="30" t="n">
+      <c r="E33" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="F33" s="30" t="n">
+      <c r="F33" s="31" t="n">
         <v>130</v>
       </c>
-      <c r="G33" s="31">
+      <c r="G33" s="32">
         <f>D33*E33</f>
         <v/>
       </c>
-      <c r="H33" s="31">
+      <c r="H33" s="32">
         <f>D33*F33</f>
         <v/>
       </c>
-      <c r="I33" s="29" t="inlineStr">
+      <c r="I33" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J33" s="32" t="n">
+      <c r="J33" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K33" s="31">
+      <c r="K33" s="32">
         <f>IF(I33="Oui",G33*J33,G33)</f>
         <v/>
       </c>
-      <c r="L33" s="31">
+      <c r="L33" s="32">
         <f>IF(I33="Oui",H33*J33,H33)</f>
         <v/>
       </c>
-      <c r="M33" s="33" t="n"/>
-      <c r="N33" s="31">
+      <c r="M33" s="34" t="n"/>
+      <c r="N33" s="32">
         <f>IF(N(M33)&gt;0,M33,(G33+H33)/2)</f>
         <v/>
       </c>
@@ -4214,186 +4241,186 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="E34" s="30" t="n">
+      <c r="E34" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="F34" s="30" t="n">
+      <c r="F34" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="32">
         <f>D34*E34</f>
         <v/>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="32">
         <f>D34*F34</f>
         <v/>
       </c>
-      <c r="I34" s="29" t="inlineStr">
+      <c r="I34" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J34" s="32" t="n">
+      <c r="J34" s="33" t="n">
         <v>0.25</v>
       </c>
-      <c r="K34" s="31">
+      <c r="K34" s="32">
         <f>IF(I34="Oui",G34*J34,G34)</f>
         <v/>
       </c>
-      <c r="L34" s="31">
+      <c r="L34" s="32">
         <f>IF(I34="Oui",H34*J34,H34)</f>
         <v/>
       </c>
-      <c r="M34" s="33" t="n"/>
-      <c r="N34" s="31">
+      <c r="M34" s="34" t="n"/>
+      <c r="N34" s="32">
         <f>IF(N(M34)&gt;0,M34,(G34+H34)/2)</f>
         <v/>
       </c>
       <c r="O34" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="B36" s="34" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <f>SUM(G5:G34)</f>
         <v/>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="36">
         <f>SUM(H5:H34)</f>
         <v/>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="36">
         <f>SUM(K5:K34)</f>
         <v/>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="36">
         <f>SUM(L5:L34)</f>
         <v/>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="36">
         <f>SUM(N5:N34)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>Imprévus</t>
         </is>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="38">
         <f>G36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="H37" s="37">
+      <c r="H37" s="38">
         <f>H36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="K37" s="37">
+      <c r="K37" s="38">
         <f>K36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="38">
         <f>L36*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="N37" s="37">
+      <c r="N37" s="38">
         <f>N36*Paramètres!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="36" t="inlineStr">
+      <c r="B38" s="37" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre</t>
         </is>
       </c>
-      <c r="G38" s="37">
+      <c r="G38" s="38">
         <f>G36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="H38" s="37">
+      <c r="H38" s="38">
         <f>H36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="K38" s="37">
+      <c r="K38" s="38">
         <f>K36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="L38" s="37">
+      <c r="L38" s="38">
         <f>L36*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="N38" s="37">
+      <c r="N38" s="38">
         <f>N36*Paramètres!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="n"/>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="A39" s="39" t="n"/>
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>TOTAL ÉTAGE TTC</t>
         </is>
       </c>
-      <c r="C39" s="38" t="n"/>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="38" t="n"/>
-      <c r="F39" s="38" t="n"/>
-      <c r="G39" s="40">
+      <c r="C39" s="39" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="41">
         <f>G36+G37+G38</f>
         <v/>
       </c>
-      <c r="H39" s="40">
+      <c r="H39" s="41">
         <f>H36+H37+H38</f>
         <v/>
       </c>
-      <c r="I39" s="38" t="n"/>
-      <c r="J39" s="38" t="n"/>
-      <c r="K39" s="40">
+      <c r="I39" s="39" t="n"/>
+      <c r="J39" s="39" t="n"/>
+      <c r="K39" s="41">
         <f>K36+K37+K38</f>
         <v/>
       </c>
-      <c r="L39" s="40">
+      <c r="L39" s="41">
         <f>L36+L37+L38</f>
         <v/>
       </c>
-      <c r="M39" s="38" t="n"/>
-      <c r="N39" s="40">
+      <c r="M39" s="39" t="n"/>
+      <c r="N39" s="41">
         <f>N36+N37+N38</f>
         <v/>
       </c>
-      <c r="O39" s="38" t="n"/>
+      <c r="O39" s="39" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="36" t="inlineStr">
+      <c r="B40" s="37" t="inlineStr">
         <is>
           <t>Soit par m² (77 m²)</t>
         </is>
       </c>
-      <c r="G40" s="41">
+      <c r="G40" s="42">
         <f>G39/77</f>
         <v/>
       </c>
-      <c r="H40" s="41">
+      <c r="H40" s="42">
         <f>H39/77</f>
         <v/>
       </c>
-      <c r="K40" s="41">
+      <c r="K40" s="42">
         <f>K39/77</f>
         <v/>
       </c>
-      <c r="L40" s="41">
+      <c r="L40" s="42">
         <f>L39/77</f>
         <v/>
       </c>
-      <c r="N40" s="41">
+      <c r="N40" s="42">
         <f>N39/77</f>
         <v/>
       </c>
@@ -4548,25 +4575,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Gros œuvre / structure</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="28" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="28" t="n"/>
-      <c r="J5" s="28" t="n"/>
-      <c r="K5" s="28" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="28" t="n"/>
-      <c r="N5" s="28" t="n"/>
-      <c r="O5" s="28" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="29" t="n"/>
+      <c r="O5" s="29" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -4580,41 +4607,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="31" t="n">
         <v>6000</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="31" t="n">
         <v>15000</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="32">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J6" s="32" t="n">
+      <c r="J6" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="32">
         <f>IF(I6="Oui",G6*J6,G6)</f>
         <v/>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="32">
         <f>IF(I6="Oui",H6*J6,H6)</f>
         <v/>
       </c>
-      <c r="M6" s="33" t="n"/>
-      <c r="N6" s="31">
+      <c r="M6" s="34" t="n"/>
+      <c r="N6" s="32">
         <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
         <v/>
       </c>
@@ -4636,41 +4663,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="31" t="n">
         <v>1000</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="31" t="n">
         <v>2500</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J7" s="32" t="n">
+      <c r="J7" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="32">
         <f>IF(I7="Oui",G7*J7,G7)</f>
         <v/>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="32">
         <f>IF(I7="Oui",H7*J7,H7)</f>
         <v/>
       </c>
-      <c r="M7" s="33" t="n"/>
-      <c r="N7" s="31">
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="32">
         <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
         <v/>
       </c>
@@ -4692,41 +4719,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="31" t="n">
         <v>90</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="31" t="n">
         <v>180</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J8" s="32" t="n">
+      <c r="J8" s="33" t="n">
         <v>0.45</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="32">
         <f>IF(I8="Oui",G8*J8,G8)</f>
         <v/>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="32">
         <f>IF(I8="Oui",H8*J8,H8)</f>
         <v/>
       </c>
-      <c r="M8" s="33" t="n"/>
-      <c r="N8" s="31">
+      <c r="M8" s="34" t="n"/>
+      <c r="N8" s="32">
         <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
         <v/>
       </c>
@@ -4737,25 +4764,25 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Menuiseries extérieures</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n"/>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="28" t="n"/>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="28" t="n"/>
-      <c r="H9" s="28" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="28" t="n"/>
-      <c r="K9" s="28" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="28" t="n"/>
-      <c r="N9" s="28" t="n"/>
-      <c r="O9" s="28" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="29" t="n"/>
+      <c r="I9" s="29" t="n"/>
+      <c r="J9" s="29" t="n"/>
+      <c r="K9" s="29" t="n"/>
+      <c r="L9" s="29" t="n"/>
+      <c r="M9" s="29" t="n"/>
+      <c r="N9" s="29" t="n"/>
+      <c r="O9" s="29" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
@@ -4769,41 +4796,41 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="31" t="n">
         <v>12000</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="31" t="n">
         <v>25000</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="29" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J10" s="32" t="n">
+      <c r="J10" s="33" t="n">
         <v>0.7</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="32">
         <f>IF(I10="Oui",G10*J10,G10)</f>
         <v/>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="32">
         <f>IF(I10="Oui",H10*J10,H10)</f>
         <v/>
       </c>
-      <c r="M10" s="33" t="n"/>
-      <c r="N10" s="31">
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="32">
         <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
         <v/>
       </c>
@@ -4825,66 +4852,66 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="31" t="n">
         <v>800</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="31" t="n">
         <v>2000</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="32">
         <f>D11*E11</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>D11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="29" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J11" s="32" t="n">
+      <c r="J11" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K11" s="31">
+      <c r="K11" s="32">
         <f>IF(I11="Oui",G11*J11,G11)</f>
         <v/>
       </c>
-      <c r="L11" s="31">
+      <c r="L11" s="32">
         <f>IF(I11="Oui",H11*J11,H11)</f>
         <v/>
       </c>
-      <c r="M11" s="33" t="n"/>
-      <c r="N11" s="31">
+      <c r="M11" s="34" t="n"/>
+      <c r="N11" s="32">
         <f>IF(N(M11)&gt;0,M11,(G11+H11)/2)</f>
         <v/>
       </c>
       <c r="O11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Isolation / doublage / plafond</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="28" t="n"/>
-      <c r="K12" s="28" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="28" t="n"/>
-      <c r="N12" s="28" t="n"/>
-      <c r="O12" s="28" t="n"/>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="29" t="n"/>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="29" t="n"/>
+      <c r="K12" s="29" t="n"/>
+      <c r="L12" s="29" t="n"/>
+      <c r="M12" s="29" t="n"/>
+      <c r="N12" s="29" t="n"/>
+      <c r="O12" s="29" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -4898,41 +4925,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <v>79</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="31" t="n">
         <v>75</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="31" t="n">
         <v>130</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>D13*E13</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J13" s="32" t="n">
+      <c r="J13" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="32">
         <f>IF(I13="Oui",G13*J13,G13)</f>
         <v/>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="32">
         <f>IF(I13="Oui",H13*J13,H13)</f>
         <v/>
       </c>
-      <c r="M13" s="33" t="n"/>
-      <c r="N13" s="31">
+      <c r="M13" s="34" t="n"/>
+      <c r="N13" s="32">
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
@@ -4954,41 +4981,41 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="31" t="n">
         <v>150</v>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F14" s="31" t="n">
         <v>300</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>D14*E14</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>D14*F14</f>
         <v/>
       </c>
-      <c r="I14" s="29" t="inlineStr">
+      <c r="I14" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J14" s="32" t="n">
+      <c r="J14" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="32">
         <f>IF(I14="Oui",G14*J14,G14)</f>
         <v/>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="32">
         <f>IF(I14="Oui",H14*J14,H14)</f>
         <v/>
       </c>
-      <c r="M14" s="33" t="n"/>
-      <c r="N14" s="31">
+      <c r="M14" s="34" t="n"/>
+      <c r="N14" s="32">
         <f>IF(N(M14)&gt;0,M14,(G14+H14)/2)</f>
         <v/>
       </c>
@@ -5010,41 +5037,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="32">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="29" t="inlineStr">
+      <c r="I15" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J15" s="32" t="n">
+      <c r="J15" s="33" t="n">
         <v>0.45</v>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="32">
         <f>IF(I15="Oui",G15*J15,G15)</f>
         <v/>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="32">
         <f>IF(I15="Oui",H15*J15,H15)</f>
         <v/>
       </c>
-      <c r="M15" s="33" t="n"/>
-      <c r="N15" s="31">
+      <c r="M15" s="34" t="n"/>
+      <c r="N15" s="32">
         <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
         <v/>
       </c>
@@ -5055,25 +5082,25 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Électricité / chauffage</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="28" t="n"/>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="28" t="n"/>
-      <c r="H16" s="28" t="n"/>
-      <c r="I16" s="28" t="n"/>
-      <c r="J16" s="28" t="n"/>
-      <c r="K16" s="28" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="28" t="n"/>
-      <c r="N16" s="28" t="n"/>
-      <c r="O16" s="28" t="n"/>
+      <c r="B16" s="29" t="n"/>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="29" t="n"/>
+      <c r="H16" s="29" t="n"/>
+      <c r="I16" s="29" t="n"/>
+      <c r="J16" s="29" t="n"/>
+      <c r="K16" s="29" t="n"/>
+      <c r="L16" s="29" t="n"/>
+      <c r="M16" s="29" t="n"/>
+      <c r="N16" s="29" t="n"/>
+      <c r="O16" s="29" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -5087,41 +5114,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="E17" s="30" t="n">
+      <c r="E17" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="31" t="n">
         <v>110</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>D17*E17</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>D17*F17</f>
         <v/>
       </c>
-      <c r="I17" s="29" t="inlineStr">
+      <c r="I17" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J17" s="32" t="n">
+      <c r="J17" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="32">
         <f>IF(I17="Oui",G17*J17,G17)</f>
         <v/>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="32">
         <f>IF(I17="Oui",H17*J17,H17)</f>
         <v/>
       </c>
-      <c r="M17" s="33" t="n"/>
-      <c r="N17" s="31">
+      <c r="M17" s="34" t="n"/>
+      <c r="N17" s="32">
         <f>IF(N(M17)&gt;0,M17,(G17+H17)/2)</f>
         <v/>
       </c>
@@ -5139,41 +5166,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="31" t="n">
         <v>4000</v>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="31" t="n">
         <v>12000</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="32">
         <f>D18*E18</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="32">
         <f>D18*F18</f>
         <v/>
       </c>
-      <c r="I18" s="29" t="inlineStr">
+      <c r="I18" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J18" s="32" t="n">
+      <c r="J18" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="32">
         <f>IF(I18="Oui",G18*J18,G18)</f>
         <v/>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="32">
         <f>IF(I18="Oui",H18*J18,H18)</f>
         <v/>
       </c>
-      <c r="M18" s="33" t="n"/>
-      <c r="N18" s="31">
+      <c r="M18" s="34" t="n"/>
+      <c r="N18" s="32">
         <f>IF(N(M18)&gt;0,M18,(G18+H18)/2)</f>
         <v/>
       </c>
@@ -5184,25 +5211,25 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Revêtements / finitions</t>
         </is>
       </c>
-      <c r="B19" s="28" t="n"/>
-      <c r="C19" s="28" t="n"/>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="28" t="n"/>
-      <c r="F19" s="28" t="n"/>
-      <c r="G19" s="28" t="n"/>
-      <c r="H19" s="28" t="n"/>
-      <c r="I19" s="28" t="n"/>
-      <c r="J19" s="28" t="n"/>
-      <c r="K19" s="28" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="28" t="n"/>
-      <c r="N19" s="28" t="n"/>
-      <c r="O19" s="28" t="n"/>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="29" t="n"/>
+      <c r="I19" s="29" t="n"/>
+      <c r="J19" s="29" t="n"/>
+      <c r="K19" s="29" t="n"/>
+      <c r="L19" s="29" t="n"/>
+      <c r="M19" s="29" t="n"/>
+      <c r="N19" s="29" t="n"/>
+      <c r="O19" s="29" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
@@ -5216,41 +5243,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="31" t="n">
         <v>110</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="32">
         <f>D20*E20</f>
         <v/>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="32">
         <f>D20*F20</f>
         <v/>
       </c>
-      <c r="I20" s="29" t="inlineStr">
+      <c r="I20" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J20" s="32" t="n">
+      <c r="J20" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="32">
         <f>IF(I20="Oui",G20*J20,G20)</f>
         <v/>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="32">
         <f>IF(I20="Oui",H20*J20,H20)</f>
         <v/>
       </c>
-      <c r="M20" s="33" t="n"/>
-      <c r="N20" s="31">
+      <c r="M20" s="34" t="n"/>
+      <c r="N20" s="32">
         <f>IF(N(M20)&gt;0,M20,(G20+H20)/2)</f>
         <v/>
       </c>
@@ -5268,41 +5295,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="30" t="n">
         <v>150</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <f>D21*E21</f>
         <v/>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <f>D21*F21</f>
         <v/>
       </c>
-      <c r="I21" s="29" t="inlineStr">
+      <c r="I21" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J21" s="32" t="n">
+      <c r="J21" s="33" t="n">
         <v>0.25</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <f>IF(I21="Oui",G21*J21,G21)</f>
         <v/>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <f>IF(I21="Oui",H21*J21,H21)</f>
         <v/>
       </c>
-      <c r="M21" s="33" t="n"/>
-      <c r="N21" s="31">
+      <c r="M21" s="34" t="n"/>
+      <c r="N21" s="32">
         <f>IF(N(M21)&gt;0,M21,(G21+H21)/2)</f>
         <v/>
       </c>
@@ -5324,41 +5351,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="30" t="n">
+      <c r="E22" s="31" t="n">
         <v>600</v>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F22" s="31" t="n">
         <v>1500</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <f>D22*E22</f>
         <v/>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <f>D22*F22</f>
         <v/>
       </c>
-      <c r="I22" s="29" t="inlineStr">
+      <c r="I22" s="30" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J22" s="32" t="n">
+      <c r="J22" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="32">
         <f>IF(I22="Oui",G22*J22,G22)</f>
         <v/>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="32">
         <f>IF(I22="Oui",H22*J22,H22)</f>
         <v/>
       </c>
-      <c r="M22" s="33" t="n"/>
-      <c r="N22" s="31">
+      <c r="M22" s="34" t="n"/>
+      <c r="N22" s="32">
         <f>IF(N(M22)&gt;0,M22,(G22+H22)/2)</f>
         <v/>
       </c>
@@ -5369,145 +5396,145 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="36">
         <f>SUM(G5:G22)</f>
         <v/>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="36">
         <f>SUM(H5:H22)</f>
         <v/>
       </c>
-      <c r="K24" s="35">
+      <c r="K24" s="36">
         <f>SUM(K5:K22)</f>
         <v/>
       </c>
-      <c r="L24" s="35">
+      <c r="L24" s="36">
         <f>SUM(L5:L22)</f>
         <v/>
       </c>
-      <c r="N24" s="35">
+      <c r="N24" s="36">
         <f>SUM(N5:N22)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Imprévus</t>
         </is>
       </c>
-      <c r="G25" s="37">
+      <c r="G25" s="38">
         <f>G24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="H25" s="37">
+      <c r="H25" s="38">
         <f>H24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="K25" s="37">
+      <c r="K25" s="38">
         <f>K24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="L25" s="37">
+      <c r="L25" s="38">
         <f>L24*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="N25" s="37">
+      <c r="N25" s="38">
         <f>N24*Paramètres!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre</t>
         </is>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="38">
         <f>G24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="H26" s="37">
+      <c r="H26" s="38">
         <f>H24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="38">
         <f>K24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="L26" s="37">
+      <c r="L26" s="38">
         <f>L24*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="N26" s="37">
+      <c r="N26" s="38">
         <f>N24*Paramètres!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="n"/>
-      <c r="B27" s="39" t="inlineStr">
+      <c r="A27" s="39" t="n"/>
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>TOTAL RDC TTC</t>
         </is>
       </c>
-      <c r="C27" s="38" t="n"/>
-      <c r="D27" s="38" t="n"/>
-      <c r="E27" s="38" t="n"/>
-      <c r="F27" s="38" t="n"/>
-      <c r="G27" s="40">
+      <c r="C27" s="39" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="41">
         <f>G24+G25+G26</f>
         <v/>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="41">
         <f>H24+H25+H26</f>
         <v/>
       </c>
-      <c r="I27" s="38" t="n"/>
-      <c r="J27" s="38" t="n"/>
-      <c r="K27" s="40">
+      <c r="I27" s="39" t="n"/>
+      <c r="J27" s="39" t="n"/>
+      <c r="K27" s="41">
         <f>K24+K25+K26</f>
         <v/>
       </c>
-      <c r="L27" s="40">
+      <c r="L27" s="41">
         <f>L24+L25+L26</f>
         <v/>
       </c>
-      <c r="M27" s="38" t="n"/>
-      <c r="N27" s="40">
+      <c r="M27" s="39" t="n"/>
+      <c r="N27" s="41">
         <f>N24+N25+N26</f>
         <v/>
       </c>
-      <c r="O27" s="38" t="n"/>
+      <c r="O27" s="39" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>Soit par m² (77 m²)</t>
         </is>
       </c>
-      <c r="G28" s="41">
+      <c r="G28" s="42">
         <f>G27/77</f>
         <v/>
       </c>
-      <c r="H28" s="41">
+      <c r="H28" s="42">
         <f>H27/77</f>
         <v/>
       </c>
-      <c r="K28" s="41">
+      <c r="K28" s="42">
         <f>K27/77</f>
         <v/>
       </c>
-      <c r="L28" s="41">
+      <c r="L28" s="42">
         <f>L27/77</f>
         <v/>
       </c>
-      <c r="N28" s="41">
+      <c r="N28" s="42">
         <f>N27/77</f>
         <v/>
       </c>
@@ -5662,25 +5689,25 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Couverture (260 m²)</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="28" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="28" t="n"/>
-      <c r="I5" s="28" t="n"/>
-      <c r="J5" s="28" t="n"/>
-      <c r="K5" s="28" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="28" t="n"/>
-      <c r="N5" s="28" t="n"/>
-      <c r="O5" s="28" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="29" t="n"/>
+      <c r="O5" s="29" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n"/>
@@ -5694,41 +5721,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>260</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="32">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="32">
         <f>D6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J6" s="32" t="n">
+      <c r="J6" s="33" t="n">
         <v>0.3</v>
       </c>
-      <c r="K6" s="31">
+      <c r="K6" s="32">
         <f>IF(I6="Oui",G6*J6,G6)</f>
         <v/>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="32">
         <f>IF(I6="Oui",H6*J6,H6)</f>
         <v/>
       </c>
-      <c r="M6" s="33" t="n"/>
-      <c r="N6" s="31">
+      <c r="M6" s="34" t="n"/>
+      <c r="N6" s="32">
         <f>IF(N(M6)&gt;0,M6,(G6+H6)/2)</f>
         <v/>
       </c>
@@ -5746,41 +5773,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>260</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>D7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J7" s="32" t="n">
+      <c r="J7" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="32">
         <f>IF(I7="Oui",G7*J7,G7)</f>
         <v/>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="32">
         <f>IF(I7="Oui",H7*J7,H7)</f>
         <v/>
       </c>
-      <c r="M7" s="33" t="n"/>
-      <c r="N7" s="31">
+      <c r="M7" s="34" t="n"/>
+      <c r="N7" s="32">
         <f>IF(N(M7)&gt;0,M7,(G7+H7)/2)</f>
         <v/>
       </c>
@@ -5798,41 +5825,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>260</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="31" t="n">
         <v>90</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>D8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J8" s="32" t="n">
+      <c r="J8" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="32">
         <f>IF(I8="Oui",G8*J8,G8)</f>
         <v/>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="32">
         <f>IF(I8="Oui",H8*J8,H8)</f>
         <v/>
       </c>
-      <c r="M8" s="33" t="n"/>
-      <c r="N8" s="31">
+      <c r="M8" s="34" t="n"/>
+      <c r="N8" s="32">
         <f>IF(N(M8)&gt;0,M8,(G8+H8)/2)</f>
         <v/>
       </c>
@@ -5854,41 +5881,41 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="32">
         <f>D9*E9</f>
         <v/>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="32">
         <f>D9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J9" s="32" t="n">
+      <c r="J9" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="32">
         <f>IF(I9="Oui",G9*J9,G9)</f>
         <v/>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="32">
         <f>IF(I9="Oui",H9*J9,H9)</f>
         <v/>
       </c>
-      <c r="M9" s="33" t="n"/>
-      <c r="N9" s="31">
+      <c r="M9" s="34" t="n"/>
+      <c r="N9" s="32">
         <f>IF(N(M9)&gt;0,M9,(G9+H9)/2)</f>
         <v/>
       </c>
@@ -5910,41 +5937,41 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>D10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="29" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J10" s="32" t="n">
+      <c r="J10" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="32">
         <f>IF(I10="Oui",G10*J10,G10)</f>
         <v/>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="32">
         <f>IF(I10="Oui",H10*J10,H10)</f>
         <v/>
       </c>
-      <c r="M10" s="33" t="n"/>
-      <c r="N10" s="31">
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="32">
         <f>IF(N(M10)&gt;0,M10,(G10+H10)/2)</f>
         <v/>
       </c>
@@ -5955,25 +5982,25 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Façades (maison + grange)</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n"/>
-      <c r="C11" s="28" t="n"/>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="28" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="28" t="n"/>
-      <c r="J11" s="28" t="n"/>
-      <c r="K11" s="28" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="28" t="n"/>
-      <c r="N11" s="28" t="n"/>
-      <c r="O11" s="28" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="29" t="n"/>
+      <c r="H11" s="29" t="n"/>
+      <c r="I11" s="29" t="n"/>
+      <c r="J11" s="29" t="n"/>
+      <c r="K11" s="29" t="n"/>
+      <c r="L11" s="29" t="n"/>
+      <c r="M11" s="29" t="n"/>
+      <c r="N11" s="29" t="n"/>
+      <c r="O11" s="29" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
@@ -5987,41 +6014,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="30" t="n">
         <v>400</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F12" s="31" t="n">
         <v>120</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="32">
         <f>D12*E12</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="32">
         <f>D12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J12" s="32" t="n">
+      <c r="J12" s="33" t="n">
         <v>0.35</v>
       </c>
-      <c r="K12" s="31">
+      <c r="K12" s="32">
         <f>IF(I12="Oui",G12*J12,G12)</f>
         <v/>
       </c>
-      <c r="L12" s="31">
+      <c r="L12" s="32">
         <f>IF(I12="Oui",H12*J12,H12)</f>
         <v/>
       </c>
-      <c r="M12" s="33" t="n"/>
-      <c r="N12" s="31">
+      <c r="M12" s="34" t="n"/>
+      <c r="N12" s="32">
         <f>IF(N(M12)&gt;0,M12,(G12+H12)/2)</f>
         <v/>
       </c>
@@ -6043,66 +6070,66 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="31" t="n">
         <v>2000</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="31" t="n">
         <v>6000</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>D13*E13</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>D13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J13" s="32" t="n">
+      <c r="J13" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="K13" s="31">
+      <c r="K13" s="32">
         <f>IF(I13="Oui",G13*J13,G13)</f>
         <v/>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="32">
         <f>IF(I13="Oui",H13*J13,H13)</f>
         <v/>
       </c>
-      <c r="M13" s="33" t="n"/>
-      <c r="N13" s="31">
+      <c r="M13" s="34" t="n"/>
+      <c r="N13" s="32">
         <f>IF(N(M13)&gt;0,M13,(G13+H13)/2)</f>
         <v/>
       </c>
       <c r="O13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Charpente / sécurité</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="28" t="n"/>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="28" t="n"/>
-      <c r="J14" s="28" t="n"/>
-      <c r="K14" s="28" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="28" t="n"/>
-      <c r="N14" s="28" t="n"/>
-      <c r="O14" s="28" t="n"/>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="29" t="n"/>
+      <c r="I14" s="29" t="n"/>
+      <c r="J14" s="29" t="n"/>
+      <c r="K14" s="29" t="n"/>
+      <c r="L14" s="29" t="n"/>
+      <c r="M14" s="29" t="n"/>
+      <c r="N14" s="29" t="n"/>
+      <c r="O14" s="29" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -6116,41 +6143,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="31" t="n">
         <v>2000</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>D15*E15</f>
         <v/>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="32">
         <f>D15*F15</f>
         <v/>
       </c>
-      <c r="I15" s="29" t="inlineStr">
+      <c r="I15" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J15" s="32" t="n">
+      <c r="J15" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="32">
         <f>IF(I15="Oui",G15*J15,G15)</f>
         <v/>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="32">
         <f>IF(I15="Oui",H15*J15,H15)</f>
         <v/>
       </c>
-      <c r="M15" s="33" t="n"/>
-      <c r="N15" s="31">
+      <c r="M15" s="34" t="n"/>
+      <c r="N15" s="32">
         <f>IF(N(M15)&gt;0,M15,(G15+H15)/2)</f>
         <v/>
       </c>
@@ -6172,41 +6199,41 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="31" t="n">
         <v>4000</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>D16*E16</f>
         <v/>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="32">
         <f>D16*F16</f>
         <v/>
       </c>
-      <c r="I16" s="29" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J16" s="32" t="n">
+      <c r="J16" s="33" t="n">
         <v>0.3</v>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="32">
         <f>IF(I16="Oui",G16*J16,G16)</f>
         <v/>
       </c>
-      <c r="L16" s="31">
+      <c r="L16" s="32">
         <f>IF(I16="Oui",H16*J16,H16)</f>
         <v/>
       </c>
-      <c r="M16" s="33" t="n"/>
-      <c r="N16" s="31">
+      <c r="M16" s="34" t="n"/>
+      <c r="N16" s="32">
         <f>IF(N(M16)&gt;0,M16,(G16+H16)/2)</f>
         <v/>
       </c>
@@ -6217,145 +6244,145 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Sous-total travaux</t>
         </is>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="36">
         <f>SUM(G5:G16)</f>
         <v/>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="36">
         <f>SUM(H5:H16)</f>
         <v/>
       </c>
-      <c r="K18" s="35">
+      <c r="K18" s="36">
         <f>SUM(K5:K16)</f>
         <v/>
       </c>
-      <c r="L18" s="35">
+      <c r="L18" s="36">
         <f>SUM(L5:L16)</f>
         <v/>
       </c>
-      <c r="N18" s="35">
+      <c r="N18" s="36">
         <f>SUM(N5:N16)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Imprévus</t>
         </is>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="38">
         <f>G18*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="H19" s="37">
+      <c r="H19" s="38">
         <f>H18*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="K19" s="37">
+      <c r="K19" s="38">
         <f>K18*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="L19" s="37">
+      <c r="L19" s="38">
         <f>L18*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="N19" s="37">
+      <c r="N19" s="38">
         <f>N18*Paramètres!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre</t>
         </is>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="38">
         <f>G18*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="H20" s="37">
+      <c r="H20" s="38">
         <f>H18*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="K20" s="37">
+      <c r="K20" s="38">
         <f>K18*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="L20" s="37">
+      <c r="L20" s="38">
         <f>L18*Paramètres!$B$5</f>
         <v/>
       </c>
-      <c r="N20" s="37">
+      <c r="N20" s="38">
         <f>N18*Paramètres!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="n"/>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="A21" s="39" t="n"/>
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>TOTAL TOITURE + FAÇADES TTC (sans sarking)</t>
         </is>
       </c>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="38" t="n"/>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="40">
+      <c r="C21" s="39" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="41">
         <f>G18+G19+G20</f>
         <v/>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="41">
         <f>H18+H19+H20</f>
         <v/>
       </c>
-      <c r="I21" s="38" t="n"/>
-      <c r="J21" s="38" t="n"/>
-      <c r="K21" s="40">
+      <c r="I21" s="39" t="n"/>
+      <c r="J21" s="39" t="n"/>
+      <c r="K21" s="41">
         <f>K18+K19+K20</f>
         <v/>
       </c>
-      <c r="L21" s="40">
+      <c r="L21" s="41">
         <f>L18+L19+L20</f>
         <v/>
       </c>
-      <c r="M21" s="38" t="n"/>
-      <c r="N21" s="40">
+      <c r="M21" s="39" t="n"/>
+      <c r="N21" s="41">
         <f>N18+N19+N20</f>
         <v/>
       </c>
-      <c r="O21" s="38" t="n"/>
+      <c r="O21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Soit par m² (260 m²)</t>
         </is>
       </c>
-      <c r="G22" s="41">
+      <c r="G22" s="42">
         <f>G21/260</f>
         <v/>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="42">
         <f>H21/260</f>
         <v/>
       </c>
-      <c r="K22" s="41">
+      <c r="K22" s="42">
         <f>K21/260</f>
         <v/>
       </c>
-      <c r="L22" s="41">
+      <c r="L22" s="42">
         <f>L21/260</f>
         <v/>
       </c>
-      <c r="N22" s="41">
+      <c r="N22" s="42">
         <f>N21/260</f>
         <v/>
       </c>
@@ -6382,29 +6409,29 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="42" t="inlineStr">
+      <c r="A28" s="43" t="inlineStr">
         <is>
           <t>OPTION SARKING</t>
         </is>
       </c>
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>Isolation posée par l'extérieur pendant la réfection (remplace l'isolation intérieure des rampants de l'étage)</t>
         </is>
       </c>
-      <c r="C28" s="43" t="n"/>
-      <c r="D28" s="43" t="n"/>
-      <c r="E28" s="43" t="n"/>
-      <c r="F28" s="43" t="n"/>
-      <c r="G28" s="43" t="n"/>
-      <c r="H28" s="43" t="n"/>
-      <c r="I28" s="43" t="n"/>
-      <c r="J28" s="43" t="n"/>
-      <c r="K28" s="43" t="n"/>
-      <c r="L28" s="43" t="n"/>
-      <c r="M28" s="43" t="n"/>
-      <c r="N28" s="43" t="n"/>
-      <c r="O28" s="43" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+      <c r="F28" s="44" t="n"/>
+      <c r="G28" s="44" t="n"/>
+      <c r="H28" s="44" t="n"/>
+      <c r="I28" s="44" t="n"/>
+      <c r="J28" s="44" t="n"/>
+      <c r="K28" s="44" t="n"/>
+      <c r="L28" s="44" t="n"/>
+      <c r="M28" s="44" t="n"/>
+      <c r="N28" s="44" t="n"/>
+      <c r="O28" s="44" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -6418,41 +6445,41 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="30" t="n">
         <v>260</v>
       </c>
-      <c r="E29" s="30" t="n">
+      <c r="E29" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="F29" s="30" t="n">
+      <c r="F29" s="31" t="n">
         <v>150</v>
       </c>
-      <c r="G29" s="31">
+      <c r="G29" s="32">
         <f>D29*E29</f>
         <v/>
       </c>
-      <c r="H29" s="31">
+      <c r="H29" s="32">
         <f>D29*F29</f>
         <v/>
       </c>
-      <c r="I29" s="29" t="inlineStr">
+      <c r="I29" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J29" s="32" t="n">
+      <c r="J29" s="33" t="n">
         <v>0.55</v>
       </c>
-      <c r="K29" s="31">
+      <c r="K29" s="32">
         <f>IF(I29="Oui",G29*J29,G29)</f>
         <v/>
       </c>
-      <c r="L29" s="31">
+      <c r="L29" s="32">
         <f>IF(I29="Oui",H29*J29,H29)</f>
         <v/>
       </c>
-      <c r="M29" s="33" t="n"/>
-      <c r="N29" s="31">
+      <c r="M29" s="34" t="n"/>
+      <c r="N29" s="32">
         <f>IF(N(M29)&gt;0,M29,(G29+H29)/2)</f>
         <v/>
       </c>
@@ -6474,135 +6501,135 @@
           <t>forfait</t>
         </is>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="30" t="n">
+      <c r="E30" s="31" t="n">
         <v>1500</v>
       </c>
-      <c r="F30" s="30" t="n">
+      <c r="F30" s="31" t="n">
         <v>4000</v>
       </c>
-      <c r="G30" s="31">
+      <c r="G30" s="32">
         <f>D30*E30</f>
         <v/>
       </c>
-      <c r="H30" s="31">
+      <c r="H30" s="32">
         <f>D30*F30</f>
         <v/>
       </c>
-      <c r="I30" s="29" t="inlineStr">
+      <c r="I30" s="30" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="J30" s="32" t="n">
+      <c r="J30" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="K30" s="31">
+      <c r="K30" s="32">
         <f>IF(I30="Oui",G30*J30,G30)</f>
         <v/>
       </c>
-      <c r="L30" s="31">
+      <c r="L30" s="32">
         <f>IF(I30="Oui",H30*J30,H30)</f>
         <v/>
       </c>
-      <c r="M30" s="33" t="n"/>
-      <c r="N30" s="31">
+      <c r="M30" s="34" t="n"/>
+      <c r="N30" s="32">
         <f>IF(N(M30)&gt;0,M30,(G30+H30)/2)</f>
         <v/>
       </c>
       <c r="O30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Sous-total option sarking</t>
         </is>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="36">
         <f>SUM(G29:G30)</f>
         <v/>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="36">
         <f>SUM(H29:H30)</f>
         <v/>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="36">
         <f>SUM(K29:K30)</f>
         <v/>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="36">
         <f>SUM(L29:L30)</f>
         <v/>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="36">
         <f>SUM(N29:N30)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="37" t="inlineStr">
         <is>
           <t>Économie : isolation intérieure des rampants supprimée (onglet étage)</t>
         </is>
       </c>
-      <c r="G32" s="37">
+      <c r="G32" s="38">
         <f>-'Budget étage'!G10</f>
         <v/>
       </c>
-      <c r="H32" s="37">
+      <c r="H32" s="38">
         <f>-'Budget étage'!H10</f>
         <v/>
       </c>
-      <c r="K32" s="37">
+      <c r="K32" s="38">
         <f>-'Budget étage'!K10</f>
         <v/>
       </c>
-      <c r="L32" s="37">
+      <c r="L32" s="38">
         <f>-'Budget étage'!L10</f>
         <v/>
       </c>
-      <c r="N32" s="37">
+      <c r="N32" s="38">
         <f>-'Budget étage'!N10</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="n"/>
-      <c r="B33" s="39" t="inlineStr">
+      <c r="A33" s="39" t="n"/>
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>SURCOÛT NET OPTION SARKING TTC (imprévus + MOE inclus)</t>
         </is>
       </c>
-      <c r="C33" s="38" t="n"/>
-      <c r="D33" s="38" t="n"/>
-      <c r="E33" s="38" t="n"/>
-      <c r="F33" s="38" t="n"/>
-      <c r="G33" s="40">
+      <c r="C33" s="39" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="41">
         <f>(G31+G32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="H33" s="40">
+      <c r="H33" s="41">
         <f>(H31+H32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="I33" s="38" t="n"/>
-      <c r="J33" s="38" t="n"/>
-      <c r="K33" s="40">
+      <c r="I33" s="39" t="n"/>
+      <c r="J33" s="39" t="n"/>
+      <c r="K33" s="41">
         <f>(K31+K32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="L33" s="40">
+      <c r="L33" s="41">
         <f>(L31+L32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="M33" s="38" t="n"/>
-      <c r="N33" s="40">
+      <c r="M33" s="39" t="n"/>
+      <c r="N33" s="41">
         <f>(N31+N32)*(1+Paramètres!$B$4+Paramètres!$B$5)</f>
         <v/>
       </c>
-      <c r="O33" s="38" t="n"/>
+      <c r="O33" s="39" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="10" t="inlineStr">
@@ -6628,7 +6655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -6645,154 +6672,208 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Paramètre</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Imprévus (% des travaux)</t>
         </is>
       </c>
-      <c r="B4" s="44" t="n">
+      <c r="B4" s="45" t="n">
         <v>0.1</v>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>Usuel en rénovation de bâti ancien : 10 à 15 %.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Maîtrise d'œuvre / architecte (% des travaux)</t>
         </is>
       </c>
-      <c r="B5" s="44" t="n">
+      <c r="B5" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>0 % si vous pilotez vous-même ; 8 à 12 % avec un maître d'œuvre.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>TVA : prix affichés TTC à 20 % (création de surface habitable dans une grange : taux réduit en principe non applicable).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Postes HORS budget étage (à chiffrer séparément)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>Min €</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
+      <c r="C10" s="43" t="inlineStr">
         <is>
           <t>Max €</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="D10" s="43" t="inlineStr">
         <is>
           <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Raccordements eau / électricité / assainissement individuel</t>
         </is>
       </c>
-      <c r="B11" s="46" t="n">
+      <c r="B11" s="47" t="n">
         <v>8000</v>
       </c>
-      <c r="C11" s="46" t="n">
+      <c r="C11" s="47" t="n">
         <v>15000</v>
       </c>
-      <c r="D11" s="36" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Selon raccordement existant de la grange.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Renfort du plancher / chape</t>
         </is>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="47" t="n">
         <v>5000</v>
       </c>
-      <c r="C12" s="46" t="n">
+      <c r="C12" s="47" t="n">
         <v>12000</v>
       </c>
-      <c r="D12" s="36" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Si le plancher de l'étage est insuffisant.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Taxe d'aménagement + dossier changement de destination</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="47" t="n">
         <v>2000</v>
       </c>
-      <c r="C13" s="46" t="n">
+      <c r="C13" s="47" t="n">
         <v>5000</v>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Selon taux communal et départemental.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>Mise à niveau de l'assainissement (microstation 5 EH → 7 EH mini)</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C14" s="47" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Promesse : OXYFIX C-90 5 EH pour 3 pièces principales ; 6 chambres = 7 EH. Étude + accord SPANC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>Électricité de la maison existante (anomalies au diagnostic)</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C15" s="47" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>Diagnostic 09/2025 : différentiel, terre, SdB, matériel vétuste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>Désamiantage conduit en cave (si touché)</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C16" s="47" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>Repérage amiante 09/2025 : conduit de fluides, évaluation périodique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>Total hors budget</t>
         </is>
       </c>
-      <c r="B14" s="35">
-        <f>SUM(B11:B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="35">
-        <f>SUM(C11:C13)</f>
+      <c r="B17" s="36">
+        <f>SUM(B11:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="36">
+        <f>SUM(C11:C16)</f>
         <v/>
       </c>
     </row>
